--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,30 +574,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86.7</v>
+        <v>63.3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>135000</v>
+        <v>94000</v>
       </c>
       <c r="E3" t="n">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
-        <v>794.1</v>
+        <v>862.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,32 +627,32 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>VENTA CASA 5 AMBIENTES ALTO DORREGO MENDOZA</t>
+          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19363/ficha/casa-en-venta-en-zeballos-500</t>
+          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 94,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56.2</v>
+        <v>60.9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -661,17 +661,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63000</v>
+        <v>98000</v>
       </c>
       <c r="E4" t="n">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>463.2</v>
+        <v>1225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -696,37 +696,37 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>Coldwell Banker ImpactoPro ofrece en venta departamento en planta baja con patio y cochera en Godoy Cruz,</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/43/ficha/departamento-en-venta-en-gutierrez-598</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 98,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55.3</v>
+        <v>56.2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95000</v>
+        <v>63000</v>
       </c>
       <c r="E5" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>871.6</v>
+        <v>463.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,26 +796,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51.6</v>
+        <v>55.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>120000</v>
+        <v>95000</v>
       </c>
       <c r="E6" t="n">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>779.2</v>
+        <v>871.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>OFRECE EN VENTA</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,11 +870,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>50.8</v>
+        <v>52.2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,17 +883,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68000</v>
+        <v>90000</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>906.7</v>
+        <v>900</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -923,47 +923,47 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>ADOBE INMOBILIARIA VENDE  DÚPLEX EN GODOY CRUZ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/403/ficha/departamento-en-venta-en-perito-moreno-al-500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48.3</v>
+        <v>51.6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>130000</v>
+        <v>120000</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="F8" t="n">
-        <v>1733.3</v>
+        <v>779.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>OFRECE EN VENTA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48.1</v>
+        <v>50.8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63000</v>
+        <v>68000</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>562.5</v>
+        <v>906.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,22 +1071,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Oportunidad de inversión!</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75000</v>
+        <v>63000</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
-        <v>1000</v>
+        <v>562.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Oportunidad de inversión!</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86000</v>
+        <v>75000</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>1228.6</v>
+        <v>1000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.3</v>
+        <v>47.7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79000</v>
+        <v>86000</v>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>718.2</v>
+        <v>1228.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,7 +1314,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.2</v>
+        <v>46.6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>140000</v>
+        <v>90000</v>
       </c>
       <c r="E13" t="n">
-        <v>575</v>
+        <v>96</v>
       </c>
       <c r="F13" t="n">
-        <v>243.5</v>
+        <v>937.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>OPENHOUSE vende desarrollo en obra gruesa sobre calle Pascual Segura de Godoy Cruz</t>
+          <t>Departamento en Venta en Godoy Cruz</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2063/ficha/departamento-en-venta-en-pascual-segura-godoy-cruz</t>
+          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/22/ficha/departamento-en-venta-en-san-martin-1338</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1462,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>39.9</v>
+        <v>41.4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70000</v>
+        <v>85000</v>
       </c>
       <c r="E15" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="F15" t="n">
-        <v>1000</v>
+        <v>904.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>Venta departamento en Godoy Cruz planta baja apto crédito 3 dormitorios reciclado</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19508/ficha/departamento-en-venta-en-salta-400</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 85,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>140000</v>
+        <v>70000</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>1866.7</v>
+        <v>1000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>130000</v>
+        <v>140000</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>1756.8</v>
+        <v>1866.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1663,17 +1663,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>Departamento en Venta – Mendoza Capital</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1684,7 +1684,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36.6</v>
+        <v>39.8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>98000</v>
+        <v>130000</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>890.9</v>
+        <v>1756.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>SCAFFIDI PROPIEDADES VENDE</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12373-scaffidi-propiedades/inmuebles/269/ficha/departamento-en-venta-en-mitre-565</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 98,000)</t>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>36.5</v>
+        <v>37.3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>90000</v>
       </c>
       <c r="E19" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="F19" t="n">
-        <v>873.8</v>
+        <v>656.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1832,11 +1832,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35</v>
+        <v>37.2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1848,10 +1848,10 @@
         <v>90000</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>1097.6</v>
+        <v>1363.6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
+          <t>En el corazón del Barrio Bombal, se encuentra este hermoso departamento en planta alta por escalera. Con una superficie total de 80 metros cuadrados y 66 metros cubiertos, cuenta con dos dormitorios, el principal con baño en suite zonificado, y un balcón que proporciona excelente ventilación e iluminación natural. La propiedad no posee gas, siendo todo eléctrico, lo que garantiza un ambiente seguro y eficiente.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/258/ficha/departamento-en-venta-en-roque-saenz-pena-2051</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>34.9</v>
+        <v>36.6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77500</v>
+        <v>98000</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="F21" t="n">
-        <v>1174.2</v>
+        <v>890.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1959,22 +1959,980 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>SCAFFIDI PROPIEDADES VENDE</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://www.inmoclick.com.ar/12373-scaffidi-propiedades/inmuebles/269/ficha/departamento-en-venta-en-mitre-565</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 98,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" t="n">
+        <v>580</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 58,000)</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>103</v>
+      </c>
+      <c r="F23" t="n">
+        <v>873.8</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>88</v>
+      </c>
+      <c r="F25" t="n">
+        <v>625</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 55,000)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>93</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 99,000)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Departamento En Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 110,000)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>90</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1333.3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 120,000)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>124900</v>
+      </c>
+      <c r="E29" t="n">
+        <v>87</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1435.6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 124,900)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>128000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>87</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1471.3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Venta Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 128,000)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>63300</v>
+      </c>
+      <c r="E31" t="n">
+        <v>73</v>
+      </c>
+      <c r="F31" t="n">
+        <v>867.1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Departamento En Gobernador Benegas</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 63,300)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>74</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>86000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>71</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1211.3</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 86,000)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>79</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1898.7</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,11 +574,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.3</v>
+        <v>56.2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,17 +587,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>94000</v>
+        <v>63000</v>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F3" t="n">
-        <v>862.4</v>
+        <v>463.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -627,28 +627,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 94,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60.9</v>
+        <v>55.3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,17 +661,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>98000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>1225</v>
+        <v>871.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -696,33 +696,33 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Coldwell Banker ImpactoPro ofrece en venta departamento en planta baja con patio y cochera en Godoy Cruz,</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/43/ficha/departamento-en-venta-en-gutierrez-598</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 98,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56.2</v>
+        <v>51.6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63000</v>
+        <v>120000</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
-        <v>463.2</v>
+        <v>779.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>OFRECE EN VENTA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55.3</v>
+        <v>50.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,17 +809,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95000</v>
+        <v>68000</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>871.6</v>
+        <v>906.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,28 +849,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52.2</v>
+        <v>48.3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>900</v>
+        <v>1733.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ADOBE INMOBILIARIA VENDE  DÚPLEX EN GODOY CRUZ</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/403/ficha/departamento-en-venta-en-perito-moreno-al-500</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51.6</v>
+        <v>48.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,17 +953,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120000</v>
+        <v>63000</v>
       </c>
       <c r="E8" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>779.2</v>
+        <v>562.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>OFRECE EN VENTA</t>
+          <t>Oportunidad de inversión!</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
+          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,11 +1018,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50.8</v>
+        <v>48.1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68000</v>
+        <v>75000</v>
       </c>
       <c r="E9" t="n">
         <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>906.7</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63000</v>
+        <v>86000</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>562.5</v>
+        <v>1228.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Oportunidad de inversión!</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48.1</v>
+        <v>45.3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75000</v>
+        <v>79000</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>1000</v>
+        <v>718.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.7</v>
+        <v>45.2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>86000</v>
+        <v>140000</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>575</v>
       </c>
       <c r="F12" t="n">
-        <v>1228.6</v>
+        <v>243.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>OPENHOUSE vende desarrollo en obra gruesa sobre calle Pascual Segura de Godoy Cruz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2063/ficha/departamento-en-venta-en-pascual-segura-godoy-cruz</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,11 +1314,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>46.6</v>
+        <v>43.4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>937.5</v>
+        <v>1233.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Departamento en Venta en Godoy Cruz</t>
+          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/22/ficha/departamento-en-venta-en-san-martin-1338</t>
+          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43.4</v>
+        <v>39.9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>95000</v>
+        <v>70000</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>1233.8</v>
+        <v>1000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>41.4</v>
+        <v>39.8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85000</v>
+        <v>140000</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>904.3</v>
+        <v>1866.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta departamento en Godoy Cruz planta baja apto crédito 3 dormitorios reciclado</t>
+          <t>Departamento en Venta – Mendoza Capital</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19508/ficha/departamento-en-venta-en-salta-400</t>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 85,000)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70000</v>
+        <v>130000</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>1000</v>
+        <v>1756.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,7 +1610,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39.8</v>
+        <v>37.3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>140000</v>
+        <v>90000</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>1866.7</v>
+        <v>656.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1684,7 +1684,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39.8</v>
+        <v>36.6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>130000</v>
+        <v>98000</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="F18" t="n">
-        <v>1756.8</v>
+        <v>890.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>SCAFFIDI PROPIEDADES VENDE</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/12373-scaffidi-propiedades/inmuebles/269/ficha/departamento-en-venta-en-mitre-565</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 98,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,11 +1758,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>37.3</v>
+        <v>36.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90000</v>
+        <v>58000</v>
       </c>
       <c r="E19" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>656.9</v>
+        <v>580</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1832,11 +1832,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37.2</v>
+        <v>36.5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1848,10 +1848,10 @@
         <v>90000</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F20" t="n">
-        <v>1363.6</v>
+        <v>873.8</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>En el corazón del Barrio Bombal, se encuentra este hermoso departamento en planta alta por escalera. Con una superficie total de 80 metros cuadrados y 66 metros cubiertos, cuenta con dos dormitorios, el principal con baño en suite zonificado, y un balcón que proporciona excelente ventilación e iluminación natural. La propiedad no posee gas, siendo todo eléctrico, lo que garantiza un ambiente seguro y eficiente.</t>
+          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/258/ficha/departamento-en-venta-en-roque-saenz-pena-2051</t>
+          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,11 +1906,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>36.6</v>
+        <v>35.9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>98000</v>
+        <v>80000</v>
       </c>
       <c r="E21" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F21" t="n">
-        <v>890.9</v>
+        <v>888.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1959,17 +1959,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>SCAFFIDI PROPIEDADES VENDE</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12373-scaffidi-propiedades/inmuebles/269/ficha/departamento-en-venta-en-mitre-565</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 98,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,11 +1980,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>36.6</v>
+        <v>35.7</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58000</v>
+        <v>55000</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,17 +2033,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2054,11 +2054,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>36.5</v>
+        <v>35.3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>90000</v>
+        <v>99000</v>
       </c>
       <c r="E23" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>873.8</v>
+        <v>1064.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2107,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,11 +2128,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>35.9</v>
+        <v>35.3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>888.9</v>
+        <v>1100</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,11 +2202,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55000</v>
+        <v>77500</v>
       </c>
       <c r="E25" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
-        <v>625</v>
+        <v>1174.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000)</t>
+          <t>Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2276,11 +2276,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>35.3</v>
+        <v>34</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>99000</v>
+        <v>120000</v>
       </c>
       <c r="E26" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>1064.5</v>
+        <v>1333.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2329,17 +2329,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 99,000)</t>
+          <t>Dentro del presupuesto (USD 120,000)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2350,11 +2350,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>110000</v>
+        <v>124900</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="F27" t="n">
-        <v>1100</v>
+        <v>1435.6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2403,17 +2403,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2424,11 +2424,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>33.3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>120000</v>
+        <v>128000</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F28" t="n">
-        <v>1333.3</v>
+        <v>1471.3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2477,17 +2477,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000)</t>
+          <t>Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>33.5</v>
+        <v>31.1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>124900</v>
+        <v>63300</v>
       </c>
       <c r="E29" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F29" t="n">
-        <v>1435.6</v>
+        <v>867.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2551,17 +2551,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 124,900)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2572,7 +2572,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>33.3</v>
+        <v>30.2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>128000</v>
+        <v>150000</v>
       </c>
       <c r="E30" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F30" t="n">
-        <v>1471.3</v>
+        <v>2027</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2620,33 +2620,33 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 128,000)</t>
+          <t>🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31.1</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63300</v>
+        <v>86000</v>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F31" t="n">
-        <v>867.1</v>
+        <v>1211.3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2699,17 +2699,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Departamento En Gobernador Benegas</t>
+          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
+          <t>Dentro del presupuesto (USD 86,000)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2720,7 +2720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>150000</v>
       </c>
       <c r="E32" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F32" t="n">
-        <v>2027</v>
+        <v>1898.7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2773,164 +2773,16 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🚗 Cuenta con cochera</t>
-        </is>
-      </c>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
-        <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>86000</v>
-      </c>
-      <c r="E33" t="n">
-        <v>71</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1211.3</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 86,000)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>79</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1898.7</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
         <is>
           <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91.5</v>
+        <v>82.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>89999</v>
+        <v>100000</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>818.2</v>
+        <v>1000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA EN 25 DE MAYO, MENDOZA CAPITAL</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19405/ficha/departamento-en-venta-en-25-de-mayo-900</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 100,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56.2</v>
+        <v>51.6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63000</v>
+        <v>120000</v>
       </c>
       <c r="E3" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="F3" t="n">
-        <v>463.2</v>
+        <v>779.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>OFRECE EN VENTA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55.3</v>
+        <v>48.3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>130000</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>871.6</v>
+        <v>1733.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51.6</v>
+        <v>45.7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -731,17 +731,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>154</v>
-      </c>
-      <c r="F5" t="n">
-        <v>779.2</v>
+        <v>140000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +779,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OFRECE EN VENTA</t>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +800,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50.8</v>
+        <v>45.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,22 +813,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68000</v>
+        <v>79000</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>906.7</v>
+        <v>718.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,32 +853,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>48.3</v>
+        <v>44.6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +887,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>130000</v>
+        <v>90000</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>1733.3</v>
+        <v>1384.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +927,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,11 +948,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48.1</v>
+        <v>40.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,13 +961,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63000</v>
+        <v>95000</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>562.5</v>
+        <v>871.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,32 +1001,32 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Oportunidad de inversión!</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48.1</v>
+        <v>38.4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,22 +1035,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75000</v>
+        <v>55000</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>1000</v>
+        <v>763.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,32 +1075,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.7</v>
+        <v>37.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1109,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86000</v>
+        <v>90000</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
-        <v>1228.6</v>
+        <v>656.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1124,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,17 +1149,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,11 +1170,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45.3</v>
+        <v>35.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1183,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79000</v>
+        <v>55000</v>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>718.2</v>
+        <v>625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1223,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,11 +1244,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.2</v>
+        <v>35.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1257,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>140000</v>
+        <v>110000</v>
       </c>
       <c r="E12" t="n">
-        <v>575</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>243.5</v>
+        <v>1100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,17 +1297,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OPENHOUSE vende desarrollo en obra gruesa sobre calle Pascual Segura de Godoy Cruz</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2063/ficha/departamento-en-venta-en-pascual-segura-godoy-cruz</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,7 +1318,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>43.4</v>
+        <v>35.1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1331,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>95000</v>
+        <v>70000</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
-        <v>1233.8</v>
+        <v>875</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1371,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 70,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1392,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>39.9</v>
+        <v>34.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70000</v>
+        <v>53000</v>
       </c>
       <c r="E14" t="n">
         <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>1000</v>
+        <v>757.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1420,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,17 +1445,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,11 +1466,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>39.8</v>
+        <v>34</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>140000</v>
+        <v>120000</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>1866.7</v>
+        <v>1333.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,17 +1519,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 120,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,11 +1540,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39.8</v>
+        <v>33.5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>130000</v>
+        <v>124900</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>1756.8</v>
+        <v>1435.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1568,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,17 +1593,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,11 +1614,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>37.3</v>
+        <v>33.1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>656.9</v>
+        <v>1000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,32 +1667,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36.6</v>
+        <v>32.7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>98000</v>
+        <v>86000</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>890.9</v>
+        <v>1228.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,28 +1741,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>SCAFFIDI PROPIEDADES VENDE</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12373-scaffidi-propiedades/inmuebles/269/ficha/departamento-en-venta-en-mitre-565</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 98,000)</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>36.6</v>
+        <v>30.2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1775,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58000</v>
+        <v>140000</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>575</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>243.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1790,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,32 +1815,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>OPENHOUSE vende desarrollo en obra gruesa sobre calle Pascual Segura de Godoy Cruz</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2063/ficha/departamento-en-venta-en-pascual-segura-godoy-cruz</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>36.5</v>
+        <v>21.6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1845,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>90000</v>
+        <v>58000</v>
       </c>
       <c r="E20" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>873.8</v>
+        <v>580</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1885,28 +1889,28 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>35.9</v>
+        <v>20.9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1974,17 +1978,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>35.7</v>
+        <v>20.3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1997,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55000</v>
+        <v>99000</v>
       </c>
       <c r="E22" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
-        <v>625</v>
+        <v>1064.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,28 +2037,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000)</t>
+          <t>Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.3</v>
+        <v>20</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>99000</v>
+        <v>150000</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
-        <v>1064.5</v>
+        <v>2027</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2086,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2102,37 +2106,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 99,000)</t>
+          <t>🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>35.3</v>
+        <v>20</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2141,13 +2145,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>110000</v>
+        <v>86000</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>1100</v>
+        <v>1211.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,32 +2185,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 86,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>34.9</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2215,13 +2219,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77500</v>
+        <v>63300</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>1174.2</v>
+        <v>867.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,32 +2259,32 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2289,13 +2293,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="E26" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
-        <v>1333.3</v>
+        <v>1898.7</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2324,33 +2328,29 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 120,000)</t>
-        </is>
-      </c>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>33.5</v>
+        <v>20</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>124900</v>
+        <v>128000</v>
       </c>
       <c r="E27" t="n">
         <v>87</v>
       </c>
       <c r="F27" t="n">
-        <v>1435.6</v>
+        <v>1471.3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2403,388 +2403,22 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 124,900)</t>
+          <t>Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>128000</v>
-      </c>
-      <c r="E28" t="n">
-        <v>87</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1471.3</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Venta Duplex En Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 128,000)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E29" t="n">
-        <v>73</v>
-      </c>
-      <c r="F29" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E30" t="n">
-        <v>74</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>86000</v>
-      </c>
-      <c r="E31" t="n">
-        <v>71</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1211.3</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 86,000)</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E32" t="n">
-        <v>79</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1898.7</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.2</v>
+        <v>96.7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,17 +509,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100000</v>
+        <v>135000</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F2" t="n">
-        <v>1000</v>
+        <v>794.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA EN 25 DE MAYO, MENDOZA CAPITAL</t>
+          <t>VENTA CASA 5 AMBIENTES ALTO DORREGO MENDOZA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19405/ficha/departamento-en-venta-en-25-de-mayo-900</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19363/ficha/casa-en-venta-en-zeballos-500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 100,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>51.6</v>
+        <v>82.2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,47 +627,47 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>OFRECE EN VENTA</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA EN 25 DE MAYO, MENDOZA CAPITAL</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18739/ficha/casa-en-venta-en-montevideo-700</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19405/ficha/departamento-en-venta-en-25-de-mayo-900</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 100,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48.3</v>
+        <v>60.5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>130000</v>
+        <v>140000</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="F4" t="n">
-        <v>1733.3</v>
+        <v>717.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Casa en venta en esquina – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19775/ficha/casa-en-venta-en-juan-b-justo-1200</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,11 +722,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45.7</v>
+        <v>55.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,17 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>79000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>110</v>
+      </c>
+      <c r="F5" t="n">
+        <v>718.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -754,7 +750,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -779,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -800,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45.3</v>
+        <v>50.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79000</v>
+        <v>95000</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>718.2</v>
+        <v>871.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -828,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -853,28 +849,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>44.6</v>
+        <v>48.4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -887,22 +883,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90000</v>
+        <v>55000</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>1384.6</v>
+        <v>763.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -927,28 +923,28 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40.3</v>
+        <v>48.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -961,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95000</v>
+        <v>130000</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>871.6</v>
+        <v>1733.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1001,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>38.4</v>
+        <v>47.3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1035,17 +1031,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
-        <v>763.9</v>
+        <v>656.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1075,47 +1071,47 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37.3</v>
+        <v>47.1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="F10" t="n">
-        <v>656.9</v>
+        <v>575.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1124,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1149,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>35.7</v>
+        <v>45.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1183,13 +1179,17 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>88</v>
-      </c>
-      <c r="F11" t="n">
-        <v>625</v>
+        <v>140000</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>35.3</v>
+        <v>45.7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>1100</v>
+        <v>625</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1318,7 +1318,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>35.1</v>
+        <v>45.1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 70,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1392,7 +1392,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>34.6</v>
+        <v>44.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1466,11 +1466,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>34</v>
+        <v>44.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>120000</v>
+        <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>1333.3</v>
+        <v>1384.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1540,11 +1540,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>33.5</v>
+        <v>44</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>124900</v>
+        <v>120000</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>1435.6</v>
+        <v>1333.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1593,17 +1593,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 124,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1614,7 +1614,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>33.1</v>
+        <v>43.5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75000</v>
+        <v>124900</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
-        <v>1000</v>
+        <v>1435.6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1667,28 +1667,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32.7</v>
+        <v>43.1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>86000</v>
+        <v>75000</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>1228.6</v>
+        <v>1000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1741,17 +1741,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1762,11 +1762,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30.2</v>
+        <v>35.3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>140000</v>
+        <v>110000</v>
       </c>
       <c r="E19" t="n">
-        <v>575</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>243.5</v>
+        <v>1100</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1815,28 +1815,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>OPENHOUSE vende desarrollo en obra gruesa sobre calle Pascual Segura de Godoy Cruz</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2063/ficha/departamento-en-venta-en-pascual-segura-godoy-cruz</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58000</v>
+        <v>86000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>580</v>
+        <v>1228.6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1889,17 +1889,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1910,7 +1910,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20.9</v>
+        <v>31.6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80000</v>
+        <v>58000</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>888.9</v>
+        <v>580</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1963,17 +1963,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1984,7 +1984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20.3</v>
+        <v>30.3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2058,7 +2058,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2132,7 +2132,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>86000</v>
+        <v>150000</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F24" t="n">
-        <v>1211.3</v>
+        <v>1898.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2180,33 +2180,33 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63300</v>
+        <v>128000</v>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F25" t="n">
-        <v>867.1</v>
+        <v>1471.3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2259,17 +2259,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento En Gobernador Benegas</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>1898.7</v>
+        <v>888.9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2328,23 +2328,27 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -2363,13 +2367,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>128000</v>
+        <v>86000</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F27" t="n">
-        <v>1471.3</v>
+        <v>1211.3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2403,20 +2407,94 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 86,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>63300</v>
+      </c>
+      <c r="E28" t="n">
+        <v>73</v>
+      </c>
+      <c r="F28" t="n">
+        <v>867.1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Departamento En Gobernador Benegas</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 63,300)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96.7</v>
+        <v>62.1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E2" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F2" t="n">
-        <v>794.1</v>
+        <v>575.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>VENTA CASA 5 AMBIENTES ALTO DORREGO MENDOZA</t>
+          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19363/ficha/casa-en-venta-en-zeballos-500</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82.2</v>
+        <v>55.3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>100000</v>
+        <v>79000</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>1000</v>
+        <v>718.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,28 +627,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA EN 25 DE MAYO, MENDOZA CAPITAL</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19405/ficha/departamento-en-venta-en-25-de-mayo-900</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 100,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60.5</v>
+        <v>50.3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>140000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>717.9</v>
+        <v>871.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,32 +701,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Casa en venta en esquina – Dorrego, Guaymallén</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19775/ficha/casa-en-venta-en-juan-b-justo-1200</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55.3</v>
+        <v>48.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79000</v>
+        <v>130000</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>718.2</v>
+        <v>1733.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50.3</v>
+        <v>47.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95000</v>
+        <v>90000</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>871.6</v>
+        <v>656.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>48.4</v>
+        <v>45.7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -886,14 +886,14 @@
         <v>55000</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>763.9</v>
+        <v>625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -923,28 +923,28 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48.3</v>
+        <v>43.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>130000</v>
+        <v>124900</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>1733.3</v>
+        <v>1435.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47.3</v>
+        <v>43.1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>656.9</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,47 +1071,47 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.1</v>
+        <v>35.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>110000</v>
       </c>
       <c r="E10" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>575.9</v>
+        <v>1100</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,28 +1145,28 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45.7</v>
+        <v>32.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,17 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>86000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1228.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1223,32 +1219,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.7</v>
+        <v>31.6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1257,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55000</v>
+        <v>58000</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>625</v>
+        <v>580</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1297,32 +1293,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.1</v>
+        <v>30.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1331,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70000</v>
+        <v>99000</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>875</v>
+        <v>1064.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1371,32 +1367,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44.6</v>
+        <v>30</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53000</v>
+        <v>150000</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>757.1</v>
+        <v>2027</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1420,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1440,37 +1436,37 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44.6</v>
+        <v>30</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
-        <v>1384.6</v>
+        <v>1898.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1514,37 +1510,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>120000</v>
+        <v>128000</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>1333.3</v>
+        <v>1471.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1593,28 +1589,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Departamento Premium De 2 Dormitorios 2 Baños Y Amenitis. En Dorrego Guaymallen</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2052069609-departamento-premium-de-2-dormitorios-2-banos-y-amenitis-en-dorrego-guaymallen-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>43.5</v>
+        <v>20.9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1627,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>124900</v>
+        <v>80000</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>1435.6</v>
+        <v>888.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1667,28 +1663,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>43.1</v>
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75000</v>
+        <v>86000</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
-        <v>1000</v>
+        <v>1211.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1716,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1741,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 86,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1762,11 +1758,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35.3</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1775,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>110000</v>
+        <v>63300</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
-        <v>1100</v>
+        <v>867.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1815,686 +1811,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>86000</v>
-      </c>
-      <c r="E20" t="n">
-        <v>70</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1228.6</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>58000</v>
-      </c>
-      <c r="E21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" t="n">
-        <v>580</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Duplex En Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>99000</v>
-      </c>
-      <c r="E22" t="n">
-        <v>93</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1064.5</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>30</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E23" t="n">
-        <v>74</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>30</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E24" t="n">
-        <v>79</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1898.7</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>30</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>128000</v>
-      </c>
-      <c r="E25" t="n">
-        <v>87</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1471.3</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Venta Duplex En Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>90</v>
-      </c>
-      <c r="F26" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>86000</v>
-      </c>
-      <c r="E27" t="n">
-        <v>71</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1211.3</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 86,000)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E28" t="n">
-        <v>73</v>
-      </c>
-      <c r="F28" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62.1</v>
+        <v>55.3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,17 +509,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>110000</v>
+        <v>79000</v>
       </c>
       <c r="E2" t="n">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>575.9</v>
+        <v>718.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55.3</v>
+        <v>50.3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79000</v>
+        <v>95000</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
-        <v>718.2</v>
+        <v>871.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,28 +627,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>130000</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>871.6</v>
+        <v>1733.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,22 +701,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -796,26 +796,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90000</v>
+        <v>98000</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="F6" t="n">
-        <v>656.9</v>
+        <v>604.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>GYG Gestiones Inmobiliarias ofrece a la VENTA una amplia y funcional propiedad ubicada sobre calle Juan de Guevara, en Luzuriaga, Maipú – Mendoza.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/311068-gyg-gestiones-inmobiliarias/inmuebles/1/ficha/casa-en-venta-en-juan-de-guevara-3326</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45.7</v>
+        <v>47.3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
-        <v>625</v>
+        <v>656.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,11 +944,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43.5</v>
+        <v>45.7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>124900</v>
+        <v>55000</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>1435.6</v>
+        <v>625</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,11 +1018,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43.1</v>
+        <v>45.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75000</v>
+        <v>65000</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>1000</v>
+        <v>764.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>RICCARDI PROPIEDADES VENDE espectacular departamento en Barrio Bombal Sur, Godoy Cruz, sobre calle Beltrán entre Tucumán y Juan B. Justo.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/537/ficha/departamento-en-venta-en-beltran-1632-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>35.3</v>
+        <v>43.5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>110000</v>
+        <v>124900</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>1100</v>
+        <v>1435.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>32.7</v>
+        <v>43.1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86000</v>
+        <v>75000</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>1228.6</v>
+        <v>1000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,11 +1240,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>31.6</v>
+        <v>35.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58000</v>
+        <v>110000</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>580</v>
+        <v>1100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>99000</v>
+        <v>86000</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>1064.5</v>
+        <v>1228.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>30</v>
+        <v>31.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>150000</v>
+        <v>58000</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>2027</v>
+        <v>580</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1436,33 +1436,33 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>150000</v>
+        <v>99000</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>1898.7</v>
+        <v>1064.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1510,27 +1510,27 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>128000</v>
+        <v>150000</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>1471.3</v>
+        <v>2027</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1584,33 +1584,33 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20.9</v>
+        <v>30</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F17" t="n">
-        <v>888.9</v>
+        <v>1898.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1658,33 +1658,33 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>86000</v>
+        <v>128000</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F18" t="n">
-        <v>1211.3</v>
+        <v>1471.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz. Complejo Privado. Dto 11</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1746780419-venta-departamento-godoy-cruz-complejo-privado-dto-11-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,73 +1758,221 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>930.2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D21" t="n">
         <v>63300</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E21" t="n">
         <v>73</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>867.1</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>No/Duda</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,26 +796,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47.8</v>
+        <v>47.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98000</v>
+        <v>90000</v>
       </c>
       <c r="E6" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>604.9</v>
+        <v>656.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>GYG Gestiones Inmobiliarias ofrece a la VENTA una amplia y funcional propiedad ubicada sobre calle Juan de Guevara, en Luzuriaga, Maipú – Mendoza.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311068-gyg-gestiones-inmobiliarias/inmuebles/1/ficha/casa-en-venta-en-juan-de-guevara-3326</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>47.3</v>
+        <v>45.7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90000</v>
+        <v>55000</v>
       </c>
       <c r="E7" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>656.9</v>
+        <v>625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,11 +944,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>625</v>
+        <v>764.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>RICCARDI PROPIEDADES VENDE espectacular departamento en Barrio Bombal Sur, Godoy Cruz, sobre calle Beltrán entre Tucumán y Juan B. Justo.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/537/ficha/departamento-en-venta-en-beltran-1632-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45.5</v>
+        <v>43.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65000</v>
+        <v>124900</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>764.7</v>
+        <v>1435.6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE espectacular departamento en Barrio Bombal Sur, Godoy Cruz, sobre calle Beltrán entre Tucumán y Juan B. Justo.</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/537/ficha/departamento-en-venta-en-beltran-1632-godoy-cruz-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,11 +1092,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>124900</v>
+        <v>75000</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>1435.6</v>
+        <v>1000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>43.1</v>
+        <v>35.3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>35.3</v>
+        <v>32.7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>110000</v>
+        <v>86000</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>1100</v>
+        <v>1228.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>32.7</v>
+        <v>31.6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>86000</v>
+        <v>58000</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>1228.6</v>
+        <v>580</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58000</v>
+        <v>99000</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>580</v>
+        <v>1064.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>99000</v>
+        <v>150000</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>1064.5</v>
+        <v>2027</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1510,27 +1510,27 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -1552,10 +1552,10 @@
         <v>150000</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F16" t="n">
-        <v>2027</v>
+        <v>1898.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>150000</v>
+        <v>128000</v>
       </c>
       <c r="E17" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
-        <v>1898.7</v>
+        <v>1471.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1658,33 +1658,33 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30</v>
+        <v>20.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>128000</v>
+        <v>80000</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
-        <v>1471.3</v>
+        <v>888.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>80000</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>888.9</v>
+        <v>930.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80000</v>
+        <v>63300</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>930.2</v>
+        <v>867.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1885,94 +1885,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E21" t="n">
-        <v>73</v>
-      </c>
-      <c r="F21" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55.3</v>
+        <v>82.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79000</v>
+        <v>100000</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>718.2</v>
+        <v>1000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA EN 25 DE MAYO, MENDOZA CAPITAL</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19405/ficha/departamento-en-venta-en-25-de-mayo-900</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 100,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>50.3</v>
+        <v>61.1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>95000</v>
+        <v>129000</v>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="F3" t="n">
-        <v>871.6</v>
+        <v>934.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,32 +627,32 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48.3</v>
+        <v>55.3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>130000</v>
+        <v>79000</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>1733.3</v>
+        <v>718.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,11 +722,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>130000</v>
+        <v>95000</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F5" t="n">
-        <v>1733.3</v>
+        <v>871.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,28 +775,28 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47.3</v>
+        <v>48.4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90000</v>
+        <v>55000</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>656.9</v>
+        <v>763.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45.7</v>
+        <v>48.3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55000</v>
+        <v>130000</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>625</v>
+        <v>1733.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45.5</v>
+        <v>48.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65000</v>
+        <v>130000</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>764.7</v>
+        <v>1733.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE espectacular departamento en Barrio Bombal Sur, Godoy Cruz, sobre calle Beltrán entre Tucumán y Juan B. Justo.</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/537/ficha/departamento-en-venta-en-beltran-1632-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,11 +1018,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43.5</v>
+        <v>47.3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>124900</v>
+        <v>90000</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
-        <v>1435.6</v>
+        <v>656.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,26 +1092,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>43.1</v>
+        <v>47.1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="F10" t="n">
-        <v>1000</v>
+        <v>575.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>35.3</v>
+        <v>46.3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110000</v>
+        <v>79000</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>1100</v>
+        <v>831.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>OPENHOUSE VENDE – DOS UNIDADES EN UNA, FRENTE A PLAZA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2511/ficha/departamento-en-venta-en-patricias-mendocinas-ciudad</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,11 +1240,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>32.7</v>
+        <v>45.7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1253,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>86000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>70</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1228.6</v>
+        <v>140000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,32 +1297,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31.6</v>
+        <v>45.7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1331,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58000</v>
+        <v>55000</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,32 +1371,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>30.3</v>
+        <v>45.1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>99000</v>
+        <v>70000</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>1064.5</v>
+        <v>875</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,32 +1445,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>44.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>150000</v>
+        <v>53000</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>2027</v>
+        <v>757.1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1510,37 +1514,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>30</v>
+        <v>44.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>1898.7</v>
+        <v>1384.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1568,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1584,33 +1588,33 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30</v>
+        <v>43.5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>128000</v>
+        <v>124900</v>
       </c>
       <c r="E17" t="n">
         <v>87</v>
       </c>
       <c r="F17" t="n">
-        <v>1471.3</v>
+        <v>1435.6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1663,28 +1667,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20.9</v>
+        <v>43.1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80000</v>
+        <v>75000</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>888.9</v>
+        <v>1000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1741,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,11 +1762,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20.6</v>
+        <v>35.3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1775,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>930.2</v>
+        <v>1100</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,94 +1815,612 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" t="n">
+        <v>580</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>93</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>74</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>30</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>79</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1898.7</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>128000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>87</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1471.3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Venta Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>930.2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>20</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D27" t="n">
         <v>63300</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E27" t="n">
         <v>73</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F27" t="n">
         <v>867.1</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>No/Duda</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.2</v>
+        <v>61.1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,17 +509,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100000</v>
+        <v>129000</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="F2" t="n">
-        <v>1000</v>
+        <v>934.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,47 +553,47 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA EN 25 DE MAYO, MENDOZA CAPITAL</t>
+          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19405/ficha/departamento-en-venta-en-25-de-mayo-900</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 100,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61.1</v>
+        <v>55.3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>129000</v>
+        <v>79000</v>
       </c>
       <c r="E3" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>934.8</v>
+        <v>718.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
+          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55.3</v>
+        <v>50.3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>718.2</v>
+        <v>871.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -701,32 +701,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50.3</v>
+        <v>48.4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,22 +735,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95000</v>
+        <v>55000</v>
       </c>
       <c r="E5" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>871.6</v>
+        <v>763.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -775,32 +775,32 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,22 +809,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55000</v>
+        <v>130000</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>763.9</v>
+        <v>1733.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -944,11 +944,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48.3</v>
+        <v>47.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>130000</v>
+        <v>90000</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="F8" t="n">
-        <v>1733.3</v>
+        <v>656.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,26 +1018,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="F9" t="n">
-        <v>656.9</v>
+        <v>575.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,47 +1071,47 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>110000</v>
+        <v>92000</v>
       </c>
       <c r="E10" t="n">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="F10" t="n">
-        <v>575.9</v>
+        <v>876.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,22 +1145,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
+          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2511/ficha/departamento-en-venta-en-patricias-mendocinas-ciudad</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2563/ficha/departamento-en-venta-en-patricias-mendocinas-ciudad</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,17 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>55000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>625</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1272,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1297,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1318,11 +1314,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1331,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55000</v>
+        <v>70000</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1371,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1392,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70000</v>
+        <v>53000</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>875</v>
+        <v>757.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1445,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1466,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44.6</v>
+        <v>43.5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53000</v>
+        <v>124900</v>
       </c>
       <c r="E15" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="F15" t="n">
-        <v>757.1</v>
+        <v>1435.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1519,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1540,11 +1536,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44.6</v>
+        <v>43.1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>1384.6</v>
+        <v>1000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1593,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>43.5</v>
+        <v>35.3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1627,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>124900</v>
+        <v>110000</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>1435.6</v>
+        <v>1100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1667,17 +1663,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1688,11 +1684,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>43.1</v>
+        <v>32.7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75000</v>
+        <v>86000</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>1000</v>
+        <v>1228.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1741,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1762,11 +1758,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35.3</v>
+        <v>31.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1775,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>110000</v>
+        <v>58000</v>
       </c>
       <c r="E19" t="n">
         <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>1100</v>
+        <v>580</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1815,28 +1811,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1849,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58000</v>
+        <v>99000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F20" t="n">
-        <v>580</v>
+        <v>1064.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1889,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1910,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1923,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>99000</v>
+        <v>150000</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="F21" t="n">
-        <v>1064.5</v>
+        <v>678.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1958,27 +1954,27 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Departamento en Venta en Godoy Cruz Ideal por la amplitud y condición, sin detalles. Apto Crédito.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2152/ficha/departamento-en-venta-en-avenida-san-martin-1600</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,26 +574,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55.3</v>
+        <v>60.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79000</v>
+        <v>140000</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="F3" t="n">
-        <v>718.2</v>
+        <v>544.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bombal Sur. Piso completo - Beltran 1.910 esquina 25 de Mayo. Excelente ubicacion geografica. Cerca Estacion Metrotanvia. Limite con Barrio Bombal de Ciudad. 2° Piso. Muy luminoso . Living comedor amplio. Cocina comedor mediana. 3 dormitorios con placares. 2 baños. Ascensor .Apto Credito . Desocupado. Javier / Armando</t>
+          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/16797-provivienda-inmobiliaria/inmuebles/811/ficha/departamento-en-venta-en-beltran-1-910</t>
+          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,11 +648,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50.3</v>
+        <v>48.4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -661,22 +661,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>55000</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>871.6</v>
+        <v>763.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -701,32 +701,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,22 +735,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55000</v>
+        <v>130000</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>763.9</v>
+        <v>1733.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -775,22 +775,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -870,11 +870,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>48.3</v>
+        <v>47.3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>130000</v>
+        <v>90000</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
-        <v>1733.3</v>
+        <v>656.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,26 +944,26 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="F8" t="n">
-        <v>656.9</v>
+        <v>575.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,47 +997,47 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>110000</v>
+        <v>92000</v>
       </c>
       <c r="E9" t="n">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>575.9</v>
+        <v>876.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
+          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46.6</v>
+        <v>45.7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92000</v>
+        <v>55000</v>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>876.2</v>
+        <v>625</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>46.3</v>
+        <v>45.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79000</v>
+        <v>65000</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>831.6</v>
+        <v>764.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE – DOS UNIDADES EN UNA, FRENTE A PLAZA INDEPENDENCIA</t>
+          <t>RICCARDI PROPIEDADES VENDE espectacular departamento en Barrio Bombal Sur, Godoy Cruz, sobre calle Beltrán entre Tucumán y Juan B. Justo.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2563/ficha/departamento-en-venta-en-patricias-mendocinas-ciudad</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/537/ficha/departamento-en-venta-en-beltran-1632-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,26 +1240,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55000</v>
+        <v>140000</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="F12" t="n">
-        <v>625</v>
+        <v>717.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Casa en venta en esquina – Dorrego, Guaymallén</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19775/ficha/casa-en-venta-en-juan-b-justo-1200</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1536,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>43.1</v>
+        <v>35.3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>35.3</v>
+        <v>32.7</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>110000</v>
+        <v>86000</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>1100</v>
+        <v>1228.6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,32 +1663,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32.7</v>
+        <v>31.6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>86000</v>
+        <v>58000</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>1228.6</v>
+        <v>580</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58000</v>
+        <v>99000</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>1064.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>99000</v>
+        <v>150000</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>1064.5</v>
+        <v>2027</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1880,27 +1880,27 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -1922,10 +1922,10 @@
         <v>150000</v>
       </c>
       <c r="E21" t="n">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="F21" t="n">
-        <v>678.7</v>
+        <v>1898.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1954,22 +1954,22 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Departamento en Venta en Godoy Cruz Ideal por la amplitud y condición, sin detalles. Apto Crédito.</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2152/ficha/departamento-en-venta-en-avenida-san-martin-1600</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>150000</v>
+        <v>128000</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>2027</v>
+        <v>1471.3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2028,33 +2028,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>20.9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>1898.7</v>
+        <v>888.9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30</v>
+        <v>20.6</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>128000</v>
+        <v>80000</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>1471.3</v>
+        <v>930.2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20.9</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>80000</v>
+        <v>63300</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>888.9</v>
+        <v>867.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,168 +2255,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>86</v>
-      </c>
-      <c r="F26" t="n">
-        <v>930.2</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E27" t="n">
-        <v>73</v>
-      </c>
-      <c r="F27" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61.1</v>
+        <v>71</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,21 +509,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>129000</v>
+        <v>120000</v>
       </c>
       <c r="E2" t="n">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>934.8</v>
+        <v>1237.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
+          <t>TRE INMOBILIARIA  VENDE Excelente departamento en 5ta Sección. Ubicado en una zona con rápida conectividad , este departamento combina amplitud, luminosidad y una ubicacióni privilegiada. Emplazado a pasos de la Casa de Gobierno, la ciclovía y con acceso inmediato a comercios, gastronomía y todos los medios de transporte.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/880/ficha/departamento-en-venta-en-coronel-rodriguez-320-casi-vicente-gil-quinta-seccion</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60.5</v>
+        <v>71</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="E3" t="n">
-        <v>257</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>544.7</v>
+        <v>1515.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -622,33 +622,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
+          <t>RE/MAX Ofrece a la Venta departamento a metros de calle Emilio Civit, la calle más linda de Mendoza y a 5 minutos caminando del Parque General San Martín. Pensado para vivir cómodo todo el año, en un edificio con Amenities completos y seguridad las 24 horas.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19860/ficha/departamento-en-venta-en-coronel-rodriguez-1000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48.4</v>
+        <v>63.5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,26 +657,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>763.9</v>
+        <v>271.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -696,52 +696,52 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
+          <t>Casa en venta , Cuarta Sección , Ciudad de Mendoza , en obra .</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19076/ficha/casa-en-venta-en-villagra-francisco-3200</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 38,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48.3</v>
+        <v>61.1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>130000</v>
+        <v>129000</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="F5" t="n">
-        <v>1733.3</v>
+        <v>934.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>48.3</v>
+        <v>60.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>130000</v>
+        <v>76000</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>1733.3</v>
+        <v>1013.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>47.3</v>
+        <v>60.5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90000</v>
+        <v>140000</v>
       </c>
       <c r="E7" t="n">
-        <v>137</v>
+        <v>257</v>
       </c>
       <c r="F7" t="n">
-        <v>656.9</v>
+        <v>544.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,26 +944,26 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47.1</v>
+        <v>58.4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
+        <v>144400</v>
       </c>
       <c r="E8" t="n">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>575.9</v>
+        <v>1110.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -992,33 +992,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Venta casa 3 dormitorios con jardín y cochera – Dorrego, Guaymallén</t>
+          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20180/ficha/casa-en-venta-en-juan-jose-paso-1400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>46.6</v>
+        <v>55</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92000</v>
+        <v>110000</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>876.2</v>
+        <v>1236</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
+          <t>Descubra este encantador departamento ubicado en el corazón de la Cuarta Sección, en Capital, Mendoza. Situado en Paraguay 2855 Piso 1 Departamento 3, esta propiedad es ideal tanto para quienes buscan un hogar permanente como para aquellos interesados en una inversión con alto potencial de alquiler. Con escritura inmediata y posibilidad de permuta, las opciones son amplias.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
+          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/262/ficha/departamento-en-venta-en-paraguay-al-2800</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,11 +1092,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45.7</v>
+        <v>48.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55000</v>
+        <v>94000</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>625</v>
+        <v>862.4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>Dentro del presupuesto (USD 94,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45.5</v>
+        <v>47.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="F11" t="n">
-        <v>764.7</v>
+        <v>675.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE espectacular departamento en Barrio Bombal Sur, Godoy Cruz, sobre calle Beltrán entre Tucumán y Juan B. Justo.</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/537/ficha/departamento-en-venta-en-beltran-1632-godoy-cruz-mendoza</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,26 +1240,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.5</v>
+        <v>47.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>140000</v>
+        <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>717.9</v>
+        <v>656.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Casa en venta en esquina – Dorrego, Guaymallén</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19775/ficha/casa-en-venta-en-juan-b-justo-1200</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.1</v>
+        <v>46.5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,17 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E13" t="n">
-        <v>80</v>
-      </c>
-      <c r="F13" t="n">
-        <v>875</v>
+        <v>125000</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1371,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
+          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,11 +1392,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44.6</v>
+        <v>45.7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53000</v>
+        <v>55000</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>757.1</v>
+        <v>625</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,17 +1445,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,11 +1466,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>43.5</v>
+        <v>44.7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>124900</v>
+        <v>115000</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>1435.6</v>
+        <v>1197.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1510,22 +1514,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>En la exclusiva 5ta sección, se ofrece en venta este departamento ubicado sobre Paso de los Andes, entre Manuel a Saez y Sargento Cabral.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/52/ficha/departamento-en-venta-en-paso-de-los-andes-570</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,11 +1540,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>35.3</v>
+        <v>43</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>110000</v>
+        <v>89000</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F16" t="n">
-        <v>1100</v>
+        <v>754.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1568,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,28 +1593,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32.7</v>
+        <v>42.1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>86000</v>
+        <v>87500</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>1228.6</v>
+        <v>875</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1663,17 +1667,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Oportunidad! Venta Departamento Godoy Cruz - 2 dormitorios, con cochera subterránea y ascensor</t>
+          <t>CORDON &amp; ASOCIADOS VENDE</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1981/ficha/departamento-en-venta-en-belgrano-200</t>
+          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 86,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1684,7 +1688,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>31.6</v>
+        <v>42</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58000</v>
+        <v>77000</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>580</v>
+        <v>793.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1741,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,7 +1762,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30.3</v>
+        <v>39.2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1775,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>99000</v>
+        <v>110000</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="F19" t="n">
-        <v>1064.5</v>
+        <v>940.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,17 +1815,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1832,11 +1836,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>35.3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1845,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>150000</v>
+        <v>110000</v>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>2027</v>
+        <v>1100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1864,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1880,37 +1884,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>32.8</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1919,13 +1923,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>150000</v>
+        <v>55000</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>1898.7</v>
+        <v>723.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1954,37 +1958,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>COCUCCI INMOBILIARIA VENDE HERMOSO DEPARTAMENTO EN EL CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20110/ficha/departamento-en-venta-en-rioja-al-1500</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>31.8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1997,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>128000</v>
+        <v>150000</v>
       </c>
       <c r="E22" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>1471.3</v>
+        <v>1666.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2028,33 +2032,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20.9</v>
+        <v>31.6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80000</v>
+        <v>58000</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>888.9</v>
+        <v>580</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2107,17 +2111,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,7 +2132,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20.6</v>
+        <v>30.9</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2145,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80000</v>
+        <v>73000</v>
       </c>
       <c r="E24" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F24" t="n">
-        <v>930.2</v>
+        <v>811.1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2185,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
+          <t>Departamento En Venta</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1948710479-departamento-en-venta-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 73,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,73 +2206,961 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>93</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>30</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>74</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>30</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>79</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1898.7</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>128000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>87</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1471.3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Venta Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>65</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1384.6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>98000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>90</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1088.9</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 98,000) | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>82000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1093.3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ALTA PROPIEDADES VENDE DEPARTAMENTO EN CIUDAD</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/284193-alta-propiedades/inmuebles/19/ficha/departamento-en-venta-en-colon-352</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 82,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>75</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1866.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Departamento en Venta – Mendoza Capital</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>90</v>
+      </c>
+      <c r="F33" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>86</v>
+      </c>
+      <c r="F34" t="n">
+        <v>930.2</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>20</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>67</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1343.3</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>67</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>63300</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E37" t="n">
         <v>73</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F37" t="n">
         <v>867.1</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71</v>
+        <v>64.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150000</v>
+        <v>115000</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>1515.2</v>
+        <v>821.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -622,33 +622,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RE/MAX Ofrece a la Venta departamento a metros de calle Emilio Civit, la calle más linda de Mendoza y a 5 minutos caminando del Parque General San Martín. Pensado para vivir cómodo todo el año, en un edificio con Amenities completos y seguridad las 24 horas.</t>
+          <t>Departamento de categoría ubicado en calle Mitre, del centro Mendocino.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19860/ficha/departamento-en-venta-en-coronel-rodriguez-1000</t>
+          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/86/ficha/departamento-en-venta-en-mitre-1638</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38000</v>
+        <v>60000</v>
       </c>
       <c r="E4" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>271.4</v>
+        <v>666.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -696,22 +696,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Casa en venta , Cuarta Sección , Ciudad de Mendoza , en obra .</t>
+          <t>COCUCCI INMOBILIARIA VENDE: Amplio departamento ubicado en el 5° piso de la Torre B2, con acceso mediante ascensor, muy buena distribución y luminosidad en la  Ciudad de Mendoza. Importante: La propiedad no dispone de cochera, aunque en la zona existen opciones de alquiler mensual. BARBARA LUCERO CCPIM 1817 - TEL: .</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19076/ficha/casa-en-venta-en-villagra-francisco-3200</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19838/ficha/departamento-en-venta-en-san-juan-al-500</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 38,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 60,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60.5</v>
+        <v>58.4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>140000</v>
+        <v>144400</v>
       </c>
       <c r="E7" t="n">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>544.7</v>
+        <v>1110.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -918,33 +918,33 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
+          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58.4</v>
+        <v>55</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>144400</v>
+        <v>110000</v>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>1110.8</v>
+        <v>1236</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -992,33 +992,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
+          <t>Descubra este encantador departamento ubicado en el corazón de la Cuarta Sección, en Capital, Mendoza. Situado en Paraguay 2855 Piso 1 Departamento 3, esta propiedad es ideal tanto para quienes buscan un hogar permanente como para aquellos interesados en una inversión con alto potencial de alquiler. Con escritura inmediata y posibilidad de permuta, las opciones son amplias.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
+          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/262/ficha/departamento-en-venta-en-paraguay-al-2800</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55</v>
+        <v>48.1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>1236</v>
+        <v>733.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1066,22 +1066,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Descubra este encantador departamento ubicado en el corazón de la Cuarta Sección, en Capital, Mendoza. Situado en Paraguay 2855 Piso 1 Departamento 3, esta propiedad es ideal tanto para quienes buscan un hogar permanente como para aquellos interesados en una inversión con alto potencial de alquiler. Con escritura inmediata y posibilidad de permuta, las opciones son amplias.</t>
+          <t>Departamento en Planta Baja con 2 Patios • Sin Expensas • Capital, Mendoza.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/262/ficha/departamento-en-venta-en-paraguay-al-2800</t>
+          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/302/ficha/departamento-en-venta-en-rondeau-y-salta</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 55,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94000</v>
+        <v>75000</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>862.4</v>
+        <v>675.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,28 +1145,28 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 94,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
-        <v>675.7</v>
+        <v>656.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.3</v>
+        <v>46.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1253,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>137</v>
-      </c>
-      <c r="F12" t="n">
-        <v>656.9</v>
+        <v>125000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,17 +1297,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,11 +1318,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>46.5</v>
+        <v>45.7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,17 +1331,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>125000</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>55000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1392,11 +1392,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45.7</v>
+        <v>43.4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55000</v>
+        <v>81000</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>625</v>
+        <v>1051.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1440,22 +1440,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1466,7 +1466,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44.7</v>
+        <v>42.7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>115000</v>
+        <v>139000</v>
       </c>
       <c r="E15" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
-        <v>1197.9</v>
+        <v>1616.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1514,22 +1514,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>En la exclusiva 5ta sección, se ofrece en venta este departamento ubicado sobre Paso de los Andes, entre Manuel a Saez y Sargento Cabral.</t>
+          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/52/ficha/departamento-en-venta-en-paso-de-los-andes-570</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1540,11 +1540,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>43</v>
+        <v>37.3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>89000</v>
+        <v>67000</v>
       </c>
       <c r="E16" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>754.2</v>
+        <v>957.1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1593,32 +1593,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
+          <t>Amplio y luminoso departamento ubicado en una de la principales avenidas del Centro de la Ciudad de Mendoza, a una cuadra del Centro Cívico, cercana a Arístides Villanueva, Parque General San Martin, y a cuadras de Av. San Martin. A sus alrededores podemos encontrar una amplia y variada oferta gastronómica, comercial, cultural, bancaria y educativa.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
+          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/420/ficha/departamento-en-venta-en-av-colon-460</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 67,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>42.1</v>
+        <v>35.3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>87500</v>
+        <v>110000</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>875</v>
+        <v>1100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1667,32 +1667,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>CORDON &amp; ASOCIADOS VENDE</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>42</v>
+        <v>31.8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77000</v>
+        <v>150000</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
-        <v>793.8</v>
+        <v>1666.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1736,33 +1736,33 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
+          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
+          <t>🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39.2</v>
+        <v>31.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>110000</v>
+        <v>58000</v>
       </c>
       <c r="E19" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>940.2</v>
+        <v>580</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1815,17 +1815,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1836,11 +1836,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>110000</v>
+        <v>73000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>1100</v>
+        <v>811.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1889,32 +1889,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento En Venta</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1948710479-departamento-en-venta-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 73,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>32.8</v>
+        <v>30.3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55000</v>
+        <v>99000</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>723.7</v>
+        <v>1064.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE HERMOSO DEPARTAMENTO EN EL CENTRO DE MENDOZA</t>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20110/ficha/departamento-en-venta-en-rioja-al-1500</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>31.8</v>
+        <v>30</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2000,10 +2000,10 @@
         <v>150000</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
-        <v>1666.7</v>
+        <v>2027</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2037,28 +2037,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>31.6</v>
+        <v>30</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58000</v>
+        <v>150000</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F23" t="n">
-        <v>580</v>
+        <v>1898.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2106,33 +2106,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73000</v>
+        <v>128000</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>811.1</v>
+        <v>1471.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2185,17 +2185,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Venta</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1948710479-departamento-en-venta-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 73,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2206,11 +2206,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30.3</v>
+        <v>29.5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>99000</v>
+        <v>85000</v>
       </c>
       <c r="E25" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
-        <v>1064.5</v>
+        <v>1231.9</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30</v>
+        <v>20.9</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E26" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>2027</v>
+        <v>888.9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2328,33 +2328,33 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30</v>
+        <v>20.6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>1898.7</v>
+        <v>930.2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2402,33 +2402,33 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>128000</v>
+        <v>75000</v>
       </c>
       <c r="E28" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F28" t="n">
-        <v>1471.3</v>
+        <v>1119.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2481,17 +2481,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2502,7 +2502,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29.6</v>
+        <v>20</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2515,13 +2515,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>90000</v>
+        <v>63300</v>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F29" t="n">
-        <v>1384.6</v>
+        <v>867.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2555,612 +2555,20 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>98000</v>
-      </c>
-      <c r="E30" t="n">
-        <v>90</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1088.9</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 98,000) | 🛗 Edificio con ascensor</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>82000</v>
-      </c>
-      <c r="E31" t="n">
-        <v>75</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1093.3</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>ALTA PROPIEDADES VENDE DEPARTAMENTO EN CIUDAD</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/284193-alta-propiedades/inmuebles/19/ficha/departamento-en-venta-en-colon-352</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 82,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E32" t="n">
-        <v>75</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1866.7</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E33" t="n">
-        <v>90</v>
-      </c>
-      <c r="F33" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>86</v>
-      </c>
-      <c r="F34" t="n">
-        <v>930.2</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E35" t="n">
-        <v>67</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1343.3</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>20</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E36" t="n">
-        <v>67</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E37" t="n">
-        <v>73</v>
-      </c>
-      <c r="F37" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,17 +513,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120000</v>
+        <v>69000</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>1237.1</v>
+        <v>627.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,22 +553,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA  VENDE Excelente departamento en 5ta Sección. Ubicado en una zona con rápida conectividad , este departamento combina amplitud, luminosidad y una ubicacióni privilegiada. Emplazado a pasos de la Casa de Gobierno, la ciclovía y con acceso inmediato a comercios, gastronomía y todos los medios de transporte.</t>
+          <t>Amplio departamento en PH ubicado en el Complejo Cerecco Centro Residencial y Comercial compuesto por 4 Torres dispuestas en forma angular confluyendo en un espacio común central.A solo 20 mts de la Plaza Yrigoyen</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/880/ficha/departamento-en-venta-en-coronel-rodriguez-320-casi-vicente-gil-quinta-seccion</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/96/ficha/departamento-en-venta-en-ciudad</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55</v>
+        <v>51.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,17 +957,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
+        <v>125000</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>1236</v>
+        <v>1562.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -992,33 +992,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Descubra este encantador departamento ubicado en el corazón de la Cuarta Sección, en Capital, Mendoza. Situado en Paraguay 2855 Piso 1 Departamento 3, esta propiedad es ideal tanto para quienes buscan un hogar permanente como para aquellos interesados en una inversión con alto potencial de alquiler. Con escritura inmediata y posibilidad de permuta, las opciones son amplias.</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/262/ficha/departamento-en-venta-en-paraguay-al-2800</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55000</v>
+        <v>75000</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="F9" t="n">
-        <v>733.3</v>
+        <v>675.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Departamento en Planta Baja con 2 Patios • Sin Expensas • Capital, Mendoza.</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/302/ficha/departamento-en-venta-en-rondeau-y-salta</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
-        <v>675.7</v>
+        <v>656.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47.3</v>
+        <v>45.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90000</v>
+        <v>55000</v>
       </c>
       <c r="E11" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>656.9</v>
+        <v>625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>46.5</v>
+        <v>43.4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,17 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>81000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1051.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1272,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1292,22 +1288,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1318,11 +1314,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.7</v>
+        <v>42.7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1331,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55000</v>
+        <v>139000</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>625</v>
+        <v>1616.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1371,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1392,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43.4</v>
+        <v>37.3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81000</v>
+        <v>67000</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>1051.9</v>
+        <v>957.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1440,22 +1436,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>Amplio y luminoso departamento ubicado en una de la principales avenidas del Centro de la Ciudad de Mendoza, a una cuadra del Centro Cívico, cercana a Arístides Villanueva, Parque General San Martin, y a cuadras de Av. San Martin. A sus alrededores podemos encontrar una amplia y variada oferta gastronómica, comercial, cultural, bancaria y educativa.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/420/ficha/departamento-en-venta-en-av-colon-460</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 67,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1466,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>42.7</v>
+        <v>35.3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>139000</v>
+        <v>110000</v>
       </c>
       <c r="E15" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>1616.3</v>
+        <v>1100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1519,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1540,7 +1536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37.3</v>
+        <v>32.8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67000</v>
+        <v>55000</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>957.1</v>
+        <v>723.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1593,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Amplio y luminoso departamento ubicado en una de la principales avenidas del Centro de la Ciudad de Mendoza, a una cuadra del Centro Cívico, cercana a Arístides Villanueva, Parque General San Martin, y a cuadras de Av. San Martin. A sus alrededores podemos encontrar una amplia y variada oferta gastronómica, comercial, cultural, bancaria y educativa.</t>
+          <t>COCUCCI INMOBILIARIA VENDE HERMOSO DEPARTAMENTO EN EL CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/420/ficha/departamento-en-venta-en-av-colon-460</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20110/ficha/departamento-en-venta-en-rioja-al-1500</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 67,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1614,11 +1610,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>35.3</v>
+        <v>31.8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1627,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>1100</v>
+        <v>1666.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1662,37 +1658,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150000</v>
+        <v>58000</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>1666.7</v>
+        <v>580</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1736,33 +1732,33 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1775,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58000</v>
+        <v>73000</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>811.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1815,17 +1811,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento En Venta</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1948710479-departamento-en-venta-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 73,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1836,7 +1832,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1849,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>811.1</v>
+        <v>2027</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1864,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1884,33 +1880,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Departamento En Venta</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1948710479-departamento-en-venta-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 73,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1923,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>99000</v>
+        <v>150000</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F21" t="n">
-        <v>1064.5</v>
+        <v>1898.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1958,37 +1954,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1997,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
-        <v>2027</v>
+        <v>1231.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2032,33 +2028,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>20.9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2071,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>1898.7</v>
+        <v>888.9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2106,33 +2102,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2145,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>128000</v>
+        <v>75000</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>1471.3</v>
+        <v>1119.4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2185,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2206,11 +2202,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29.5</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2219,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>85000</v>
+        <v>63300</v>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>1231.9</v>
+        <v>867.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2234,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2259,316 +2255,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>90</v>
-      </c>
-      <c r="F26" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E27" t="n">
-        <v>86</v>
-      </c>
-      <c r="F27" t="n">
-        <v>930.2</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E28" t="n">
-        <v>67</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E29" t="n">
-        <v>73</v>
-      </c>
-      <c r="F29" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -805,17 +805,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>76000</v>
+        <v>130000</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="F6" t="n">
-        <v>1013.3</v>
+        <v>541.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
+          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58.4</v>
+        <v>51.5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,17 +883,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>144400</v>
+        <v>125000</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>1110.8</v>
+        <v>1562.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -918,33 +918,33 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51.5</v>
+        <v>47.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>125000</v>
+        <v>90000</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="F8" t="n">
-        <v>1562.5</v>
+        <v>656.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47.5</v>
+        <v>45.7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75000</v>
+        <v>120000</v>
       </c>
       <c r="E9" t="n">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
-        <v>675.7</v>
+        <v>863.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>COCUCCI INMOBILIARIA VENDE: EXCELENTE DEPARTAMENTO EN EL CORAZON DE MENDOZA,  PLENA CALLE BELGRANO, PARA QUIENES BUSCAN COMODIDAD Y ESPACIO AL AIRE LIBRE EN PLENO CENTRO, AMPLIO Y LUMINOSO.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19421/ficha/departamento-en-venta-en-belgrano-al-1200</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.3</v>
+        <v>43.4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>90000</v>
+        <v>81000</v>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>656.9</v>
+        <v>1051.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45.7</v>
+        <v>42.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55000</v>
+        <v>139000</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>625</v>
+        <v>1616.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,11 +1240,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>43.4</v>
+        <v>36.9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81000</v>
+        <v>43000</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
-        <v>1051.9</v>
+        <v>551.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1288,37 +1288,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>DEPARTAMENTO 3 HAB. EN VENTA – APTO CREDITO -CDAD MENDOZA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2811/ficha/departamento-en-venta-en-san-juan-200</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 43,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42.7</v>
+        <v>35.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>139000</v>
+        <v>110000</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>1616.3</v>
+        <v>1100</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,11 +1388,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37.3</v>
+        <v>33.4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,17 +1401,17 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67000</v>
+        <v>55000</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>957.1</v>
+        <v>763.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Amplio y luminoso departamento ubicado en una de la principales avenidas del Centro de la Ciudad de Mendoza, a una cuadra del Centro Cívico, cercana a Arístides Villanueva, Parque General San Martin, y a cuadras de Av. San Martin. A sus alrededores podemos encontrar una amplia y variada oferta gastronómica, comercial, cultural, bancaria y educativa.</t>
+          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/420/ficha/departamento-en-venta-en-av-colon-460</t>
+          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 67,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>35.3</v>
+        <v>32.8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>1100</v>
+        <v>723.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>COCUCCI INMOBILIARIA VENDE HERMOSO DEPARTAMENTO EN EL CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20110/ficha/departamento-en-venta-en-rioja-al-1500</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,11 +1536,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>32.8</v>
+        <v>31.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55000</v>
+        <v>58000</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>723.7</v>
+        <v>580</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE HERMOSO DEPARTAMENTO EN EL CENTRO DE MENDOZA</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20110/ficha/departamento-en-venta-en-rioja-al-1500</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31.8</v>
+        <v>30</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1626,10 +1626,10 @@
         <v>150000</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>1666.7</v>
+        <v>2027</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,28 +1663,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>31.6</v>
+        <v>30</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58000</v>
+        <v>150000</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>580</v>
+        <v>1898.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1732,37 +1732,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30.9</v>
+        <v>29.5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73000</v>
+        <v>85000</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>811.1</v>
+        <v>1231.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento En Venta</t>
+          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1948710479-departamento-en-venta-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 73,000)</t>
+          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>20.9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>2027</v>
+        <v>888.9</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1880,33 +1880,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>1898.7</v>
+        <v>1119.4</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1954,37 +1954,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>29.5</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85000</v>
+        <v>63300</v>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
-        <v>1231.9</v>
+        <v>867.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2033,242 +2033,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E23" t="n">
-        <v>90</v>
-      </c>
-      <c r="F23" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E24" t="n">
-        <v>67</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E25" t="n">
-        <v>73</v>
-      </c>
-      <c r="F25" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69000</v>
+        <v>63000</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F2" t="n">
-        <v>627.3</v>
+        <v>463.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Amplio departamento en PH ubicado en el Complejo Cerecco Centro Residencial y Comercial compuesto por 4 Torres dispuestas en forma angular confluyendo en un espacio común central.A solo 20 mts de la Plaza Yrigoyen</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/96/ficha/departamento-en-venta-en-ciudad</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115000</v>
+        <v>85000</v>
       </c>
       <c r="E3" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>821.4</v>
+        <v>658.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -622,22 +622,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Departamento de categoría ubicado en calle Mitre, del centro Mendocino.</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/86/ficha/departamento-en-venta-en-mitre-1638</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>294</v>
       </c>
       <c r="F4" t="n">
-        <v>666.7</v>
+        <v>323.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE: Amplio departamento ubicado en el 5° piso de la Torre B2, con acceso mediante ascensor, muy buena distribución y luminosidad en la  Ciudad de Mendoza. Importante: La propiedad no dispone de cochera, aunque en la zona existen opciones de alquiler mensual. BARBARA LUCERO CCPIM 1817 - TEL: .</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19838/ficha/departamento-en-venta-en-san-juan-al-500</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 60,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>129000</v>
+        <v>88000</v>
       </c>
       <c r="E5" t="n">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>934.8</v>
+        <v>888.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61.1</v>
+        <v>56.1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,17 +809,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>130000</v>
+        <v>90000</v>
       </c>
       <c r="E6" t="n">
-        <v>240</v>
+        <v>152</v>
       </c>
       <c r="F6" t="n">
-        <v>541.7</v>
+        <v>592.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
+          <t>CASA EN VENTA 3 AMBIENTES MENDOZA MAURE AVELINO - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2064/ficha/casa-en-venta-en-maure-avelino-100</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47.3</v>
+        <v>50.8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90000</v>
+        <v>68000</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>656.9</v>
+        <v>906.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45.7</v>
+        <v>49.9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="E9" t="n">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>863.3</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE: EXCELENTE DEPARTAMENTO EN EL CORAZON DE MENDOZA,  PLENA CALLE BELGRANO, PARA QUIENES BUSCAN COMODIDAD Y ESPACIO AL AIRE LIBRE EN PLENO CENTRO, AMPLIO Y LUMINOSO.</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19421/ficha/departamento-en-venta-en-belgrano-al-1200</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,26 +1092,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>43.4</v>
+        <v>48</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81000</v>
+        <v>94900</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="F10" t="n">
-        <v>1051.9</v>
+        <v>379.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1140,52 +1140,52 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>42.7</v>
+        <v>47.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>139000</v>
+        <v>100000</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="F11" t="n">
-        <v>1616.3</v>
+        <v>534.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1214,37 +1214,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
+          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36.9</v>
+        <v>47.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43000</v>
+        <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>551.3</v>
+        <v>656.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,47 +1293,47 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 HAB. EN VENTA – APTO CREDITO -CDAD MENDOZA</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2811/ficha/departamento-en-venta-en-san-juan-200</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 43,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>35.3</v>
+        <v>47.2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>110000</v>
+        <v>90000</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,28 +1367,28 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>33.4</v>
+        <v>46.9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1397,26 +1397,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55000</v>
+        <v>115000</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="F14" t="n">
-        <v>763.9</v>
+        <v>642.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,47 +1441,47 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE 4 AMBIENTES - CENTRICO</t>
+          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/68264-gaustralinmobiliariaatgmail-com/inmuebles/4/ficha/departamento-en-venta-en-rondeau</t>
+          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000) | 🔥 Red de gas natural confirmada</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>32.8</v>
+        <v>46.9</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55000</v>
+        <v>115000</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="F15" t="n">
-        <v>723.7</v>
+        <v>642.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,32 +1515,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE HERMOSO DEPARTAMENTO EN EL CENTRO DE MENDOZA</t>
+          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20110/ficha/departamento-en-venta-en-rioja-al-1500</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31.6</v>
+        <v>46.8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58000</v>
+        <v>105000</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
-        <v>580</v>
+        <v>954.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,28 +1589,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30</v>
+        <v>46.6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1619,17 +1619,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>220</v>
       </c>
       <c r="F17" t="n">
-        <v>2027</v>
+        <v>545.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1658,37 +1658,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30</v>
+        <v>46.5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F18" t="n">
-        <v>1898.7</v>
+        <v>873.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1732,37 +1732,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>29.5</v>
+        <v>45.7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>85000</v>
+        <v>55000</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>1231.9</v>
+        <v>625</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20.9</v>
+        <v>45.6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80000</v>
+        <v>138000</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="F20" t="n">
-        <v>888.9</v>
+        <v>862.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>45.6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>75000</v>
+        <v>139000</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="F21" t="n">
-        <v>1119.4</v>
+        <v>958.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,73 +1980,1183 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>152</v>
+      </c>
+      <c r="F22" t="n">
+        <v>921.1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>77500</v>
+      </c>
+      <c r="E23" t="n">
+        <v>66</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1174.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>96</v>
+      </c>
+      <c r="F24" t="n">
+        <v>708.3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>74</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1756.8</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>146000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>204</v>
+      </c>
+      <c r="F26" t="n">
+        <v>715.7</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>VENDIMIA VENDE!!!</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2321/ficha/casa-en-venta-en-25-de-mayo-1900</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 146,000 (Requiere contraoferta del 4.3%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>78900</v>
+      </c>
+      <c r="E27" t="n">
+        <v>203</v>
+      </c>
+      <c r="F27" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>VENDIMIA VENDE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2303/ficha/casa-en-venta-en-julian-barraquero-300</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 78,900)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>188</v>
+      </c>
+      <c r="F28" t="n">
+        <v>585.1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>135000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>290</v>
+      </c>
+      <c r="F29" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Departamento En Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 110,000)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
+      <c r="F31" t="n">
+        <v>580</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>88</v>
+      </c>
+      <c r="F32" t="n">
+        <v>625</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>74</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>79</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1898.7</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>90</v>
+      </c>
+      <c r="F35" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D36" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>67</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>63300</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E37" t="n">
         <v>73</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F37" t="n">
         <v>867.1</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66.2</v>
+        <v>71</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,17 +513,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63000</v>
+        <v>120000</v>
       </c>
       <c r="E2" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>463.2</v>
+        <v>1237.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>TRE INMOBILIARIA  VENDE Excelente departamento en 5ta Sección. Ubicado en una zona con rápida conectividad , este departamento combina amplitud, luminosidad y una ubicacióni privilegiada. Emplazado a pasos de la Casa de Gobierno, la ciclovía y con acceso inmediato a comercios, gastronomía y todos los medios de transporte.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/880/ficha/departamento-en-venta-en-coronel-rodriguez-320-casi-vicente-gil-quinta-seccion</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.5</v>
+        <v>71</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85000</v>
+        <v>150000</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>658.9</v>
+        <v>1515.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -622,33 +622,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>RE/MAX Ofrece a la Venta departamento a metros de calle Emilio Civit, la calle más linda de Mendoza y a 5 minutos caminando del Parque General San Martín. Pensado para vivir cómodo todo el año, en un edificio con Amenities completos y seguridad las 24 horas.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19860/ficha/departamento-en-venta-en-coronel-rodriguez-1000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>85000</v>
       </c>
       <c r="E4" t="n">
-        <v>294</v>
+        <v>129</v>
       </c>
       <c r="F4" t="n">
-        <v>323.1</v>
+        <v>658.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>88000</v>
+        <v>95000</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>294</v>
       </c>
       <c r="F5" t="n">
-        <v>888.9</v>
+        <v>323.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56.1</v>
+        <v>62.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,17 +809,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90000</v>
+        <v>98000</v>
       </c>
       <c r="E6" t="n">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>592.1</v>
+        <v>490</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,28 +849,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 AMBIENTES MENDOZA MAURE AVELINO - APTO CRÉDITO</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2064/ficha/casa-en-venta-en-maure-avelino-100</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>51.5</v>
+        <v>62.2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -879,21 +879,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>125000</v>
+        <v>88000</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>1562.5</v>
+        <v>888.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -918,33 +918,33 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>50.8</v>
+        <v>62.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,21 +953,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68000</v>
+        <v>110000</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="F8" t="n">
-        <v>906.7</v>
+        <v>687.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49.9</v>
+        <v>60.8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70000</v>
+        <v>76000</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>1000</v>
+        <v>1013.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,26 +1092,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48</v>
+        <v>58.4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94900</v>
+        <v>144400</v>
       </c>
       <c r="E10" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="F10" t="n">
-        <v>379.6</v>
+        <v>1110.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1140,52 +1140,52 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
+          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47.7</v>
+        <v>55</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="E11" t="n">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>534.8</v>
+        <v>1236</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,28 +1219,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
+          <t>Descubra este encantador departamento ubicado en el corazón de la Cuarta Sección, en Capital, Mendoza. Situado en Paraguay 2855 Piso 1 Departamento 3, esta propiedad es ideal tanto para quienes buscan un hogar permanente como para aquellos interesados en una inversión con alto potencial de alquiler. Con escritura inmediata y posibilidad de permuta, las opciones son amplias.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
+          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/262/ficha/departamento-en-venta-en-paraguay-al-2800</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.3</v>
+        <v>51.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90000</v>
+        <v>125000</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>656.9</v>
+        <v>1562.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1288,56 +1288,56 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47.2</v>
+        <v>48.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>90000</v>
+        <v>94000</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>900</v>
+        <v>862.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1367,28 +1367,28 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
+          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 94,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46.9</v>
+        <v>48</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>115000</v>
+        <v>94900</v>
       </c>
       <c r="E14" t="n">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="F14" t="n">
-        <v>642.5</v>
+        <v>379.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
+          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>46.9</v>
+        <v>47.7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>115000</v>
+        <v>100000</v>
       </c>
       <c r="E15" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F15" t="n">
-        <v>642.5</v>
+        <v>534.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1510,22 +1510,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
+          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>105000</v>
+        <v>75000</v>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F16" t="n">
-        <v>954.5</v>
+        <v>675.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,26 +1610,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>46.6</v>
+        <v>47.3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>120000</v>
+        <v>90000</v>
       </c>
       <c r="E17" t="n">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>545.5</v>
+        <v>656.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,47 +1663,47 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>46.5</v>
+        <v>47.2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>90000</v>
       </c>
       <c r="E18" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>873.8</v>
+        <v>900</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,47 +1737,47 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>SOPPELSA INMOBILIARIA VENDE amplio Departamento en ciudad. Calle Gutiérrez y Mitre. Semipiso de doble ingreso, Ubicado en 5to Piso. Posee Living comedor con Balcón. Cocina comedor amplia. Dependencia de servicio con Baño. 3 Dormitorios. Baño principal y Toilette.</t>
+          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12197-soppelsa-inmobiliaria/inmuebles/397/ficha/departamento-en-venta-en-gutierrez-466-5to-piso</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>45.7</v>
+        <v>46.9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55000</v>
+        <v>115000</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="F19" t="n">
-        <v>625</v>
+        <v>642.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45.6</v>
+        <v>46.9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>138000</v>
+        <v>115000</v>
       </c>
       <c r="E20" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F20" t="n">
-        <v>862.5</v>
+        <v>642.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
+          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>45.6</v>
+        <v>46.6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>139000</v>
+        <v>120000</v>
       </c>
       <c r="E21" t="n">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="F21" t="n">
-        <v>958.6</v>
+        <v>545.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1959,17 +1959,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
+          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,26 +1980,30 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E22" t="n">
-        <v>152</v>
-      </c>
-      <c r="F22" t="n">
-        <v>921.1</v>
+        <v>125000</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,32 +2037,32 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>44.9</v>
+        <v>45.7</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2067,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77500</v>
+        <v>55000</v>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
-        <v>1174.2</v>
+        <v>625</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2107,17 +2111,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,7 +2132,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>41.9</v>
+        <v>45.6</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2137,17 +2141,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68000</v>
+        <v>138000</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="F24" t="n">
-        <v>708.3</v>
+        <v>862.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2185,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,26 +2206,26 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39.8</v>
+        <v>45.6</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>130000</v>
+        <v>139000</v>
       </c>
       <c r="E25" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="F25" t="n">
-        <v>1756.8</v>
+        <v>958.6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,28 +2259,28 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39.5</v>
+        <v>45.5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2293,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>146000</v>
+        <v>140000</v>
       </c>
       <c r="E26" t="n">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="F26" t="n">
-        <v>715.7</v>
+        <v>921.1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2324,33 +2328,33 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>VENDIMIA VENDE!!!</t>
+          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2321/ficha/casa-en-venta-en-25-de-mayo-1900</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 146,000 (Requiere contraoferta del 4.3%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37.9</v>
+        <v>41.9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2359,17 +2363,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78900</v>
+        <v>68000</v>
       </c>
       <c r="E27" t="n">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="F27" t="n">
-        <v>388.7</v>
+        <v>708.3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2378,7 +2382,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2403,17 +2407,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>VENDIMIA VENDE</t>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2303/ficha/casa-en-venta-en-julian-barraquero-300</t>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 78,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2424,7 +2428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37.1</v>
+        <v>37.9</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2437,13 +2441,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="E28" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="F28" t="n">
-        <v>585.1</v>
+        <v>363</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2477,17 +2481,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
+          <t>TRE INMOBILIARIA VENDE CASA ubicada en Ciudad de Mendoza sobre calle Federico Moreno 1191, Capital - Mendoza. A cuadras de Av. San Martín, centros Comerciales, supermercados, Universidad Aconcagua ,escuelas etc.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/846/ficha/casa-en-venta-en-federico-moreno-al-1191-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 49,000)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2498,7 +2502,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35.8</v>
+        <v>37.1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2511,13 +2515,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E29" t="n">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F29" t="n">
-        <v>465.5</v>
+        <v>585.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2551,17 +2555,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
+          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2572,26 +2576,26 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35.3</v>
+        <v>35.8</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="F30" t="n">
-        <v>1100</v>
+        <v>465.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2600,7 +2604,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2625,32 +2629,32 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31.6</v>
+        <v>35.3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2659,13 +2663,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>58000</v>
+        <v>110000</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>580</v>
+        <v>1100</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2699,32 +2703,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30.7</v>
+        <v>31.8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2733,13 +2737,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>55000</v>
+        <v>150000</v>
       </c>
       <c r="E32" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F32" t="n">
-        <v>625</v>
+        <v>1666.7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2768,33 +2772,33 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30</v>
+        <v>31.6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2807,13 +2811,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>150000</v>
+        <v>58000</v>
       </c>
       <c r="E33" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>2027</v>
+        <v>580</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2822,7 +2826,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2842,27 +2846,27 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -2884,10 +2888,10 @@
         <v>150000</v>
       </c>
       <c r="E34" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F34" t="n">
-        <v>1898.7</v>
+        <v>2027</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2896,7 +2900,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2921,17 +2925,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2942,7 +2946,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20.9</v>
+        <v>30</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2955,13 +2959,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="E35" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F35" t="n">
-        <v>888.9</v>
+        <v>1898.7</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2990,33 +2994,33 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3029,13 +3033,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>75000</v>
+        <v>80000</v>
       </c>
       <c r="E36" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F36" t="n">
-        <v>1119.4</v>
+        <v>888.9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3069,17 +3073,17 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3103,60 +3107,134 @@
         </is>
       </c>
       <c r="D37" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>67</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>20</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>63300</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E38" t="n">
         <v>73</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F38" t="n">
         <v>867.1</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71</v>
+        <v>64.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150000</v>
+        <v>115000</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>1515.2</v>
+        <v>821.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -622,33 +622,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RE/MAX Ofrece a la Venta departamento a metros de calle Emilio Civit, la calle más linda de Mendoza y a 5 minutos caminando del Parque General San Martín. Pensado para vivir cómodo todo el año, en un edificio con Amenities completos y seguridad las 24 horas.</t>
+          <t>Departamento de categoría ubicado en calle Mitre, del centro Mendocino.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19860/ficha/departamento-en-venta-en-coronel-rodriguez-1000</t>
+          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/86/ficha/departamento-en-venta-en-mitre-1638</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85000</v>
+        <v>60000</v>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>658.9</v>
+        <v>666.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>COCUCCI INMOBILIARIA VENDE: Amplio departamento ubicado en el 5° piso de la Torre B2, con acceso mediante ascensor, muy buena distribución y luminosidad en la  Ciudad de Mendoza. Importante: La propiedad no dispone de cochera, aunque en la zona existen opciones de alquiler mensual. BARBARA LUCERO CCPIM 1817 - TEL: .</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19838/ficha/departamento-en-venta-en-san-juan-al-500</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 60,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95000</v>
+        <v>85000</v>
       </c>
       <c r="E5" t="n">
-        <v>294</v>
+        <v>129</v>
       </c>
       <c r="F5" t="n">
-        <v>323.1</v>
+        <v>658.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98000</v>
+        <v>95000</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>294</v>
       </c>
       <c r="F6" t="n">
-        <v>490</v>
+        <v>323.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1388,26 +1388,26 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>94900</v>
+        <v>75000</v>
       </c>
       <c r="E14" t="n">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="F14" t="n">
-        <v>379.6</v>
+        <v>675.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,47 +1441,47 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>100000</v>
+        <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="F15" t="n">
-        <v>534.8</v>
+        <v>656.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1510,33 +1510,33 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,17 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E16" t="n">
-        <v>111</v>
-      </c>
-      <c r="F16" t="n">
-        <v>675.7</v>
+        <v>125000</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1568,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,17 +1593,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,26 +1614,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47.3</v>
+        <v>46.1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="F17" t="n">
-        <v>656.9</v>
+        <v>541.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,28 +1667,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47.2</v>
+        <v>46.1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90000</v>
+        <v>129000</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F18" t="n">
-        <v>900</v>
+        <v>645</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1732,22 +1736,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
+          <t>Esta propiedad con excelente funcionalidad para uso profesional, instituto o familia numerosa, ofrece una residencia de 200 m² cubiertos sobre un terreno total de 143 m². Dispone de cuatro dormitorios espaciosos con placares, tres baños (incluyendo uno en las dependencias de servicio)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/18273-furlan-propiedades/inmuebles/3/ficha/casa-en-venta-en-tte-1-ibanez-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,26 +1762,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46.9</v>
+        <v>45.7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>115000</v>
+        <v>55000</v>
       </c>
       <c r="E19" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>642.5</v>
+        <v>625</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1790,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,28 +1815,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>115000</v>
+        <v>140000</v>
       </c>
       <c r="E20" t="n">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="F20" t="n">
-        <v>642.5</v>
+        <v>544.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1885,17 +1889,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
+          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
+          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,26 +1910,26 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46.6</v>
+        <v>43.4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>120000</v>
+        <v>81000</v>
       </c>
       <c r="E21" t="n">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>545.5</v>
+        <v>1051.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1954,33 +1958,33 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46.5</v>
+        <v>42.7</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,17 +1997,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>125000</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>139000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>86</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1616.3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
+          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2058,11 +2058,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45.7</v>
+        <v>41.9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55000</v>
+        <v>68000</v>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
-        <v>625</v>
+        <v>708.3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2111,47 +2111,47 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>45.6</v>
+        <v>35.3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>138000</v>
+        <v>110000</v>
       </c>
       <c r="E24" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>862.5</v>
+        <v>1100</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2185,47 +2185,47 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>45.6</v>
+        <v>31.8</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>139000</v>
+        <v>150000</v>
       </c>
       <c r="E25" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>958.6</v>
+        <v>1666.7</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2254,33 +2254,33 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
+          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
+          <t>🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>45.5</v>
+        <v>31.6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,17 +2289,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>140000</v>
+        <v>58000</v>
       </c>
       <c r="E26" t="n">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>921.1</v>
+        <v>580</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>41.9</v>
+        <v>30.7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68000</v>
+        <v>55000</v>
       </c>
       <c r="E27" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F27" t="n">
-        <v>708.3</v>
+        <v>625</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2428,7 +2428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37.9</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49000</v>
+        <v>150000</v>
       </c>
       <c r="E28" t="n">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="F28" t="n">
-        <v>363</v>
+        <v>2027</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2476,33 +2476,33 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA ubicada en Ciudad de Mendoza sobre calle Federico Moreno 1191, Capital - Mendoza. A cuadras de Av. San Martín, centros Comerciales, supermercados, Universidad Aconcagua ,escuelas etc.</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/846/ficha/casa-en-venta-en-federico-moreno-al-1191-ciudad-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 49,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>37.1</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="E29" t="n">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="F29" t="n">
-        <v>585.1</v>
+        <v>1898.7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2550,52 +2550,52 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35.8</v>
+        <v>29.5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>135000</v>
+        <v>85000</v>
       </c>
       <c r="E30" t="n">
-        <v>290</v>
+        <v>69</v>
       </c>
       <c r="F30" t="n">
-        <v>465.5</v>
+        <v>1231.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2629,17 +2629,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
+          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2650,11 +2650,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>35.3</v>
+        <v>20.9</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>110000</v>
+        <v>80000</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n">
-        <v>1100</v>
+        <v>888.9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2703,32 +2703,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31.8</v>
+        <v>20</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="E32" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="F32" t="n">
-        <v>1666.7</v>
+        <v>1119.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2772,33 +2772,33 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31.6</v>
+        <v>20</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>58000</v>
+        <v>63300</v>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F33" t="n">
-        <v>580</v>
+        <v>867.1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2851,390 +2851,20 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>74</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E35" t="n">
-        <v>79</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1898.7</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E36" t="n">
-        <v>90</v>
-      </c>
-      <c r="F36" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E37" t="n">
-        <v>67</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E38" t="n">
-        <v>73</v>
-      </c>
-      <c r="F38" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71</v>
+        <v>63.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,21 +509,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>1237.1</v>
+        <v>666.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA  VENDE Excelente departamento en 5ta Sección. Ubicado en una zona con rápida conectividad , este departamento combina amplitud, luminosidad y una ubicacióni privilegiada. Emplazado a pasos de la Casa de Gobierno, la ciclovía y con acceso inmediato a comercios, gastronomía y todos los medios de transporte.</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/880/ficha/departamento-en-venta-en-coronel-rodriguez-320-casi-vicente-gil-quinta-seccion</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115000</v>
+        <v>85000</v>
       </c>
       <c r="E3" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>821.4</v>
+        <v>658.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -622,22 +622,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Departamento de categoría ubicado en calle Mitre, del centro Mendocino.</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/86/ficha/departamento-en-venta-en-mitre-1638</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60000</v>
+        <v>130000</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="F4" t="n">
-        <v>666.7</v>
+        <v>541.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE: Amplio departamento ubicado en el 5° piso de la Torre B2, con acceso mediante ascensor, muy buena distribución y luminosidad en la  Ciudad de Mendoza. Importante: La propiedad no dispone de cochera, aunque en la zona existen opciones de alquiler mensual. BARBARA LUCERO CCPIM 1817 - TEL: .</t>
+          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19838/ficha/departamento-en-venta-en-san-juan-al-500</t>
+          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 60,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63.5</v>
+        <v>61.1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85000</v>
+        <v>129000</v>
       </c>
       <c r="E5" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="F5" t="n">
-        <v>658.9</v>
+        <v>871.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>Dueño vende .</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/19594-yanet-biluron/inmuebles/3/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.9</v>
+        <v>61.1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95000</v>
+        <v>129000</v>
       </c>
       <c r="E6" t="n">
-        <v>294</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>323.1</v>
+        <v>645</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -844,22 +844,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>Esta propiedad con excelente funcionalidad para uso profesional, instituto o familia numerosa, ofrece una residencia de 200 m² cubiertos sobre un terreno total de 143 m². Dispone de cuatro dormitorios espaciosos con placares, tres baños (incluyendo uno en las dependencias de servicio)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/18273-furlan-propiedades/inmuebles/3/ficha/casa-en-venta-en-tte-1-ibanez-mendoza</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62.2</v>
+        <v>60.5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88000</v>
+        <v>140000</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>257</v>
       </c>
       <c r="F7" t="n">
-        <v>888.9</v>
+        <v>544.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.1</v>
+        <v>56.9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,17 +953,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
+        <v>68000</v>
       </c>
       <c r="E8" t="n">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>687.5</v>
+        <v>708.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,30 +1018,30 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60.8</v>
+        <v>54.1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76000</v>
+        <v>128000</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="F9" t="n">
-        <v>1013.3</v>
+        <v>691.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,28 +1071,28 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
+          <t>FOLLOW presenta esta exclusiva casa, ubicada en el consolidado Barrio Soberanía Nacional. Esta propiedad combina una estructura sólida de excelente calidad constructiva con una ubicación inmejorable.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2515/ficha/casa-en-venta-en-posta-del-retamo-1800</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>58.4</v>
+        <v>51.5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>144400</v>
+        <v>125000</v>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>1110.8</v>
+        <v>1562.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1140,52 +1140,52 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55</v>
+        <v>48.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110000</v>
+        <v>62000</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="F11" t="n">
-        <v>1236</v>
+        <v>380.4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1214,56 +1214,56 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Descubra este encantador departamento ubicado en el corazón de la Cuarta Sección, en Capital, Mendoza. Situado en Paraguay 2855 Piso 1 Departamento 3, esta propiedad es ideal tanto para quienes buscan un hogar permanente como para aquellos interesados en una inversión con alto potencial de alquiler. Con escritura inmediata y posibilidad de permuta, las opciones son amplias.</t>
+          <t>A INGRESAR FINES DE JULIO</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/288316-coldwell-banker-impacto-pro/inmuebles/262/ficha/departamento-en-venta-en-paraguay-al-2800</t>
+          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 62,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>51.5</v>
+        <v>48.2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>125000</v>
+        <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="F12" t="n">
-        <v>1562.5</v>
+        <v>569.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1288,56 +1288,56 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>TRE INMOBILIARIA VENDE: CASA ubicada en Calle Rioja 228, casi esquina Julián Barraquero, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/865/ficha/casa-en-venta-en-rioja-al-200</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>94000</v>
+        <v>94900</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="F13" t="n">
-        <v>862.4</v>
+        <v>379.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1367,47 +1367,47 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
+          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 94,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="E14" t="n">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="F14" t="n">
-        <v>675.7</v>
+        <v>534.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1536,30 +1536,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46.5</v>
+        <v>47.2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>125000</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>90000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>900</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1593,28 +1589,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
+          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 125,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>46.1</v>
+        <v>46.9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1627,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>130000</v>
+        <v>115000</v>
       </c>
       <c r="E17" t="n">
-        <v>240</v>
+        <v>179</v>
       </c>
       <c r="F17" t="n">
-        <v>541.7</v>
+        <v>642.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1667,17 +1663,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
+          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
+          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1688,7 +1684,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>46.1</v>
+        <v>46.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>129000</v>
+        <v>115000</v>
       </c>
       <c r="E18" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="F18" t="n">
-        <v>645</v>
+        <v>642.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1736,22 +1732,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Esta propiedad con excelente funcionalidad para uso profesional, instituto o familia numerosa, ofrece una residencia de 200 m² cubiertos sobre un terreno total de 143 m². Dispone de cuatro dormitorios espaciosos con placares, tres baños (incluyendo uno en las dependencias de servicio)</t>
+          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/18273-furlan-propiedades/inmuebles/3/ficha/casa-en-venta-en-tte-1-ibanez-mendoza</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1762,26 +1758,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>45.7</v>
+        <v>46.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55000</v>
+        <v>120000</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="F19" t="n">
-        <v>625</v>
+        <v>545.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1790,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1815,47 +1811,47 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>140000</v>
+        <v>55000</v>
       </c>
       <c r="E20" t="n">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
-        <v>544.7</v>
+        <v>625</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1864,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1889,32 +1885,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
+          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>43.4</v>
+        <v>45.7</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1923,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81000</v>
+        <v>55000</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>1051.9</v>
+        <v>625</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1958,22 +1954,22 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1984,26 +1980,26 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>42.7</v>
+        <v>45.6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>139000</v>
       </c>
       <c r="E22" t="n">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="F22" t="n">
-        <v>1616.3</v>
+        <v>958.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2012,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2037,28 +2033,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Vendo departamento en Barrio Bombal, complejo Terrazas de Bombal, Godoy Cruz, 3er piso.</t>
+          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/6/ficha/departamento-en-venta-en-beltran-1812</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>41.9</v>
+        <v>45.6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,17 +2063,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68000</v>
+        <v>138000</v>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="F23" t="n">
-        <v>708.3</v>
+        <v>862.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2111,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2132,26 +2128,26 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>35.3</v>
+        <v>45.5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>110000</v>
+        <v>140000</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="F24" t="n">
-        <v>1100</v>
+        <v>921.1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2160,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2185,32 +2181,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31.8</v>
+        <v>43.5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2219,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>150000</v>
+        <v>124900</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F25" t="n">
-        <v>1666.7</v>
+        <v>1435.6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2254,33 +2250,33 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31.6</v>
+        <v>38.5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,17 +2285,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58000</v>
+        <v>75000</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="F26" t="n">
-        <v>580</v>
+        <v>421.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2308,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2328,22 +2324,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>ACL PROPIEDADES VENDE CASA - En la ciudad de Mendoza Capital, específicamente en la Sexta Sección Residencial. Ubicada en la calle Quiniela Martin, a pocos metros del Polo Judicial, y a pocos minutos de la universidad nacional de cuyo y del centro de la ciudad. Esta propiedad cuenta con una superficie total de 299m2 y una superficie cubierta de 178m2, ya posee proyección para construir una segunda planta. Menos de 19 años de antigüedad. Al ingresar, te recibirá un amplio living comedor, perfecto para disfrutar de momentos en familia o con amigos. La cocina integrada, muy iluminada. Además, la casa cuenta con una lavandería, 2 baños completos (uno de ellos en suite con antebaño), y 2 acogedores dormitorios. El patio de esta propiedad es muy generoso, ideal para disfrutar de momentos al aire libre y para que tus mascotas jueguen libremente. Además, cuenta con una cochera techada, brindándote comodidad y seguridad para tu estancia vehículo. Posee una antigüedad de 20 años y en excelente estado de conservación, esta casa es apta para crédito hipotecario y está lista para escriturar. Además, se encuentra en una zona escolar, perfecta para familias con niños en edad escolar. Si estás buscando un hogar acogedor, luminoso y listo para habitar, esta propiedad es la opción ideal para ti. No pierdas la oportunidad de conocerla y hacerla tuya. ¡Contáctanos para más información y para agendar una visita! Valor: USD75.000 (se escuchan ofertas razonables). ¿Recibes permuta? ¡Sí! ¡Esta casa podría ser tuya!</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/593/ficha/casa-en-venta-en-quiniela-martin</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2354,7 +2350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30.7</v>
+        <v>37.9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2363,17 +2359,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>55000</v>
+        <v>49000</v>
       </c>
       <c r="E27" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="F27" t="n">
-        <v>625</v>
+        <v>363</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2407,17 +2403,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+          <t>TRE INMOBILIARIA VENDE CASA ubicada en Ciudad de Mendoza sobre calle Federico Moreno 1191, Capital - Mendoza. A cuadras de Av. San Martín, centros Comerciales, supermercados, Universidad Aconcagua ,escuelas etc.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/846/ficha/casa-en-venta-en-federico-moreno-al-1191-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 49,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2428,7 +2424,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>37.1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2437,17 +2433,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>150000</v>
+        <v>110000</v>
       </c>
       <c r="E28" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="F28" t="n">
-        <v>2027</v>
+        <v>585.1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2476,33 +2472,33 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>35.8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2511,17 +2507,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>150000</v>
+        <v>135000</v>
       </c>
       <c r="E29" t="n">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="F29" t="n">
-        <v>1898.7</v>
+        <v>465.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2530,7 +2526,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2550,37 +2546,37 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29.5</v>
+        <v>35.3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2589,13 +2585,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>85000</v>
+        <v>110000</v>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>1231.9</v>
+        <v>1100</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2604,7 +2600,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2629,28 +2625,28 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20.9</v>
+        <v>31.6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2663,13 +2659,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80000</v>
+        <v>58000</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>888.9</v>
+        <v>580</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2703,17 +2699,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2724,7 +2720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>31.5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2737,13 +2733,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="F32" t="n">
-        <v>1119.4</v>
+        <v>882.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2777,17 +2773,17 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>Complejo Villa Guadalupe</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3950323436-complejo-villa-guadalupe-_JM</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2798,73 +2794,739 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>93</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>74</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>221</v>
+      </c>
+      <c r="F35" t="n">
+        <v>678.7</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Venta Departamento Sobre Calle San Martin ,g.c</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3912783154-venta-departamento-sobre-calle-san-martin-gc-_JM</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1898.7</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>78</v>
+      </c>
+      <c r="F37" t="n">
+        <v>961.5</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Departamento Tipo Dúplex En Barrio Bancario Godoy Cruz Mendoza</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4032188450-departamento-tipo-duplex-en-barrio-bancario-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>128000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>87</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1471.3</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Venta Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>95</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1315.8</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Dúplex En Calle Beltrán - 3 Dormitorios, 2 Baños, Seguridad - Complejo Privado</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1951199593-duplex-en-calle-beltran-3-dormitorios-2-banos-seguridad-complejo-privado-_JM</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 125,000)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>86</v>
+      </c>
+      <c r="F40" t="n">
+        <v>930.2</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Dúplex En Venta -g.cruz-id:314510</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>20</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>73</v>
-      </c>
-      <c r="F33" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="D41" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>67</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>20</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Venta De Departamento En Pozo En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3888610428-venta-de-departamento-en-pozo-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 115,000)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63.5</v>
+        <v>84.3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80000</v>
+        <v>85500</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
-        <v>666.7</v>
+        <v>381.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,22 +553,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>El equipo de Re/max Follow a cargo del corredor inmobiliario Gustavo Silva CCPIM 1947, ofrece a la venta casa con piscina y cabaña o departamento independiente, en el Barrio Privado "Condominio Nuevas Quintas".</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2109/ficha/casa-en-venta-en-ruta-provincial-99-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,500) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1018,26 +1018,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54.1</v>
+        <v>51.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>128000</v>
+        <v>125000</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>691.9</v>
+        <v>1562.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1066,56 +1066,56 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FOLLOW presenta esta exclusiva casa, ubicada en el consolidado Barrio Soberanía Nacional. Esta propiedad combina una estructura sólida de excelente calidad constructiva con una ubicación inmejorable.</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2515/ficha/casa-en-venta-en-posta-del-retamo-1800</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>51.5</v>
+        <v>48</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>125000</v>
+        <v>94900</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="F10" t="n">
-        <v>1562.5</v>
+        <v>379.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1140,33 +1140,33 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62000</v>
+        <v>100000</v>
       </c>
       <c r="E11" t="n">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="F11" t="n">
-        <v>380.4</v>
+        <v>534.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A INGRESAR FINES DE JULIO</t>
+          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 62,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,26 +1240,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48.2</v>
+        <v>47.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>569.6</v>
+        <v>656.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE: CASA ubicada en Calle Rioja 228, casi esquina Julián Barraquero, Ciudad de Mendoza.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/865/ficha/casa-en-venta-en-rioja-al-200</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>94900</v>
+        <v>90000</v>
       </c>
       <c r="E13" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>379.6</v>
+        <v>900</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
+          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>47.7</v>
+        <v>46.9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100000</v>
+        <v>115000</v>
       </c>
       <c r="E14" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F14" t="n">
-        <v>534.8</v>
+        <v>642.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
+          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
+          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,26 +1462,26 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90000</v>
+        <v>115000</v>
       </c>
       <c r="E15" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="F15" t="n">
-        <v>656.9</v>
+        <v>642.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,28 +1515,28 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90000</v>
+        <v>120000</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="F16" t="n">
-        <v>900</v>
+        <v>545.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
+          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,26 +1610,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>46.9</v>
+        <v>45.7</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>115000</v>
+        <v>55000</v>
       </c>
       <c r="E17" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>642.5</v>
+        <v>625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,47 +1663,47 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
+          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>46.9</v>
+        <v>45.7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>115000</v>
+        <v>55000</v>
       </c>
       <c r="E18" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>642.5</v>
+        <v>625</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46.6</v>
+        <v>45.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>120000</v>
+        <v>138000</v>
       </c>
       <c r="E19" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>545.5</v>
+        <v>862.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
+          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1832,26 +1832,26 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55000</v>
+        <v>139000</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="F20" t="n">
-        <v>625</v>
+        <v>958.6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1885,47 +1885,47 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55000</v>
+        <v>140000</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="F21" t="n">
-        <v>625</v>
+        <v>921.1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1959,28 +1959,28 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>45.6</v>
+        <v>39.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>139000</v>
+        <v>146000</v>
       </c>
       <c r="E22" t="n">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="F22" t="n">
-        <v>958.6</v>
+        <v>715.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2028,33 +2028,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
+          <t>VENDIMIA VENDE!!!</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2321/ficha/casa-en-venta-en-25-de-mayo-1900</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 146,000 (Requiere contraoferta del 4.3%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45.6</v>
+        <v>38.5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>138000</v>
+        <v>75000</v>
       </c>
       <c r="E23" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="F23" t="n">
-        <v>862.5</v>
+        <v>421.3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2102,22 +2102,22 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
+          <t>ACL PROPIEDADES VENDE CASA - En la ciudad de Mendoza Capital, específicamente en la Sexta Sección Residencial. Ubicada en la calle Quiniela Martin, a pocos metros del Polo Judicial, y a pocos minutos de la universidad nacional de cuyo y del centro de la ciudad. Esta propiedad cuenta con una superficie total de 299m2 y una superficie cubierta de 178m2, ya posee proyección para construir una segunda planta. Menos de 19 años de antigüedad. Al ingresar, te recibirá un amplio living comedor, perfecto para disfrutar de momentos en familia o con amigos. La cocina integrada, muy iluminada. Además, la casa cuenta con una lavandería, 2 baños completos (uno de ellos en suite con antebaño), y 2 acogedores dormitorios. El patio de esta propiedad es muy generoso, ideal para disfrutar de momentos al aire libre y para que tus mascotas jueguen libremente. Además, cuenta con una cochera techada, brindándote comodidad y seguridad para tu estancia vehículo. Posee una antigüedad de 20 años y en excelente estado de conservación, esta casa es apta para crédito hipotecario y está lista para escriturar. Además, se encuentra en una zona escolar, perfecta para familias con niños en edad escolar. Si estás buscando un hogar acogedor, luminoso y listo para habitar, esta propiedad es la opción ideal para ti. No pierdas la oportunidad de conocerla y hacerla tuya. ¡Contáctanos para más información y para agendar una visita! Valor: USD75.000 (se escuchan ofertas razonables). ¿Recibes permuta? ¡Sí! ¡Esta casa podría ser tuya!</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/593/ficha/casa-en-venta-en-quiniela-martin</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>45.5</v>
+        <v>37.9</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>140000</v>
+        <v>78900</v>
       </c>
       <c r="E24" t="n">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="F24" t="n">
-        <v>921.1</v>
+        <v>388.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
+          <t>VENDIMIA VENDE</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2303/ficha/casa-en-venta-en-julian-barraquero-300</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 78,900)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>43.5</v>
+        <v>37.1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2211,17 +2211,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>124900</v>
+        <v>110000</v>
       </c>
       <c r="E25" t="n">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="F25" t="n">
-        <v>1435.6</v>
+        <v>585.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2255,28 +2255,28 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Venta Hermoso Departamento Duplex - Barrio Bombal</t>
+          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1945076259-venta-hermoso-departamento-duplex-barrio-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,900)</t>
+          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>38.5</v>
+        <v>35.8</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75000</v>
+        <v>135000</v>
       </c>
       <c r="E26" t="n">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="F26" t="n">
-        <v>421.3</v>
+        <v>465.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2324,22 +2324,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES VENDE CASA - En la ciudad de Mendoza Capital, específicamente en la Sexta Sección Residencial. Ubicada en la calle Quiniela Martin, a pocos metros del Polo Judicial, y a pocos minutos de la universidad nacional de cuyo y del centro de la ciudad. Esta propiedad cuenta con una superficie total de 299m2 y una superficie cubierta de 178m2, ya posee proyección para construir una segunda planta. Menos de 19 años de antigüedad. Al ingresar, te recibirá un amplio living comedor, perfecto para disfrutar de momentos en familia o con amigos. La cocina integrada, muy iluminada. Además, la casa cuenta con una lavandería, 2 baños completos (uno de ellos en suite con antebaño), y 2 acogedores dormitorios. El patio de esta propiedad es muy generoso, ideal para disfrutar de momentos al aire libre y para que tus mascotas jueguen libremente. Además, cuenta con una cochera techada, brindándote comodidad y seguridad para tu estancia vehículo. Posee una antigüedad de 20 años y en excelente estado de conservación, esta casa es apta para crédito hipotecario y está lista para escriturar. Además, se encuentra en una zona escolar, perfecta para familias con niños en edad escolar. Si estás buscando un hogar acogedor, luminoso y listo para habitar, esta propiedad es la opción ideal para ti. No pierdas la oportunidad de conocerla y hacerla tuya. ¡Contáctanos para más información y para agendar una visita! Valor: USD75.000 (se escuchan ofertas razonables). ¿Recibes permuta? ¡Sí! ¡Esta casa podría ser tuya!</t>
+          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/593/ficha/casa-en-venta-en-quiniela-martin</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2350,26 +2350,26 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37.9</v>
+        <v>35.3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49000</v>
+        <v>110000</v>
       </c>
       <c r="E27" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>363</v>
+        <v>1100</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2403,28 +2403,28 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA ubicada en Ciudad de Mendoza sobre calle Federico Moreno 1191, Capital - Mendoza. A cuadras de Av. San Martín, centros Comerciales, supermercados, Universidad Aconcagua ,escuelas etc.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/846/ficha/casa-en-venta-en-federico-moreno-al-1191-ciudad-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 49,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37.1</v>
+        <v>31.6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2433,17 +2433,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>110000</v>
+        <v>58000</v>
       </c>
       <c r="E28" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>585.1</v>
+        <v>580</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35.8</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2507,17 +2507,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>135000</v>
+        <v>150000</v>
       </c>
       <c r="E29" t="n">
-        <v>290</v>
+        <v>74</v>
       </c>
       <c r="F29" t="n">
-        <v>465.5</v>
+        <v>2027</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2546,37 +2546,37 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
+          <t>Venta Departamento Godoy Cruz Con Cochera</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35.3</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F30" t="n">
-        <v>1100</v>
+        <v>1898.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2620,33 +2620,33 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31.6</v>
+        <v>20.9</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>58000</v>
+        <v>80000</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n">
-        <v>580</v>
+        <v>888.9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2699,17 +2699,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2720,7 +2720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31.5</v>
+        <v>20</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="E32" t="n">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="F32" t="n">
-        <v>882.4</v>
+        <v>1119.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2773,17 +2773,17 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Complejo Villa Guadalupe</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3950323436-complejo-villa-guadalupe-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2794,7 +2794,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30.3</v>
+        <v>20</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2807,13 +2807,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>99000</v>
+        <v>63300</v>
       </c>
       <c r="E33" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="F33" t="n">
-        <v>1064.5</v>
+        <v>867.1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2847,686 +2847,20 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Venta Amplio Departamento Godoy Cruz  Apto Credito</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912396714-venta-amplio-departamento-godoy-cruz-apto-credito-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>74</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E35" t="n">
-        <v>221</v>
-      </c>
-      <c r="F35" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Venta Departamento Sobre Calle San Martin ,g.c</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3912783154-venta-departamento-sobre-calle-san-martin-gc-_JM</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>30</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E36" t="n">
-        <v>79</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1898.7</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>30</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E37" t="n">
-        <v>78</v>
-      </c>
-      <c r="F37" t="n">
-        <v>961.5</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Departamento Tipo Dúplex En Barrio Bancario Godoy Cruz Mendoza</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4032188450-departamento-tipo-duplex-en-barrio-bancario-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>128000</v>
-      </c>
-      <c r="E38" t="n">
-        <v>87</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1471.3</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Venta Duplex En Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>30</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>125000</v>
-      </c>
-      <c r="E39" t="n">
-        <v>95</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1315.8</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Dúplex En Calle Beltrán - 3 Dormitorios, 2 Baños, Seguridad - Complejo Privado</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1951199593-duplex-en-calle-beltran-3-dormitorios-2-banos-seguridad-complejo-privado-_JM</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 125,000)</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E40" t="n">
-        <v>86</v>
-      </c>
-      <c r="F40" t="n">
-        <v>930.2</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Dúplex En Venta -g.cruz-id:314510</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3724250208-duplex-en-venta-gcruz-id314510-_JM</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E41" t="n">
-        <v>67</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>20</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>115000</v>
-      </c>
-      <c r="E42" t="n">
-        <v>100</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Venta De Departamento En Pozo En Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3888610428-venta-de-departamento-en-pozo-en-godoy-cruz-_JM</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 115,000)</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,26 +500,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84.3</v>
+        <v>66.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85500</v>
+        <v>63000</v>
       </c>
       <c r="E2" t="n">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="F2" t="n">
-        <v>381.7</v>
+        <v>463.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,22 +553,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>El equipo de Re/max Follow a cargo del corredor inmobiliario Gustavo Silva CCPIM 1947, ofrece a la venta casa con piscina y cabaña o departamento independiente, en el Barrio Privado "Condominio Nuevas Quintas".</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2109/ficha/casa-en-venta-en-ruta-provincial-99-0</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,500) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61.1</v>
+        <v>62.9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>130000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="F4" t="n">
-        <v>541.7</v>
+        <v>323.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61.1</v>
+        <v>62.8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>129000</v>
+        <v>98000</v>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>871.6</v>
+        <v>490</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dueño vende .</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/19594-yanet-biluron/inmuebles/3/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>129000</v>
+        <v>88000</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F6" t="n">
-        <v>645</v>
+        <v>888.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -844,22 +844,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Esta propiedad con excelente funcionalidad para uso profesional, instituto o familia numerosa, ofrece una residencia de 200 m² cubiertos sobre un terreno total de 143 m². Dispone de cuatro dormitorios espaciosos con placares, tres baños (incluyendo uno en las dependencias de servicio)</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/18273-furlan-propiedades/inmuebles/3/ficha/casa-en-venta-en-tte-1-ibanez-mendoza</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60.5</v>
+        <v>62.1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>140000</v>
+        <v>110000</v>
       </c>
       <c r="E7" t="n">
-        <v>257</v>
+        <v>160</v>
       </c>
       <c r="F7" t="n">
-        <v>544.7</v>
+        <v>687.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56.9</v>
+        <v>53.4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68000</v>
+        <v>95000</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>708.3</v>
+        <v>1233.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1092,30 +1092,30 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94900</v>
+        <v>68000</v>
       </c>
       <c r="E10" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>379.6</v>
+        <v>906.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1145,51 +1145,51 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>El equipo de Follow ofrece una propiedad única, que combina espacio comercial</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2424/ficha/casa-en-venta-en-jose-federico-moreno-2400</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47.7</v>
+        <v>48.8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>100000</v>
+        <v>129000</v>
       </c>
       <c r="E11" t="n">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
-        <v>534.8</v>
+        <v>1131.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1214,27 +1214,27 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES - VENDE CASA EN SEXTA SECCIÓN a metros del metro tranvía, muy cerca del parque Central, excelente ubicación, muy cerca del centro de la ciudad, en un punto muy estratégico. Se desarrolla en una superficie total de 318 metros cuadrados y 187 metros cubiertos. Se desarrolla en amplio living comedor, cocina con comedor de diario, 4 dormitorios y 2 baños, cochera, amplio patio y quincho. APTA CRÉDITO- VALOR USD100.000</t>
+          <t>DEPARTAMENTO 9 AMBIENTES EN VENTA - GODOY CRUZ - MENDOZA - 157 M²</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/504/ficha/casa-en-venta-en-jose-hernandez-58</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18971/ficha/departamento-en-venta-en-juan-de-garay-400</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -1314,26 +1314,26 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47.2</v>
+        <v>46.8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>90000</v>
+        <v>105000</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>900</v>
+        <v>954.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,47 +1367,47 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA  ubicada  en calle Rondeau, entre Rioja y Salta, Ciudad de Mendoza.</t>
+          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/723/ficha/casa-en-venta-en-rondeau-346-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46.9</v>
+        <v>45.7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>115000</v>
+        <v>55000</v>
       </c>
       <c r="E14" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>642.5</v>
+        <v>625</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,47 +1441,47 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Casa en 6ta sección de Ciudad de Mendoza.</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/30802-monserrat-inmobiliaria/inmuebles/449/ficha/casa-en-venta-en-martinez-de-rosas-3091-mendoza-provincia-de-mendoza-argentina</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>46.9</v>
+        <v>45</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>115000</v>
+        <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>642.5</v>
+        <v>1097.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,47 +1515,47 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>VENTA | CASA | SEXTA SECCION | CIUDAD MENDOZA</t>
+          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/672/ficha/casa-en-venta-en-martinez-de-rosas-3091</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46.6</v>
+        <v>44.9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>120000</v>
+        <v>77500</v>
       </c>
       <c r="E16" t="n">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>545.5</v>
+        <v>1174.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE CASA, Ubicada en Calle Soler esquina España, 4ta sección, Ciudad.</t>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/684/ficha/casa-en-venta-en-soler-199-esquina-espana-4ta-seccion-ciudad</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45.7</v>
+        <v>41.9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55000</v>
+        <v>68000</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
-        <v>625</v>
+        <v>708.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,32 +1663,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>45.7</v>
+        <v>39.8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55000</v>
+        <v>130000</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>625</v>
+        <v>1756.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,26 +1758,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>45.6</v>
+        <v>35.3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>138000</v>
+        <v>110000</v>
       </c>
       <c r="E19" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>862.5</v>
+        <v>1100</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD DE INVERSION - VENTA - CASA CIUDAD DE MENDOZA!</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/774/ficha/casa-en-venta-en-25-de-mayo-al-2000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45.6</v>
+        <v>31.6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>139000</v>
+        <v>58000</v>
       </c>
       <c r="E20" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>958.6</v>
+        <v>580</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>RICCARDI PROPIEDADES VENDE, hermosísima casa ubicada en Barrio Residencial Covse , excelente ubicación logística , cercano al parque general san martín , adyacente a Universidad de Cuyo, mucho movimiento de transporte publico en cercanías.</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/540/ficha/casa-en-venta-en-calle-democracia</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>45.5</v>
+        <v>30.7</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>140000</v>
+        <v>55000</v>
       </c>
       <c r="E21" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>921.1</v>
+        <v>625</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE casa a reciclar en plena Quinta Sección</t>
+          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2408/ficha/casa-en-venta-en-olegario-andrade-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,7 +1980,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>39.5</v>
+        <v>30</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1989,17 +1989,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>146000</v>
+        <v>53000</v>
       </c>
       <c r="E22" t="n">
-        <v>204</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>715.7</v>
+        <v>757.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2028,33 +2028,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>VENDIMIA VENDE!!!</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2321/ficha/casa-en-venta-en-25-de-mayo-1900</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 146,000 (Requiere contraoferta del 4.3%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>38.5</v>
+        <v>30</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="E23" t="n">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="F23" t="n">
-        <v>421.3</v>
+        <v>1898.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2102,33 +2102,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES VENDE CASA - En la ciudad de Mendoza Capital, específicamente en la Sexta Sección Residencial. Ubicada en la calle Quiniela Martin, a pocos metros del Polo Judicial, y a pocos minutos de la universidad nacional de cuyo y del centro de la ciudad. Esta propiedad cuenta con una superficie total de 299m2 y una superficie cubierta de 178m2, ya posee proyección para construir una segunda planta. Menos de 19 años de antigüedad. Al ingresar, te recibirá un amplio living comedor, perfecto para disfrutar de momentos en familia o con amigos. La cocina integrada, muy iluminada. Además, la casa cuenta con una lavandería, 2 baños completos (uno de ellos en suite con antebaño), y 2 acogedores dormitorios. El patio de esta propiedad es muy generoso, ideal para disfrutar de momentos al aire libre y para que tus mascotas jueguen libremente. Además, cuenta con una cochera techada, brindándote comodidad y seguridad para tu estancia vehículo. Posee una antigüedad de 20 años y en excelente estado de conservación, esta casa es apta para crédito hipotecario y está lista para escriturar. Además, se encuentra en una zona escolar, perfecta para familias con niños en edad escolar. Si estás buscando un hogar acogedor, luminoso y listo para habitar, esta propiedad es la opción ideal para ti. No pierdas la oportunidad de conocerla y hacerla tuya. ¡Contáctanos para más información y para agendar una visita! Valor: USD75.000 (se escuchan ofertas razonables). ¿Recibes permuta? ¡Sí! ¡Esta casa podría ser tuya!</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/593/ficha/casa-en-venta-en-quiniela-martin</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>37.9</v>
+        <v>30</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2137,17 +2137,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78900</v>
+        <v>128000</v>
       </c>
       <c r="E24" t="n">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>388.7</v>
+        <v>1471.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>VENDIMIA VENDE</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2303/ficha/casa-en-venta-en-julian-barraquero-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 78,900)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>37.1</v>
+        <v>20.9</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2211,17 +2211,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>110000</v>
+        <v>80000</v>
       </c>
       <c r="E25" t="n">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>585.1</v>
+        <v>888.9</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>CASA EN VENTA – EXCELENTE UBICACIÓN EN SEXTA SECCIÓN, MENDOZAJosé Hernández 340 – Sexta Sección, Mendoza</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/639/ficha/casa-en-venta-en-jose-hernandez-al-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2276,7 +2276,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>35.8</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2285,17 +2285,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>135000</v>
+        <v>75000</v>
       </c>
       <c r="E26" t="n">
-        <v>290</v>
+        <v>67</v>
       </c>
       <c r="F26" t="n">
-        <v>465.5</v>
+        <v>1119.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ubicada en la calle 12 de Febrero, en la 6.ª Sección Residencial Norte de Mendoza, esta casa, además, posee un hermoso local comercial en venta, se presenta como una oportunidad única para quienes buscan un espacio amplio y versátil, tanto para vivir y desarrollar su actividad comercial o para vivienda y alquiler de local comercial. Con un precio de U$D 135.000 , esta propiedad cuenta con una antigüedad de 27 años, ofreciendo un total de 290 m2, todos ellos cubiertos. La distribución interior incluye en su planta alta de 150 m2: 2 dormitorios, 2 baños, cocina, comedor y un gran y acogedor living con estufa hogar colgante, de diseño, además de un escritorio y una enorme dependencia de servicio o de usos múltiples y un patio con churrasquera, brindando el espacio ideal para familias o profesionales. En su planta baja se encuentra el local comercial de 140 m2, distribuido en un espacio reservado para recepción y vidriera, baño, oficina, depósito y el área destinada a salón comercial.-</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/720/ficha/casa-en-venta-en-12-de-febrero-3660</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2350,11 +2350,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35.3</v>
+        <v>20</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>110000</v>
+        <v>63300</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F27" t="n">
-        <v>1100</v>
+        <v>867.1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2403,464 +2403,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>58000</v>
-      </c>
-      <c r="E28" t="n">
-        <v>100</v>
-      </c>
-      <c r="F28" t="n">
-        <v>580</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Duplex En Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>30</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E29" t="n">
-        <v>74</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Venta Departamento Godoy Cruz Con Cochera</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1805521295-venta-departamento-godoy-cruz-con-cochera-_JM</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E30" t="n">
-        <v>79</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1898.7</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90</v>
-      </c>
-      <c r="F31" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>20</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E32" t="n">
-        <v>67</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>20</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>73</v>
-      </c>
-      <c r="F33" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66.2</v>
+        <v>63.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,17 +509,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63000</v>
+        <v>80000</v>
       </c>
       <c r="E2" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>463.2</v>
+        <v>666.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.5</v>
+        <v>62.9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85000</v>
+        <v>95000</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>294</v>
       </c>
       <c r="F3" t="n">
-        <v>658.9</v>
+        <v>323.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62.9</v>
+        <v>62.2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>88000</v>
       </c>
       <c r="E4" t="n">
-        <v>294</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>323.1</v>
+        <v>888.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62.8</v>
+        <v>51.5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -731,21 +731,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>98000</v>
+        <v>125000</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>490</v>
+        <v>1562.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -770,33 +770,33 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.2</v>
+        <v>50.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88000</v>
+        <v>68000</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>888.9</v>
+        <v>906.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,28 +849,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62.1</v>
+        <v>49.9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>110000</v>
+        <v>70000</v>
       </c>
       <c r="E7" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>687.5</v>
+        <v>1000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53.4</v>
+        <v>48.8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,17 +957,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95000</v>
+        <v>129000</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F8" t="n">
-        <v>1233.8</v>
+        <v>1131.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>DEPARTAMENTO 9 AMBIENTES EN VENTA - GODOY CRUZ - MENDOZA - 157 M²</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18971/ficha/departamento-en-venta-en-juan-de-garay-400</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51.5</v>
+        <v>47.3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>125000</v>
+        <v>90000</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
-        <v>1562.5</v>
+        <v>656.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1066,33 +1066,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.8</v>
+        <v>46.8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68000</v>
+        <v>105000</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>906.7</v>
+        <v>954.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48.8</v>
+        <v>45.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,22 +1179,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>129000</v>
+        <v>55000</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>1131.6</v>
+        <v>625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1219,28 +1219,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 9 AMBIENTES EN VENTA - GODOY CRUZ - MENDOZA - 157 M²</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18971/ficha/departamento-en-venta-en-juan-de-garay-400</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.3</v>
+        <v>45</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>656.9</v>
+        <v>1097.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1314,7 +1314,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>46.8</v>
+        <v>44.9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>105000</v>
+        <v>77500</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>954.5</v>
+        <v>1174.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,11 +1388,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45.7</v>
+        <v>41.9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55000</v>
+        <v>68000</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>625</v>
+        <v>708.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>45</v>
+        <v>35.3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>1097.6</v>
+        <v>1100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44.9</v>
+        <v>33.1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>77500</v>
+        <v>63000</v>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
-        <v>1174.2</v>
+        <v>562.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,28 +1589,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>Oportunidad de inversión!</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>41.9</v>
+        <v>31.6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68000</v>
+        <v>58000</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>708.3</v>
+        <v>580</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1684,11 +1684,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39.8</v>
+        <v>30.7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>130000</v>
+        <v>55000</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>1756.8</v>
+        <v>625</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35.3</v>
+        <v>30</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>110000</v>
+        <v>53000</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>1100</v>
+        <v>757.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,28 +1811,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31.6</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58000</v>
+        <v>150000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
-        <v>580</v>
+        <v>1898.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,33 +1880,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30.7</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55000</v>
+        <v>128000</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>625</v>
+        <v>1471.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1959,17 +1959,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+          <t>Venta Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,7 +1980,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>20.9</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>53000</v>
+        <v>80000</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>757.1</v>
+        <v>888.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,17 +2033,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2054,7 +2054,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
-        <v>1898.7</v>
+        <v>1119.4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>128000</v>
+        <v>63300</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
-        <v>1471.3</v>
+        <v>867.1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,242 +2181,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E25" t="n">
-        <v>90</v>
-      </c>
-      <c r="F25" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>67</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E27" t="n">
-        <v>73</v>
-      </c>
-      <c r="F27" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63.5</v>
+        <v>66.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,17 +509,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80000</v>
+        <v>63000</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F2" t="n">
-        <v>666.7</v>
+        <v>463.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>95000</v>
+        <v>85000</v>
       </c>
       <c r="E3" t="n">
-        <v>294</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>323.1</v>
+        <v>658.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62.2</v>
+        <v>63.5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88000</v>
+        <v>80000</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
-        <v>888.9</v>
+        <v>666.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51.5</v>
+        <v>62.9</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -731,21 +731,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>125000</v>
+        <v>95000</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="F5" t="n">
-        <v>1562.5</v>
+        <v>323.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -770,33 +770,33 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50.8</v>
+        <v>62.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68000</v>
+        <v>98000</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>906.7</v>
+        <v>490</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,28 +849,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>49.9</v>
+        <v>62.2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70000</v>
+        <v>88000</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>1000</v>
+        <v>888.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48.8</v>
+        <v>62.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,21 +953,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>129000</v>
+        <v>110000</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="F8" t="n">
-        <v>1131.6</v>
+        <v>687.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 9 AMBIENTES EN VENTA - GODOY CRUZ - MENDOZA - 157 M²</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18971/ficha/departamento-en-venta-en-juan-de-garay-400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47.3</v>
+        <v>53.4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>656.9</v>
+        <v>1233.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46.8</v>
+        <v>51.5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>105000</v>
+        <v>125000</v>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>954.5</v>
+        <v>1562.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
+          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45.7</v>
+        <v>48.8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,22 +1179,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55000</v>
+        <v>129000</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
-        <v>625</v>
+        <v>1131.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1219,28 +1219,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>DEPARTAMENTO 9 AMBIENTES EN VENTA - GODOY CRUZ - MENDOZA - 157 M²</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18971/ficha/departamento-en-venta-en-juan-de-garay-400</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45</v>
+        <v>47.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>1097.6</v>
+        <v>656.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1314,7 +1314,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44.9</v>
+        <v>47.2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77500</v>
+        <v>145000</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="F13" t="n">
-        <v>1174.2</v>
+        <v>1394.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1362,37 +1362,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>Departamento de categoría en pleno centro mendocino, Edificio Elipsium</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19113/ficha/departamento-en-venta-en-necochea-1400</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>41.9</v>
+        <v>46.8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>68000</v>
+        <v>105000</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>708.3</v>
+        <v>954.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,28 +1441,28 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>35.3</v>
+        <v>45.7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>1100</v>
+        <v>625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>33.1</v>
+        <v>45</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63000</v>
+        <v>90000</v>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>562.5</v>
+        <v>1097.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Oportunidad de inversión!</t>
+          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31.6</v>
+        <v>44.9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58000</v>
+        <v>77500</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>580</v>
+        <v>1174.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1663,28 +1663,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30.7</v>
+        <v>41.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55000</v>
+        <v>68000</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
-        <v>625</v>
+        <v>708.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA CON BALCÓN EN CORONEL DORREGO, GUAYMALLÉN, MENDOZA</t>
+          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/2417/ficha/departamento-en-venta-en-falucho-300</t>
+          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,11 +1758,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30</v>
+        <v>39.8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53000</v>
+        <v>130000</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
-        <v>757.1</v>
+        <v>1756.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,32 +1811,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>35.3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>150000</v>
+        <v>110000</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>1898.7</v>
+        <v>1100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,37 +1880,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>33.1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>128000</v>
+        <v>63000</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>1471.3</v>
+        <v>562.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta Duplex En Godoy Cruz</t>
+          <t>Oportunidad de inversión!</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3914417650-venta-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000)</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,7 +1980,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20.9</v>
+        <v>31.6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80000</v>
+        <v>58000</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>888.9</v>
+        <v>580</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,17 +2033,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2054,7 +2054,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F23" t="n">
-        <v>1119.4</v>
+        <v>1898.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2102,99 +2102,247 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>20</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>67</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>63300</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>73</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>867.1</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>No/Duda</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66.2</v>
+        <v>63.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -509,17 +509,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63000</v>
+        <v>80000</v>
       </c>
       <c r="E2" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>463.2</v>
+        <v>666.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,17 +553,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.5</v>
+        <v>62.8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85000</v>
+        <v>98000</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
-        <v>658.9</v>
+        <v>490</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63.5</v>
+        <v>62.1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>666.7</v>
+        <v>687.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,26 +722,26 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62.9</v>
+        <v>51.2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95000</v>
+        <v>63000</v>
       </c>
       <c r="E5" t="n">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>323.1</v>
+        <v>463.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,28 +775,28 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.8</v>
+        <v>47.3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -805,17 +805,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98000</v>
+        <v>90000</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>490</v>
+        <v>656.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,26 +870,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62.2</v>
+        <v>46.6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88000</v>
+        <v>120000</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="F7" t="n">
-        <v>888.9</v>
+        <v>800</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,28 +923,28 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.1</v>
+        <v>45.7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,17 +953,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>160</v>
-      </c>
-      <c r="F8" t="n">
-        <v>687.5</v>
+        <v>140000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +1001,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,11 +1022,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53.4</v>
+        <v>45.7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,13 +1035,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>95000</v>
+        <v>55000</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
-        <v>1233.8</v>
+        <v>625</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,17 +1075,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1096,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>51.5</v>
+        <v>45.1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,22 +1109,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>125000</v>
+        <v>70000</v>
       </c>
       <c r="E10" t="n">
         <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>1562.5</v>
+        <v>875</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1140,33 +1144,33 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE Exclusivo departamento de categoría en el prestigioso Barrio Bombal – Godoy Cruz</t>
+          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/20148/ficha/departamento-en-venta-en-arizu-al-278</t>
+          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 125,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48.8</v>
+        <v>44.6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,22 +1183,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>129000</v>
+        <v>53000</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>1131.6</v>
+        <v>757.1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1219,28 +1223,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 9 AMBIENTES EN VENTA - GODOY CRUZ - MENDOZA - 157 M²</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18971/ficha/departamento-en-venta-en-juan-de-garay-400</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 129,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.3</v>
+        <v>44.6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1256,10 +1260,10 @@
         <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>656.9</v>
+        <v>1384.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,17 +1297,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,11 +1318,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47.2</v>
+        <v>43</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1331,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>145000</v>
+        <v>89000</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>1394.2</v>
+        <v>754.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1362,37 +1366,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Departamento de categoría en pleno centro mendocino, Edificio Elipsium</t>
+          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19113/ficha/departamento-en-venta-en-necochea-1400</t>
+          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46.8</v>
+        <v>42.1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>105000</v>
+        <v>87500</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>954.5</v>
+        <v>875</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,32 +1445,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Departamento en venta , Calle Gutierrez, Ciudad de Mendoza . Amoblado.</t>
+          <t>CORDON &amp; ASOCIADOS VENDE</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19925/ficha/departamento-en-venta-en-gutierrez-400</t>
+          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>45.7</v>
+        <v>42</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55000</v>
+        <v>77000</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>625</v>
+        <v>793.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,32 +1519,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45</v>
+        <v>39.2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="F16" t="n">
-        <v>1097.6</v>
+        <v>940.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,32 +1593,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
+          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>44.9</v>
+        <v>38.4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77500</v>
+        <v>95000</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>1174.2</v>
+        <v>1233.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,32 +1667,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>41.9</v>
+        <v>35.3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68000</v>
+        <v>110000</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>708.3</v>
+        <v>1100</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,32 +1741,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>SILVIA NAPOLI CORREDORA PUBLICA MAT 724, vende departamento en Coronel Dorrego, Guaymallén, Mendoza. Ubicación privilegiada.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/251492-silvia-napoli/inmuebles/197/ficha/departamento-en-venta-en-joaquin-v-gonzalez-325</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39.8</v>
+        <v>31.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1775,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>1756.8</v>
+        <v>580</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1790,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,32 +1815,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35.3</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1845,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>110000</v>
+        <v>85000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
-        <v>1100</v>
+        <v>1133.3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,37 +1884,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>33.1</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1919,13 +1923,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63000</v>
+        <v>150000</v>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="F21" t="n">
-        <v>562.5</v>
+        <v>1898.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1954,33 +1958,33 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Oportunidad de inversión!</t>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>31.6</v>
+        <v>28.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1997,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58000</v>
+        <v>90000</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,17 +2037,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2054,7 +2058,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>24.8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>1898.7</v>
+        <v>1866.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2086,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2102,27 +2106,27 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Departamento en Venta – Mendoza Capital</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -2215,13 +2219,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E25" t="n">
         <v>67</v>
       </c>
       <c r="F25" t="n">
-        <v>1119.4</v>
+        <v>1343.3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,17 +2259,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2289,60 +2293,134 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>67</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>63300</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>73</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>867.1</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,17 +513,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80000</v>
+        <v>95000</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F2" t="n">
-        <v>666.7</v>
+        <v>730.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>Casa en venta c/ cochera en 6.ª sección residencial norte</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-seccion-6-residencial-norte-5-ambientes--19590149</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>98000</v>
+        <v>120000</v>
       </c>
       <c r="E3" t="n">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="F3" t="n">
-        <v>490</v>
+        <v>810.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -627,32 +627,32 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>Casa en venta 3 dormitorios – jardín con churrasquera – 2 cocheras – sexta sección</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-sexta-seccion-5-ambientes--20476730</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62.1</v>
+        <v>69</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>110000</v>
+        <v>65000</v>
       </c>
       <c r="E4" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>687.5</v>
+        <v>866.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -701,32 +701,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>Dúplex en venta c/ cochera en godoy cruz</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-godoy-cruz-3-ambientes--19590152</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 65,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51.2</v>
+        <v>65.8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63000</v>
+        <v>65000</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="F5" t="n">
-        <v>463.2</v>
+        <v>601.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,28 +775,28 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>Departamento con terraza y quincho 106m2 ciudad mendoza</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-mendoza-4-ambientes--19928492</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47.3</v>
+        <v>63.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -805,17 +805,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>656.9</v>
+        <v>666.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,26 +870,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>46.6</v>
+        <v>62.9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120000</v>
+        <v>95000</v>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>294</v>
       </c>
       <c r="F7" t="n">
-        <v>800</v>
+        <v>323.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,28 +923,28 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45.7</v>
+        <v>62.9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,21 +953,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>95000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>250</v>
+      </c>
+      <c r="F8" t="n">
+        <v>380</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1001,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Vendo casa en ciudad de mendoza. apta credito hipotecario</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-mendoza-7-ambientes--20386270</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1022,26 +1018,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45.7</v>
+        <v>62.8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55000</v>
+        <v>98000</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>625</v>
+        <v>490</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1050,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1075,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1096,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45.1</v>
+        <v>62.8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1109,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70000</v>
+        <v>98000</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="F10" t="n">
-        <v>875</v>
+        <v>248.1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1124,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1149,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
+          <t>Complejo de 4 unidades. duplex + 3 departamentos a reciclar</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-mendoza-10-ambientes--20608486</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1170,7 +1166,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>44.6</v>
+        <v>62.7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,17 +1175,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53000</v>
+        <v>100000</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="F11" t="n">
-        <v>757.1</v>
+        <v>500</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1198,7 +1194,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1223,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>Hauser vende casa interna</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-quinta-seccion--19148242</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1244,7 +1240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>44.6</v>
+        <v>62.1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,17 +1249,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="F12" t="n">
-        <v>1384.6</v>
+        <v>687.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1297,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1318,26 +1314,26 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>43</v>
+        <v>62.1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>89000</v>
+        <v>110000</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>185</v>
       </c>
       <c r="F13" t="n">
-        <v>754.2</v>
+        <v>594.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1371,47 +1367,47 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
+          <t>Venta - casa en dorrego - 3 dormitorios   estudio / 2 baños</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-coronel-dorrego-7-ambientes--20364060</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>42.1</v>
+        <v>61.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>87500</v>
+        <v>120000</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="F14" t="n">
-        <v>875</v>
+        <v>512.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1445,47 +1441,47 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CORDON &amp; ASOCIADOS VENDE</t>
+          <t>Vendo casa en dorrego</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-coronel-dorrego-4-ambientes--19123113</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>42</v>
+        <v>60.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77000</v>
+        <v>138000</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F15" t="n">
-        <v>793.8</v>
+        <v>1150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1519,56 +1515,56 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
+          <t>Casa en venta c/ cochera en 6.ª sección residencial norte</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-seccion-6-residencial-norte-6-ambientes--19590925</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 138,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39.2</v>
+        <v>58.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>110000</v>
+        <v>138000</v>
       </c>
       <c r="E16" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>940.2</v>
+        <v>985.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1593,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
+          <t>Dúplex en venta c/ cochera en centro</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-mendoza-3-ambientes--19590175</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 138,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>38.4</v>
+        <v>58.1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1627,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>95000</v>
+        <v>87000</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>1233.8</v>
+        <v>580</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1667,32 +1663,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>Depto venta cuarta oeste 3 dorm</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-cuarta-seccion-6-ambientes--17673475</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>35.3</v>
+        <v>55.7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>110000</v>
+        <v>84500</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>1100</v>
+        <v>1056.2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1716,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1741,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento céntrico, calle 9 de julio</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-mendoza-6-ambientes--19595730</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 84,500) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1762,11 +1758,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31.6</v>
+        <v>55.7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1775,22 +1771,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58000</v>
+        <v>148000</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>740</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1810,37 +1806,37 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Departamento en venta c/ cochera en centro</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-mendoza-7-ambientes--19590181</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 148,000 (Requiere contraoferta del 5.7%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>54.1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1849,22 +1845,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>85000</v>
+        <v>99000</v>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F20" t="n">
-        <v>1133.3</v>
+        <v>1020.6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1889,32 +1885,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
+          <t>Depto venta duplex 2 dorm cochera</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-s1-parque-central-3-ambientes--19531214</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 99,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>54.1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1923,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>150000</v>
+        <v>72000</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>1898.7</v>
+        <v>774.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1958,52 +1954,52 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>Venta departamento 3 dormitorios – ciudad de mendoza</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-primera-seccion-5-ambientes--19707482</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 72,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>28.5</v>
+        <v>53.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="F22" t="n">
-        <v>1000</v>
+        <v>322.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2012,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2037,28 +2033,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
+          <t>Vendo casa en dorrego</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-coronel-dorrego-3-ambientes--20431316</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 50,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24.8</v>
+        <v>52.8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2071,17 +2067,17 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>140000</v>
+        <v>75000</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F23" t="n">
-        <v>1866.7</v>
+        <v>961.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2106,52 +2102,52 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>Departamento tipo dúplex en barrio bancario godoy cruz mendoza</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://www.argenprop.com/departamento-en-venta-en-godoy-cruz-5-ambientes--20617012</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20.9</v>
+        <v>51.5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="F24" t="n">
-        <v>888.9</v>
+        <v>681.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2160,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2180,52 +2176,52 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Casa en b° bombal - apta estudio y oficinas - apta credito</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-mendoza-9-ambientes--19928430</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>48.9</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>90000</v>
+        <v>140000</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>1343.3</v>
+        <v>1538.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2234,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2259,28 +2255,28 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+          <t>Duplex frente al dalvian</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-mendoza--18669561</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>48.5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,17 +2285,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75000</v>
+        <v>79000</v>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="F26" t="n">
-        <v>1119.4</v>
+        <v>658.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2308,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2333,17 +2329,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>Casa 500m2 parque hiper libertad</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.argenprop.com/casa-en-venta-en-godoy-cruz-4-ambientes--19742664</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2354,73 +2350,2445 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>76000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>117</v>
+      </c>
+      <c r="F27" t="n">
+        <v>649.6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Vendo casa en barrio san ignacio, godoy cruz</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-villa-hipodromo-4-ambientes--19442483</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>164</v>
+      </c>
+      <c r="F28" t="n">
+        <v>518.3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Casa en venta - 3 dormitorios, 2 baños, amplio jardín y terraza</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-villa-hipodromo-6-ambientes--19928448</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>200</v>
+      </c>
+      <c r="F29" t="n">
+        <v>350</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Casa esquina en 2 planta con salón comercial – godoy cruz</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-villa-hipodromo-6-ambientes--17029440</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>48</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>94900</v>
+      </c>
+      <c r="E30" t="n">
+        <v>170</v>
+      </c>
+      <c r="F30" t="n">
+        <v>558.2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Venta casa en el barrio trapiche de godoy cruz</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-gobernador-benegas-5-ambientes--19957421</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 94,900) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>130</v>
+      </c>
+      <c r="F31" t="n">
+        <v>600</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Departamento en venta en centro</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/departamento-en-venta-en-mendoza-6-ambientes--19590129</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 78,000)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>137</v>
+      </c>
+      <c r="F32" t="n">
+        <v>656.9</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>105</v>
+      </c>
+      <c r="F33" t="n">
+        <v>876.2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>150</v>
+      </c>
+      <c r="F34" t="n">
+        <v>800</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>124000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>166</v>
+      </c>
+      <c r="F35" t="n">
+        <v>747</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Casa en venta en san martín sur, godoy cruz</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-godoy-cruz-5-ambientes--20223446</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 124,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>88</v>
+      </c>
+      <c r="F36" t="n">
+        <v>625</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>53000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>70</v>
+      </c>
+      <c r="F37" t="n">
+        <v>757.1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>116000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>120</v>
+      </c>
+      <c r="F38" t="n">
+        <v>966.7</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO EN VENTA</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/34/ficha/departamento-en-venta-en-sarmiento-290</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 116,000) | 🔥 Red de gas natural confirmada</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>44</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>78</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Vendo departamento en ciudad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/departamento-en-venta-en-mendoza-4-ambientes--20024054</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 78,000)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>43</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>89000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>118</v>
+      </c>
+      <c r="F40" t="n">
+        <v>754.2</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>139000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>86</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1616.3</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Vendo departamento en barrio bombal. apto credito hipotecario.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/departamento-en-venta-en-godoy-cruz-4-ambientes--18838233</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 139,000)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>42</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>97</v>
+      </c>
+      <c r="F42" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>110</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1045.5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>FEMMESTATE VENDE Departamento  en plena Ciudad de Mendoza</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/178/ficha/departamento-en-venta-en-necochea</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Casa en venta – barrio fuchs – godoy cruz – apta crédito hipotecario</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-godoy-cruz-5-ambientes--20067816</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>117</v>
+      </c>
+      <c r="F45" t="n">
+        <v>940.2</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>120</v>
+      </c>
+      <c r="F46" t="n">
+        <v>666.7</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Se ofrece a la venta amplio departamento en planta baja, ubicado en una excelente zona del centro de Mendoza, sobre calle España, entre Godoy Cruz y Barcala.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/287601-garach-gestiones-inmobiliarias/inmuebles/55/ficha/departamento-en-venta-en-espana-1751</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>74000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>211</v>
+      </c>
+      <c r="F47" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Venta de casa con local comercial</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/casa-en-venta-en-godoy-cruz-7-ambientes--18020627</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 74,000)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E48" t="n">
+        <v>75</v>
+      </c>
+      <c r="F48" t="n">
+        <v>906.7</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Departamento En Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 110,000)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>100</v>
+      </c>
+      <c r="F50" t="n">
+        <v>580</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Duplex En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>30</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>79</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1898.7</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>65</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1384.6</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>90</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>83000</v>
+      </c>
+      <c r="E54" t="n">
+        <v>66</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1257.6</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Vendo departamentos y dúplex en lote iv complejo cervantes, godoy cruz</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://www.argenprop.com/departamento-en-venta-en-godoy-cruz-3-ambientes--20157226</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 83,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>75</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1866.7</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Departamento en Venta – Mendoza Capital</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E56" t="n">
+        <v>90</v>
+      </c>
+      <c r="F56" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>20</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D57" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>67</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1343.3</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>20</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>67</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>20</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>63300</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E59" t="n">
         <v>73</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F59" t="n">
         <v>867.1</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61.6</v>
+        <v>66.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,10 +516,10 @@
         <v>120000</v>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
+          <t>Ubicado en el micro-centro de Mendoza, a 2 cuadras de la Plaza Independencia. La unidad pertenece al Edificio Elipsium, uno de los proyectos edilicios de mayor categoría de servicios en la Ciudad.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
+          <t>https://www.inmoclick.com.ar/310969-aureo-propiedades/inmuebles/4/ficha/departamento-en-venta-en-necochea-473</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59.2</v>
+        <v>63.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,26 +583,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116000</v>
+        <v>80000</v>
       </c>
       <c r="E3" t="n">
         <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>966.7</v>
+        <v>666.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,28 +627,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/34/ficha/departamento-en-venta-en-sarmiento-290</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 116,000) | 🔥 Red de gas natural confirmada</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58</v>
+        <v>62.9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F4" t="n">
-        <v>672.7</v>
+        <v>646.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Departamento en Mendoza</t>
+          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/70/ficha/departamento-en-venta-en-departamento-ciudad</t>
+          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 74,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56.3</v>
+        <v>62.8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>115000</v>
+        <v>98000</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>1045.5</v>
+        <v>490</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FEMMESTATE VENDE Departamento  en plena Ciudad de Mendoza</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/178/ficha/departamento-en-venta-en-necochea</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54.2</v>
+        <v>62.1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -805,17 +805,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>110000</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>940.2</v>
+        <v>687.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,11 +870,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53.4</v>
+        <v>51.2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95000</v>
+        <v>63000</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="F7" t="n">
-        <v>1233.8</v>
+        <v>463.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,32 +923,32 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51.2</v>
+        <v>47.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63000</v>
+        <v>90000</v>
       </c>
       <c r="E8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F8" t="n">
-        <v>463.2</v>
+        <v>656.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50.8</v>
+        <v>46.6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68000</v>
+        <v>92000</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>906.7</v>
+        <v>876.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.3</v>
+        <v>46.6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>90000</v>
+        <v>120000</v>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F10" t="n">
-        <v>656.9</v>
+        <v>800</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,22 +1145,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>43.5</v>
+        <v>44.6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90000</v>
+        <v>53000</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>1000</v>
+        <v>757.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1610,11 +1610,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39.8</v>
+        <v>39.2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>140000</v>
+        <v>110000</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
-        <v>1866.7</v>
+        <v>940.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,22 +1663,22 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1758,11 +1758,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90000</v>
+        <v>58000</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>1343.3</v>
+        <v>580</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,28 +1811,28 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31.6</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58000</v>
+        <v>85000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
-        <v>580</v>
+        <v>1133.3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,22 +1880,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>85000</v>
+        <v>90000</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>1133.3</v>
+        <v>1384.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1954,22 +1954,22 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,7 +1980,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>1898.7</v>
+        <v>1000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2028,33 +2028,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Venta - Departamento Apto Airbnb - Green Wave - Financiacion</t>
+          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1835271625-venta-departamento-apto-airbnb-green-wave-financiacion-_JM</t>
+          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29.6</v>
+        <v>24.8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>90000</v>
+        <v>140000</v>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>1384.6</v>
+        <v>1866.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2107,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>Departamento en Venta – Mendoza Capital</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E25" t="n">
         <v>67</v>
       </c>
       <c r="F25" t="n">
-        <v>1119.4</v>
+        <v>1343.3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2289,60 +2289,134 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>67</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>63300</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>73</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>867.1</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,26 +500,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66.2</v>
+        <v>63.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>1200</v>
+        <v>534.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ubicado en el micro-centro de Mendoza, a 2 cuadras de la Plaza Independencia. La unidad pertenece al Edificio Elipsium, uno de los proyectos edilicios de mayor categoría de servicios en la Ciudad.</t>
+          <t>- 🏠 Plantas: 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/310969-aureo-propiedades/inmuebles/4/ficha/departamento-en-venta-en-necochea-473</t>
+          <t>https://www.inmoclick.com.ar/311873-carolina-munoz/inmuebles/1/ficha/casa-en-venta-en-remedios-de-escalada</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.5</v>
+        <v>61.6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F3" t="n">
-        <v>666.7</v>
+        <v>869.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62.9</v>
+        <v>61.1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>130000</v>
       </c>
       <c r="E4" t="n">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="F4" t="n">
-        <v>646.3</v>
+        <v>541.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
+          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
+          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,26 +722,26 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62.8</v>
+        <v>51.2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>98000</v>
+        <v>63000</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>490</v>
+        <v>463.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,47 +775,47 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>OPORTUNIDAD EN PLENO CENTRO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.1</v>
+        <v>50.9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>110000</v>
+        <v>69000</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>687.5</v>
+        <v>627.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,28 +849,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>Amplio departamento en PH ubicado en el Complejo Cerecco Centro Residencial y Comercial compuesto por 4 Torres dispuestas en forma angular confluyendo en un espacio común central.A solo 20 mts de la Plaza Yrigoyen</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/96/ficha/departamento-en-venta-en-ciudad</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>51.2</v>
+        <v>49.5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63000</v>
+        <v>115000</v>
       </c>
       <c r="E7" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F7" t="n">
-        <v>463.2</v>
+        <v>821.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -918,22 +918,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>Departamento de categoría ubicado en calle Mitre, del centro Mendocino.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/86/ficha/departamento-en-venta-en-mitre-1638</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92000</v>
+        <v>120000</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F9" t="n">
-        <v>876.2</v>
+        <v>800</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
+          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
+          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46.6</v>
+        <v>45.7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F10" t="n">
-        <v>800</v>
+        <v>140000</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,22 +1149,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1244,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1257,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53000</v>
+        <v>70000</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>757.1</v>
+        <v>875</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,17 +1297,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,11 +1318,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>43</v>
+        <v>44.6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1331,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>89000</v>
+        <v>53000</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>754.2</v>
+        <v>757.1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,32 +1371,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>42.1</v>
+        <v>44.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>87500</v>
+        <v>90000</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>875</v>
+        <v>1384.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,28 +1445,28 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CORDON &amp; ASOCIADOS VENDE</t>
+          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
+          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77000</v>
+        <v>89000</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
-        <v>793.8</v>
+        <v>754.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,17 +1519,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
+          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
+          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,7 +1540,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>110000</v>
+        <v>87500</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>802.9</v>
+        <v>875</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,17 +1593,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Excelente departamento en planta alta, ubicado sobre calle Videla Correa 321, en una zona consolidada de Ciudad de Mendoza, con muy buenos accesos y cercanía a servicios.</t>
+          <t>CORDON &amp; ASOCIADOS VENDE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/120033-grosso-inmobiliaria/inmuebles/97/ficha/departamento-en-venta-en-videla-correa-321</t>
+          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,7 +1614,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39.2</v>
+        <v>42</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1627,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>110000</v>
+        <v>77000</v>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>940.2</v>
+        <v>793.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,17 +1667,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ZELTA Inmobiliaria Vendo Departamento en Ciudad de Mendoza.</t>
+          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/170/ficha/departamento-en-venta-en-general-paz-135</t>
+          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1684,11 +1688,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>35.3</v>
+        <v>41.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1700,10 +1704,10 @@
         <v>110000</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>1100</v>
+        <v>802.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,28 +1741,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Excelente departamento en planta alta, ubicado sobre calle Videla Correa 321, en una zona consolidada de Ciudad de Mendoza, con muy buenos accesos y cercanía a servicios.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/120033-grosso-inmobiliaria/inmuebles/97/ficha/departamento-en-venta-en-videla-correa-321</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31.6</v>
+        <v>35.8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,22 +1775,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58000</v>
+        <v>68000</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>906.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,32 +1815,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>35.3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1845,13 +1849,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>85000</v>
+        <v>110000</v>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>1133.3</v>
+        <v>1100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,33 +1884,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1923,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>90000</v>
+        <v>58000</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>1384.6</v>
+        <v>580</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1959,17 +1963,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>Duplex En Godoy Cruz</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1980,7 +1984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1997,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F22" t="n">
-        <v>1000</v>
+        <v>1133.3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2028,22 +2032,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
+          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
+          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2054,7 +2058,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24.8</v>
+        <v>30</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2071,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>140000</v>
+        <v>90000</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>1866.7</v>
+        <v>1097.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2086,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,17 +2111,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,7 +2132,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20.9</v>
+        <v>28.5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2145,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80000</v>
+        <v>90000</v>
       </c>
       <c r="E24" t="n">
         <v>90</v>
       </c>
       <c r="F24" t="n">
-        <v>888.9</v>
+        <v>1000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2185,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2206,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>24.8</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2215,13 +2219,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>90000</v>
+        <v>140000</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>1343.3</v>
+        <v>1866.7</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2230,7 +2234,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2255,17 +2259,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+          <t>Departamento en Venta – Mendoza Capital</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2276,7 +2280,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2293,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75000</v>
+        <v>80000</v>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>1119.4</v>
+        <v>888.9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2329,17 +2333,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2363,60 +2367,208 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>67</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1343.3</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>67</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>63300</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E29" t="n">
         <v>73</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>867.1</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,26 +500,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85000</v>
+        <v>105000</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>534.6</v>
+        <v>1141.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,28 +553,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>- 🏠 Plantas: 2</t>
+          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311873-carolina-munoz/inmuebles/1/ficha/casa-en-venta-en-remedios-de-escalada</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61.6</v>
+        <v>63.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E3" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>869.6</v>
+        <v>666.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -648,7 +648,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61.1</v>
+        <v>62.9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>130000</v>
+        <v>95000</v>
       </c>
       <c r="E4" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="F4" t="n">
-        <v>541.7</v>
+        <v>323.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,26 +722,26 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51.2</v>
+        <v>62.9</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63000</v>
+        <v>95000</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F5" t="n">
-        <v>463.2</v>
+        <v>646.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,47 +775,47 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OPORTUNIDAD EN PLENO CENTRO</t>
+          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/102/ficha/departamento-en-venta-en-buenos-aires-n0-258-ciudad</t>
+          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50.9</v>
+        <v>62.8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69000</v>
+        <v>98000</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>627.3</v>
+        <v>490</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,47 +849,47 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Amplio departamento en PH ubicado en el Complejo Cerecco Centro Residencial y Comercial compuesto por 4 Torres dispuestas en forma angular confluyendo en un espacio común central.A solo 20 mts de la Plaza Yrigoyen</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/96/ficha/departamento-en-venta-en-ciudad</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>49.5</v>
+        <v>62.2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>115000</v>
+        <v>88000</v>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>821.4</v>
+        <v>888.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -918,33 +918,33 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Departamento de categoría ubicado en calle Mitre, del centro Mendocino.</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/254044-lorenzo-propiedades/inmuebles/86/ficha/departamento-en-venta-en-mitre-1638</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47.3</v>
+        <v>62.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -953,17 +953,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F8" t="n">
-        <v>656.9</v>
+        <v>687.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>46.6</v>
+        <v>54.9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>120000</v>
+        <v>128000</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>800</v>
+        <v>1662.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>🏢 DEPARTAMENTO EN VENTA – CAPITAL, MENDOZA</t>
+          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/312047-alvarez-asociados/inmuebles/12/ficha/departamento-en-venta-en-olascoaga-n-o-1566-entre-agustin-alvarez-y-avellaneda</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45.7</v>
+        <v>50.9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,17 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>69000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>110</v>
+      </c>
+      <c r="F10" t="n">
+        <v>627.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1149,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Amplio departamento en PH ubicado en el Complejo Cerecco Centro Residencial y Comercial compuesto por 4 Torres dispuestas en forma angular confluyendo en un espacio común central.A solo 20 mts de la Plaza Yrigoyen</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/96/ficha/departamento-en-venta-en-ciudad</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45.7</v>
+        <v>48.1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1183,22 +1179,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55000</v>
+        <v>110000</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>625</v>
+        <v>1208.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1223,28 +1219,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en complejo cerrado sobre calle Huarpes 1945 - Sexta Sección - Ciudad - Mendoza.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/801/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.1</v>
+        <v>47.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1257,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70000</v>
+        <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>875</v>
+        <v>656.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1297,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>📍 En pleno corazón de la ciudad de Mendoza, este amplio departamento amoblado ofrece comodidad y practicidad en una ubicación difícil de igualar. Espacios bien distribuidos que invitan a sentirse en casa desde el primer momento: cocina funcional, estar-comedor acogedor y dos dormitorios que garantizan privacidad. El mobiliario incluido —camas, mesas de luz, comedor y sala con TV— permite mudarse sin preocupaciones, y la opción de alquiler sin muebles brinda flexibilidad según tus necesidades.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311442-plus-valor/inmuebles/2/ficha/departamento-en-venta-en-9-de-julio-1570</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1318,7 +1314,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44.6</v>
+        <v>46.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1331,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53000</v>
+        <v>79000</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F13" t="n">
-        <v>757.1</v>
+        <v>831.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1371,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>OPENHOUSE VENDE – DOS UNIDADES EN UNA, FRENTE A PLAZA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2563/ficha/departamento-en-venta-en-patricias-mendocinas-ciudad</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1392,11 +1388,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44.6</v>
+        <v>45.8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90000</v>
+        <v>76000</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>1384.6</v>
+        <v>1013.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1445,32 +1441,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Departamento ubicado en 5° piso de Avenida Pedro Molina, Segunda sección de Capital.</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/105122-helga-kruls-propiedades/inmuebles/121/ficha/departamento-en-venta-en-pedro-molina-461</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>43</v>
+        <v>45.7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89000</v>
+        <v>55000</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>754.2</v>
+        <v>625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1519,32 +1515,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SIGILO DESARROLLOS INMOBILIARIOS VENDE</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29891-sigilo-desarrollos-inmobiliarios/inmuebles/109/ficha/departamento-en-venta-en-paraguay-y-castelar</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>42.1</v>
+        <v>44.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>87500</v>
+        <v>53000</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>875</v>
+        <v>757.1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1568,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1593,28 +1589,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>CORDON &amp; ASOCIADOS VENDE</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/27015-cordon-asociados/inmuebles/7/ficha/departamento-en-venta-en-san-martin-y-peatonal</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>42</v>
+        <v>44.5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1627,17 +1623,17 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77000</v>
+        <v>150000</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="F17" t="n">
-        <v>793.8</v>
+        <v>852.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1662,33 +1658,33 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>VENTA DE DEPARTAMENTO DE 3 HABITACIONES CON TERRAZA PROPIA A RECICLAR A METROS DE LA PLAZA ITALIA, MENDOZA.</t>
+          <t>Dúplex tipo casa en Quinta Sección</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/310522-ana-lucia-raina-propiedades/inmuebles/9/ficha/departamento-en-venta-en-peru-y-montevideo</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>41.9</v>
+        <v>43.2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>110000</v>
+        <v>75000</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F18" t="n">
-        <v>802.9</v>
+        <v>543.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1741,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Excelente departamento en planta alta, ubicado sobre calle Videla Correa 321, en una zona consolidada de Ciudad de Mendoza, con muy buenos accesos y cercanía a servicios.</t>
+          <t>Amplio, luminoso y cómodo departamento ubicado en el Centro de la Cuidad de Mendoza, a metros de Av. San Martin. rodeado de comercios y galerías como así también de las actividades culturales, educativas y gastronómicas que presenta el centro mendocino. Se encuentra en un quinto piso con balcón a General Paz. cuenta con la siguiente distribución y comodidades, doble ingreso, hall de entrada, living comedor con salida a balcón, dos baños, tres dormitorios con amplísimos placares, cocina comedor, lavandería y dependencia de servicio. la propiedad se ofrece con cochera para un auto en Galería Bamac, con entrada por calle Buenos Aires.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/120033-grosso-inmobiliaria/inmuebles/97/ficha/departamento-en-venta-en-videla-correa-321</t>
+          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/402/ficha/departamento-en-venta-en-general-paz-n0-65</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1762,7 +1758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35.8</v>
+        <v>40.2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1775,22 +1771,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>68000</v>
+        <v>90000</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>906.7</v>
+        <v>796.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1815,32 +1811,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35.3</v>
+        <v>40</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1849,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>110000</v>
+        <v>145000</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>1100</v>
+        <v>2071.4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1884,33 +1880,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31.6</v>
+        <v>40</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1923,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58000</v>
+        <v>145000</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
-        <v>580</v>
+        <v>2071.4</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1958,33 +1954,33 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Duplex En Godoy Cruz</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3846544412-duplex-en-godoy-cruz-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>35.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1997,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85000</v>
+        <v>132000</v>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F22" t="n">
-        <v>1133.3</v>
+        <v>1670.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2012,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2032,22 +2028,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>🏡 ¡Viví en una de las zonas más buscadas de Ciudad! 📍 Paso de los Andes N° 570, a 100 metros de Arístides de Villanueva, Ciudad</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado sobre calle Paso de Los Andes 940 - Quinta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/133635-di-luca-propiedades/inmuebles/98/ficha/departamento-en-venta-en-paso-de-los-andes-n0-570-ciudad</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/742/ficha/departamento-en-venta-en-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 132,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2058,11 +2054,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>35.3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2071,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>1097.6</v>
+        <v>1100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2111,28 +2107,28 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28.5</v>
+        <v>32.5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2145,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="F24" t="n">
-        <v>1000</v>
+        <v>675.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2185,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>#Oportunidad de Inversión – Zona Poder Judicial#</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308921-femmestate/inmuebles/133/ficha/departamento-en-venta-en-p-molina-y-mitre</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2206,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24.8</v>
+        <v>31.4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2219,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>140000</v>
+        <v>88000</v>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>1866.7</v>
+        <v>967</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2259,17 +2255,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>Ubicado en una de las zonas más lindas del centro de Mendoza.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/780/ficha/departamento-en-venta-en-gutierrez-al-400</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2280,7 +2276,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20.9</v>
+        <v>30.7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2293,13 +2289,17 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>90</v>
-      </c>
-      <c r="F26" t="n">
-        <v>888.9</v>
+        <v>140000</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>30.5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>90000</v>
+        <v>135000</v>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="F27" t="n">
-        <v>1343.3</v>
+        <v>1097.6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>¡Departamento remodelado frente a Plaza España! – 9 de Julio, Planta Baja</t>
+          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/8993-lombardo-propiedades/inmuebles/136/ficha/departamento-en-venta-en-espana-esq-san-lorenzo</t>
+          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 90,000)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2428,7 +2428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20</v>
+        <v>30.4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75000</v>
+        <v>92000</v>
       </c>
       <c r="E28" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F28" t="n">
-        <v>1119.4</v>
+        <v>1295.8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>INMOBILIARIA TRE VENDE  esta excelente oportunidad de inversión o vivienda permanente en una de las zonas residenciales más consolidadas de la Ciudad. Ubicado en primer piso por escalera, la propiedad destaca por su amplitud y funcionalidad.Distribución y Características:</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/782/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 92,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2502,73 +2502,369 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>81000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1051.9</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>74</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1756.8</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>90</v>
+      </c>
+      <c r="F31" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>20</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D32" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>67</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>20</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>63300</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E33" t="n">
         <v>73</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F33" t="n">
         <v>867.1</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>No/Duda</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>105000</v>
+        <v>89999</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>1141.3</v>
+        <v>818.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,47 +553,47 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
+          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80000</v>
+        <v>105000</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>666.7</v>
+        <v>1141.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,28 +627,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95000</v>
+        <v>85000</v>
       </c>
       <c r="E4" t="n">
-        <v>294</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>323.1</v>
+        <v>702.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95000</v>
+        <v>38000</v>
       </c>
       <c r="E5" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>646.3</v>
+        <v>271.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
+          <t>Casa en venta , Cuarta Sección , Ciudad de Mendoza , en obra .</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19076/ficha/casa-en-venta-en-villagra-francisco-3200</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 38,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.8</v>
+        <v>61.6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98000</v>
+        <v>120000</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="F6" t="n">
-        <v>490</v>
+        <v>869.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88000</v>
+        <v>120000</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
-        <v>888.9</v>
+        <v>810.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>Dueño vende .</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/19594-yanet-biluron/inmuebles/3/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.1</v>
+        <v>61</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,17 +957,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
+        <v>147999</v>
       </c>
       <c r="E8" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="F8" t="n">
-        <v>687.5</v>
+        <v>1049.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -992,56 +992,56 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>DUEÑA VENDE CASA EN DORREGO, inmejorable Ubicación: Juan B. Justo 1059, a un paso de Acceso Sur, Costanera y Paseo Dorrego. ¡Ideal para tener la vida resuelta y moverte rápido a todos lados</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/24080-dueno-vende/inmuebles/6/ficha/casa-en-venta-en-juan-b-justo-1059-guaymallen</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 147,999 (Requiere contraoferta del 5.7%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54.9</v>
+        <v>60.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>128000</v>
+        <v>140000</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="F9" t="n">
-        <v>1662.3</v>
+        <v>544.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
+          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
+          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.9</v>
+        <v>55.8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69000</v>
+        <v>65000</v>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F10" t="n">
-        <v>627.3</v>
+        <v>601.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Amplio departamento en PH ubicado en el Complejo Cerecco Centro Residencial y Comercial compuesto por 4 Torres dispuestas en forma angular confluyendo en un espacio común central.A solo 20 mts de la Plaza Yrigoyen</t>
+          <t>Departamento Dúplex de 2 Dormitorios con Terraza y Quincho Propio en Ciudad de Mendoza | Sin Expensas</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/96/ficha/departamento-en-venta-en-ciudad</t>
+          <t>https://www.inmoclick.com.ar/305394-mosaico-propiedades/inmuebles/286/ficha/departamento-en-venta-en-don-bosco-al-281-mendoza</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 65,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48.1</v>
+        <v>54.9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110000</v>
+        <v>128000</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>1208.8</v>
+        <v>1662.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,28 +1219,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en complejo cerrado sobre calle Huarpes 1945 - Sexta Sección - Ciudad - Mendoza.</t>
+          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/801/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.3</v>
+        <v>53.4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>656.9</v>
+        <v>1233.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,7 +1314,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>46.3</v>
+        <v>50.8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79000</v>
+        <v>68000</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>831.6</v>
+        <v>906.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,32 +1367,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE – DOS UNIDADES EN UNA, FRENTE A PLAZA INDEPENDENCIA</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2563/ficha/departamento-en-venta-en-patricias-mendocinas-ciudad</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 79,000)</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76000</v>
+        <v>120000</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>1013.3</v>
+        <v>1558.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,32 +1441,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>45.7</v>
+        <v>47.3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="F15" t="n">
-        <v>625</v>
+        <v>656.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,11 +1536,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44.6</v>
+        <v>45.8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53000</v>
+        <v>76000</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>757.1</v>
+        <v>1013.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>150000</v>
+        <v>55000</v>
       </c>
       <c r="E17" t="n">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>852.3</v>
+        <v>625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1658,37 +1658,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dúplex tipo casa en Quinta Sección</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E18" t="n">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
-        <v>543.5</v>
+        <v>1097.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Amplio, luminoso y cómodo departamento ubicado en el Centro de la Cuidad de Mendoza, a metros de Av. San Martin. rodeado de comercios y galerías como así también de las actividades culturales, educativas y gastronómicas que presenta el centro mendocino. Se encuentra en un quinto piso con balcón a General Paz. cuenta con la siguiente distribución y comodidades, doble ingreso, hall de entrada, living comedor con salida a balcón, dos baños, tres dormitorios con amplísimos placares, cocina comedor, lavandería y dependencia de servicio. la propiedad se ofrece con cochera para un auto en Galería Bamac, con entrada por calle Buenos Aires.</t>
+          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/402/ficha/departamento-en-venta-en-general-paz-n0-65</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40.2</v>
+        <v>44.5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,22 +1771,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="E19" t="n">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="F19" t="n">
-        <v>796.5</v>
+        <v>852.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1806,33 +1806,33 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
+          <t>Dúplex tipo casa en Quinta Sección</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40</v>
+        <v>43.2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>145000</v>
+        <v>75000</v>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="F20" t="n">
-        <v>2071.4</v>
+        <v>543.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1880,33 +1880,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Amplio, luminoso y cómodo departamento ubicado en el Centro de la Cuidad de Mendoza, a metros de Av. San Martin. rodeado de comercios y galerías como así también de las actividades culturales, educativas y gastronómicas que presenta el centro mendocino. Se encuentra en un quinto piso con balcón a General Paz. cuenta con la siguiente distribución y comodidades, doble ingreso, hall de entrada, living comedor con salida a balcón, dos baños, tres dormitorios con amplísimos placares, cocina comedor, lavandería y dependencia de servicio. la propiedad se ofrece con cochera para un auto en Galería Bamac, con entrada por calle Buenos Aires.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/402/ficha/departamento-en-venta-en-general-paz-n0-65</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>145000</v>
+        <v>85000</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="F21" t="n">
-        <v>2071.4</v>
+        <v>841.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1954,33 +1954,33 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>SE VENDE DEPARTAMENTO | RECICLADO A NUEVO | EN PLENO CENTRO DE MENDOZA.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/356/ficha/departamento-en-venta-en-9-de-julio-1050</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>35.5</v>
+        <v>40.5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>132000</v>
+        <v>135000</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="F22" t="n">
-        <v>1670.9</v>
+        <v>592.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,17 +2033,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado sobre calle Paso de Los Andes 940 - Quinta Sección - Mendoza.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/742/ficha/departamento-en-venta-en-quinta-seccion-mendoza</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1485/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 132,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2054,11 +2054,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.3</v>
+        <v>40.5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>228</v>
       </c>
       <c r="F23" t="n">
-        <v>1100</v>
+        <v>592.1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,28 +2107,28 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1565/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>32.5</v>
+        <v>40.2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E24" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F24" t="n">
-        <v>675.7</v>
+        <v>796.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31.4</v>
+        <v>40</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>88000</v>
+        <v>145000</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>967</v>
+        <v>2071.4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2250,33 +2250,33 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Ubicado en una de las zonas más lindas del centro de Mendoza.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/780/ficha/departamento-en-venta-en-gutierrez-al-400</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30.7</v>
+        <v>40</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,17 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>145000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2071.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2308,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2328,37 +2324,37 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30.5</v>
+        <v>35.3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2367,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E27" t="n">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>1097.6</v>
+        <v>1100</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2382,7 +2378,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2407,32 +2403,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30.4</v>
+        <v>33.1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2441,13 +2437,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>92000</v>
+        <v>63000</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="F28" t="n">
-        <v>1295.8</v>
+        <v>562.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2481,17 +2477,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>INMOBILIARIA TRE VENDE  esta excelente oportunidad de inversión o vivienda permanente en una de las zonas residenciales más consolidadas de la Ciudad. Ubicado en primer piso por escalera, la propiedad destaca por su amplitud y funcionalidad.Distribución y Características:</t>
+          <t>Oportunidad de inversión!</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/782/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 92,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2502,7 +2498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>32.8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2515,13 +2511,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>81000</v>
+        <v>65000</v>
       </c>
       <c r="E29" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F29" t="n">
-        <v>1051.9</v>
+        <v>915.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2550,22 +2546,22 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2576,7 +2572,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24.8</v>
+        <v>32.5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2589,13 +2585,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>130000</v>
+        <v>75000</v>
       </c>
       <c r="E30" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="F30" t="n">
-        <v>1756.8</v>
+        <v>675.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2604,7 +2600,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2629,17 +2625,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2650,7 +2646,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20.9</v>
+        <v>30.5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2663,13 +2659,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80000</v>
+        <v>135000</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F31" t="n">
-        <v>888.9</v>
+        <v>1097.6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2678,7 +2674,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2703,17 +2699,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2724,7 +2720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2737,13 +2733,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>75000</v>
+        <v>81000</v>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F32" t="n">
-        <v>1119.4</v>
+        <v>1051.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2772,22 +2768,22 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2798,73 +2794,221 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>90</v>
+      </c>
+      <c r="F33" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>20</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D34" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>67</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>63300</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E35" t="n">
         <v>73</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F35" t="n">
         <v>867.1</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>No/Duda</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38000</v>
+        <v>85000</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="F5" t="n">
-        <v>271.4</v>
+        <v>534.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Casa en venta , Cuarta Sección , Ciudad de Mendoza , en obra .</t>
+          <t>- 🏠 Plantas: 2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19076/ficha/casa-en-venta-en-villagra-francisco-3200</t>
+          <t>https://www.inmoclick.com.ar/311873-carolina-munoz/inmuebles/1/ficha/casa-en-venta-en-remedios-de-escalada</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 38,000) | 🚗 Cuenta con cochera | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,17 +957,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>147999</v>
+        <v>130000</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>1049.6</v>
+        <v>541.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -992,33 +992,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DUEÑA VENDE CASA EN DORREGO, inmejorable Ubicación: Juan B. Justo 1059, a un paso de Acceso Sur, Costanera y Paseo Dorrego. ¡Ideal para tener la vida resuelta y moverte rápido a todos lados</t>
+          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/24080-dueno-vende/inmuebles/6/ficha/casa-en-venta-en-juan-b-justo-1059-guaymallen</t>
+          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Publicado en USD 147,999 (Requiere contraoferta del 5.7%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60.5</v>
+        <v>55.8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1027,17 +1027,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>140000</v>
+        <v>65000</v>
       </c>
       <c r="E9" t="n">
-        <v>257</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>544.7</v>
+        <v>601.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CASANOVA NEGOCIOS INMOBILIARIOS</t>
+          <t>Departamento Dúplex de 2 Dormitorios con Terraza y Quincho Propio en Ciudad de Mendoza | Sin Expensas</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/303761-casanova-negocios-inmobiliarios/inmuebles/2/ficha/casa-en-venta-en-jose-federico-moreno-1400</t>
+          <t>https://www.inmoclick.com.ar/305394-mosaico-propiedades/inmuebles/286/ficha/departamento-en-venta-en-don-bosco-al-281-mendoza</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 65,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,11 +1092,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55.8</v>
+        <v>54.9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,17 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65000</v>
+        <v>128000</v>
       </c>
       <c r="E10" t="n">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>601.9</v>
+        <v>1662.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Departamento Dúplex de 2 Dormitorios con Terraza y Quincho Propio en Ciudad de Mendoza | Sin Expensas</t>
+          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/305394-mosaico-propiedades/inmuebles/286/ficha/departamento-en-venta-en-don-bosco-al-281-mendoza</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 65,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54.9</v>
+        <v>53.4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,17 +1179,17 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>128000</v>
+        <v>95000</v>
       </c>
       <c r="E11" t="n">
         <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>1662.3</v>
+        <v>1233.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1219,28 +1219,28 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
+          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
+          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53.4</v>
+        <v>50.8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,17 +1253,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>95000</v>
+        <v>68000</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>1233.8</v>
+        <v>906.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,17 +1327,17 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68000</v>
+        <v>120000</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>906.7</v>
+        <v>1558.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1367,28 +1367,28 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>1558.4</v>
+        <v>1000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1684,7 +1684,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90000</v>
+        <v>77500</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>1097.6</v>
+        <v>1174.2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Vendo Departamento en Ciudad de Mendoza. 82 mtrs terreno total. La propiedad cuenta con cocina comedor, living, 3 habitaciones, placares, 2 baños, aire acondicionado, calefactores. Los principales ventanales dan a la cordillera. En pleno centro de Mendoza. Se evalúan ofertas. Zelta Inmobiliaria</t>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/95/ficha/departamento-en-venta-en-catamarca-35</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>43.2</v>
+        <v>40.2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E20" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="F20" t="n">
-        <v>543.5</v>
+        <v>796.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Amplio, luminoso y cómodo departamento ubicado en el Centro de la Cuidad de Mendoza, a metros de Av. San Martin. rodeado de comercios y galerías como así también de las actividades culturales, educativas y gastronómicas que presenta el centro mendocino. Se encuentra en un quinto piso con balcón a General Paz. cuenta con la siguiente distribución y comodidades, doble ingreso, hall de entrada, living comedor con salida a balcón, dos baños, tres dormitorios con amplísimos placares, cocina comedor, lavandería y dependencia de servicio. la propiedad se ofrece con cochera para un auto en Galería Bamac, con entrada por calle Buenos Aires.</t>
+          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/402/ficha/departamento-en-venta-en-general-paz-n0-65</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>85000</v>
+        <v>145000</v>
       </c>
       <c r="E21" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
-        <v>841.6</v>
+        <v>2071.4</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1954,33 +1954,33 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>SE VENDE DEPARTAMENTO | RECICLADO A NUEVO | EN PLENO CENTRO DE MENDOZA.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/356/ficha/departamento-en-venta-en-9-de-julio-1050</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>135000</v>
+        <v>145000</v>
       </c>
       <c r="E22" t="n">
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>592.1</v>
+        <v>2071.4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2028,37 +2028,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1485/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40.5</v>
+        <v>35.3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E23" t="n">
-        <v>228</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>592.1</v>
+        <v>1100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,28 +2107,28 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1565/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>40.2</v>
+        <v>32.8</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>90000</v>
+        <v>65000</v>
       </c>
       <c r="E24" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>796.5</v>
+        <v>915.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>145000</v>
+        <v>75000</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="F25" t="n">
-        <v>2071.4</v>
+        <v>675.7</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2250,33 +2250,33 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40</v>
+        <v>30.5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>145000</v>
+        <v>135000</v>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="F26" t="n">
-        <v>2071.4</v>
+        <v>1097.6</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2324,37 +2324,37 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35.3</v>
+        <v>30</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>110000</v>
+        <v>81000</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F27" t="n">
-        <v>1100</v>
+        <v>1051.9</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2398,37 +2398,37 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33.1</v>
+        <v>20.9</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63000</v>
+        <v>80000</v>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="F28" t="n">
-        <v>562.5</v>
+        <v>888.9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Oportunidad de inversión!</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/259304-bcg-desarrollos-inmobiliarios/inmuebles/28/ficha/departamento-en-venta-en-pte-derqui-243</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 63,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>32.8</v>
+        <v>20</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F29" t="n">
-        <v>915.5</v>
+        <v>1119.4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2551,17 +2551,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2572,7 +2572,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32.5</v>
+        <v>20</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75000</v>
+        <v>63300</v>
       </c>
       <c r="E30" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="F30" t="n">
-        <v>675.7</v>
+        <v>867.1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2625,390 +2625,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>135000</v>
-      </c>
-      <c r="E31" t="n">
-        <v>123</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1097.6</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>81000</v>
-      </c>
-      <c r="E32" t="n">
-        <v>77</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1051.9</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E33" t="n">
-        <v>90</v>
-      </c>
-      <c r="F33" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>20</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>67</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>73</v>
-      </c>
-      <c r="F35" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,17 +513,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>89999</v>
+        <v>145000</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>818.2</v>
+        <v>2071.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -548,33 +548,33 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
+          <t>GALEA PROPIEDADES Ofrece a la venta Departamento en Edificio Bombal Nuevo, ubicado en calle Echeverría, Barrio Bombal de Godoy Cruz.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/813/ficha/departamento-en-venta-en-calle-echeverria-al-1600</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>105000</v>
+        <v>145000</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>1141.3</v>
+        <v>2071.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
+          <t>GALEA PROPIEDADES Ofrece a la venta Departamento en Edificio Bombal Nuevo, ubicado en calle Echeverría, Barrio Bombal de Godoy Cruz.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
+          <t>https://www.inmoclick.com.ar/74830-galea-propiedades/inmuebles/524/ficha/departamento-en-venta-en-echeverria-al-1600</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%)</t>
         </is>
       </c>
     </row>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85000</v>
+        <v>58000</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="F4" t="n">
-        <v>702.5</v>
+        <v>355.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
+          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
+          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -738,10 +738,10 @@
         <v>85000</v>
       </c>
       <c r="E5" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="F5" t="n">
-        <v>534.6</v>
+        <v>658.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>- 🏠 Plantas: 2</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311873-carolina-munoz/inmuebles/1/ficha/casa-en-venta-en-remedios-de-escalada</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61.6</v>
+        <v>62.9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>120000</v>
+        <v>95000</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="F6" t="n">
-        <v>869.6</v>
+        <v>323.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61.6</v>
+        <v>62.9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120000</v>
+        <v>95000</v>
       </c>
       <c r="E7" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F7" t="n">
-        <v>810.8</v>
+        <v>646.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dueño vende .</t>
+          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/19594-yanet-biluron/inmuebles/3/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61.1</v>
+        <v>62.1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>130000</v>
+        <v>110000</v>
       </c>
       <c r="E8" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="F8" t="n">
-        <v>541.7</v>
+        <v>687.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55.8</v>
+        <v>61.2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1027,17 +1027,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65000</v>
+        <v>128000</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="F9" t="n">
-        <v>601.9</v>
+        <v>984.6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Departamento Dúplex de 2 Dormitorios con Terraza y Quincho Propio en Ciudad de Mendoza | Sin Expensas</t>
+          <t>OPENHOUSE VENDE CASA EN SEXTA SECCIÓN – CIUDAD DE MENDOZA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/305394-mosaico-propiedades/inmuebles/286/ficha/departamento-en-venta-en-don-bosco-al-281-mendoza</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2693/ficha/casa-en-venta-en-ferroviarios-argentinos</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 65,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54.9</v>
+        <v>50.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>128000</v>
+        <v>95000</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>1662.3</v>
+        <v>871.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53.4</v>
+        <v>48.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,17 +1179,17 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>95000</v>
+        <v>89000</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="F11" t="n">
-        <v>1233.8</v>
+        <v>816.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Departamento ubicado en una zona estratégica, a poca distancia de Plaza Independencia: una propuesta ideal para quienes buscan comodidad y funcionalidad en el centro. Se trata de un 1° piso frontal que ofrece ambientes bien distribuidos y posibilidades para adaptarlo según tus necesidades.</t>
+          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/11968-inmobiliaria-miguel-angel-juan-pablo-simon/inmuebles/51/ficha/departamento-en-venta-en-gutierrez-434</t>
+          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 89,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>50.8</v>
+        <v>48.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,17 +1253,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>68000</v>
+        <v>130000</v>
       </c>
       <c r="E12" t="n">
         <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>906.7</v>
+        <v>1733.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1293,32 +1293,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>1558.4</v>
+        <v>1733.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
+          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
+          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>49.9</v>
+        <v>47.3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70000</v>
+        <v>90000</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="F14" t="n">
-        <v>1000</v>
+        <v>656.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1478,10 +1478,10 @@
         <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>656.9</v>
+        <v>900</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,32 +1515,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>ADOBE INMOBILIARIA VENDE  DÚPLEX EN GODOY CRUZ</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/403/ficha/departamento-en-venta-en-perito-moreno-al-500</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45.8</v>
+        <v>46.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76000</v>
+        <v>92000</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F16" t="n">
-        <v>1013.3</v>
+        <v>876.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,22 +1589,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
+          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>44.9</v>
+        <v>44.6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77500</v>
+        <v>53000</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>1174.2</v>
+        <v>757.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>44.5</v>
+        <v>43.1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,17 +1771,17 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="E19" t="n">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>852.3</v>
+        <v>1000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1806,33 +1806,33 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Dúplex tipo casa en Quinta Sección</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>90000</v>
+        <v>145000</v>
       </c>
       <c r="E20" t="n">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>796.5</v>
+        <v>2071.4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1980,11 +1980,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40</v>
+        <v>35.3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>145000</v>
+        <v>110000</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>2071.4</v>
+        <v>1100</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2028,37 +2028,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.3</v>
+        <v>29.5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>110000</v>
+        <v>85000</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>1100</v>
+        <v>1231.9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,28 +2107,28 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>32.8</v>
+        <v>20.9</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65000</v>
+        <v>80000</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F24" t="n">
-        <v>915.5</v>
+        <v>888.9</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>32.5</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         <v>75000</v>
       </c>
       <c r="E25" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="F25" t="n">
-        <v>675.7</v>
+        <v>1119.4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2276,7 +2276,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30.5</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>135000</v>
+        <v>63300</v>
       </c>
       <c r="E26" t="n">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
-        <v>1097.6</v>
+        <v>867.1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2329,316 +2329,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>30</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>81000</v>
-      </c>
-      <c r="E27" t="n">
-        <v>77</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1051.9</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E28" t="n">
-        <v>90</v>
-      </c>
-      <c r="F28" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E29" t="n">
-        <v>67</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E30" t="n">
-        <v>73</v>
-      </c>
-      <c r="F30" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,17 +513,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>145000</v>
+        <v>89999</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>2071.4</v>
+        <v>818.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -548,33 +548,33 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GALEA PROPIEDADES Ofrece a la venta Departamento en Edificio Bombal Nuevo, ubicado en calle Echeverría, Barrio Bombal de Godoy Cruz.</t>
+          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/813/ficha/departamento-en-venta-en-calle-echeverria-al-1600</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%)</t>
+          <t>Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>145000</v>
+        <v>105000</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>2071.4</v>
+        <v>1141.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>GALEA PROPIEDADES Ofrece a la venta Departamento en Edificio Bombal Nuevo, ubicado en calle Echeverría, Barrio Bombal de Godoy Cruz.</t>
+          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/74830-galea-propiedades/inmuebles/524/ficha/departamento-en-venta-en-echeverria-al-1600</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95000</v>
+        <v>80000</v>
       </c>
       <c r="E6" t="n">
-        <v>294</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>323.1</v>
+        <v>666.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.1</v>
+        <v>62.8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
+        <v>98000</v>
       </c>
       <c r="E8" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="F8" t="n">
-        <v>687.5</v>
+        <v>490</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>CASA EN VENTA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61.2</v>
+        <v>62.2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>128000</v>
+        <v>88000</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>984.6</v>
+        <v>888.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE CASA EN SEXTA SECCIÓN – CIUDAD DE MENDOZA</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2693/ficha/casa-en-venta-en-ferroviarios-argentinos</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 128,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.3</v>
+        <v>54.9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95000</v>
+        <v>128000</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>871.6</v>
+        <v>1662.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>89000</v>
+        <v>68000</v>
       </c>
       <c r="E11" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>816.5</v>
+        <v>906.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ADOBE INMOBILIARIA VENDE EXCELENTE DÚPLEX EN CALLE TOMBA, GODOY CRUZ</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/318/ficha/departamento-en-venta-en-tomba-35</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 89,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>130000</v>
+        <v>95000</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F12" t="n">
-        <v>1733.3</v>
+        <v>871.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,32 +1293,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3601/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48.3</v>
+        <v>50.2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>130000</v>
+        <v>45000</v>
       </c>
       <c r="E13" t="n">
         <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>1733.3</v>
+        <v>600</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>"CARINA DROZD gestiones inmobiliarias" VENDE: DEPARTAMENTOS Ubicadísimos: Calle ALMIRANTE BROWN, B° BOMBAL SUR. Complejo de 7 deptos con cocheras subterráneas. ASCENSOR. Piso 1 y Piso 2. FRONTALES!. Constan de: COCINA LIVING COMEDOR con Equipo A.A. y Calefactor; cocina con extractor, alacenas, bajomesada, Barra Desayunador- 2 DORMITORIOS (1 con A.A.) con Placares y Calefactores- 2 BAÑOS (uno en SUITE)- Recién Pintados! BALCON- PATIO LAVANDERÍA con bacha y mueble- COCHERA AUTOMATIZADA, en Subsuelo. VALORES: U$S 115.000 sin cochera en Piso 1- U$S 130.000 con Cochera en Piso 2. ESCRITURACION Inmediata. ALQUILADOS con Excelentes Rentas, pero se desocupan si lo desea el comprador-</t>
+          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1406-carina-drozd-gestiones-inmobiliarias/inmuebles/3522/ficha/departamento-en-venta-en-almirante-brown-1524</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.2</v>
+        <v>45.8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90000</v>
+        <v>76000</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>900</v>
+        <v>1013.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ADOBE INMOBILIARIA VENDE  DÚPLEX EN GODOY CRUZ</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276954-adobe-inmobiliaria-y-desarrollos/inmuebles/403/ficha/departamento-en-venta-en-perito-moreno-al-500</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1536,11 +1536,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46.6</v>
+        <v>45.7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>92000</v>
+        <v>55000</v>
       </c>
       <c r="E16" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>876.2</v>
+        <v>625</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>RE/MAX Follow presenta departamento en venta en Ciudad de Mendoza</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2549/ficha/departamento-en-venta-en-avenida-san-martin-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 92,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1610,11 +1610,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45.7</v>
+        <v>44.5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55000</v>
+        <v>150000</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F17" t="n">
-        <v>625</v>
+        <v>852.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1658,37 +1658,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Dúplex tipo casa en Quinta Sección</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>44.6</v>
+        <v>40.2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53000</v>
+        <v>90000</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="F18" t="n">
-        <v>757.1</v>
+        <v>796.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1737,28 +1737,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Planta baja confortable y funcional en excelente zona de Dorrego, entre las calles Laprida y Cobos, adyacencias calle Lamadrid, ideal para quienes buscan comodidad, privacidad y ubicación estratégica. Un hogar pensado para el día a día: living comedor para recibir visitas, cocina comedor práctica para las comidas diarias y una lavandería independiente que facilita las tareas del hogar. Tres dormitorios bien distribuidos: dos con placares y un tercero en suite con su propio placard, que ofrece mayor privacidad y confort.</t>
+          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/308706-cm/inmuebles/6/ficha/departamento-en-venta-en-laprida-y-cobos</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>43.1</v>
+        <v>40</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75000</v>
+        <v>145000</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>1000</v>
+        <v>2071.4</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1806,27 +1806,27 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en Torres San Vicente sobre calle San Martín Sur 499 frente calle Leguizamón - Godoy Cruz - Mendoza.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/754/ficha/departamento-en-venta-en-torres-san-vicente-godoy-cruz-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1906,11 +1906,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>40</v>
+        <v>35.3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>145000</v>
+        <v>110000</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>2071.4</v>
+        <v>1100</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1954,37 +1954,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>35.3</v>
+        <v>32.8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>110000</v>
+        <v>65000</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>1100</v>
+        <v>915.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2033,28 +2033,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29.5</v>
+        <v>32.5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
-        <v>1231.9</v>
+        <v>675.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>| VENTA | DUPLEX | GODOY CRUZ | 2 DORMITORIOS | COMPEJO CERRADO CON COCHERA</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/424/ficha/departamento-en-venta-en-f-sanchez-al-300</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20.9</v>
+        <v>30.5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80000</v>
+        <v>135000</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
-        <v>888.9</v>
+        <v>1097.6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75000</v>
+        <v>81000</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F25" t="n">
-        <v>1119.4</v>
+        <v>1051.9</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2250,22 +2250,22 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2276,73 +2276,221 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>90</v>
+      </c>
+      <c r="F26" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>20</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>67</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>63300</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>73</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>867.1</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>No/Duda</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>89999</v>
+        <v>85000</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>818.2</v>
+        <v>702.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,47 +553,47 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
+          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>105000</v>
+        <v>58000</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="F3" t="n">
-        <v>1141.3</v>
+        <v>355.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
+          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
+          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58000</v>
+        <v>85000</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="F4" t="n">
-        <v>355.8</v>
+        <v>658.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85000</v>
+        <v>80000</v>
       </c>
       <c r="E5" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>658.9</v>
+        <v>666.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63.5</v>
+        <v>62.9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80000</v>
+        <v>95000</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>294</v>
       </c>
       <c r="F6" t="n">
-        <v>666.7</v>
+        <v>323.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1092,30 +1092,30 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54.9</v>
+        <v>62.1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>128000</v>
+        <v>110000</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>1662.3</v>
+        <v>687.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50.8</v>
+        <v>56</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,17 +1179,17 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68000</v>
+        <v>150000</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="F11" t="n">
-        <v>906.7</v>
+        <v>1515.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1214,33 +1214,33 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>RE/MAX Ofrece a la Venta departamento a metros de calle Emilio Civit, la calle más linda de Mendoza y a 5 minutos caminando del Parque General San Martín. Pensado para vivir cómodo todo el año, en un edificio con Amenities completos y seguridad las 24 horas.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19860/ficha/departamento-en-venta-en-coronel-rodriguez-1000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>95000</v>
+        <v>45000</v>
       </c>
       <c r="E12" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>871.6</v>
+        <v>600</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45000</v>
+        <v>120000</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>600</v>
+        <v>1558.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>47.3</v>
+        <v>49.9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90000</v>
+        <v>70000</v>
       </c>
       <c r="E14" t="n">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>656.9</v>
+        <v>1000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>45.8</v>
+        <v>47.3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76000</v>
+        <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="F15" t="n">
-        <v>1013.3</v>
+        <v>656.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en calle España y Bogado, Torre 3, Cereco II, Ciudad, Mendoza.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/726/ficha/departamento-en-venta-en-espana-2870-ciudad-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 76,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -1610,11 +1610,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>150000</v>
+        <v>77500</v>
       </c>
       <c r="E17" t="n">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>852.3</v>
+        <v>1174.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1658,33 +1658,33 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dúplex tipo casa en Quinta Sección</t>
+          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
+          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40.2</v>
+        <v>44.5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,22 +1697,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="E18" t="n">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="F18" t="n">
-        <v>796.5</v>
+        <v>852.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1732,33 +1732,33 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
+          <t>Dúplex tipo casa en Quinta Sección</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40</v>
+        <v>43.4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>145000</v>
+        <v>144400</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="F19" t="n">
-        <v>2071.4</v>
+        <v>1110.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1906,11 +1906,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>35.3</v>
+        <v>40</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>110000</v>
+        <v>145000</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
-        <v>1100</v>
+        <v>2071.4</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1954,37 +1954,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>32.8</v>
+        <v>39.8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65000</v>
+        <v>140000</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F22" t="n">
-        <v>915.5</v>
+        <v>1866.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2033,28 +2033,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
+          <t>Departamento en Venta – Mendoza Capital</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
+          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>32.5</v>
+        <v>38.5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="E23" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="F23" t="n">
-        <v>675.7</v>
+        <v>322.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>ZELTA Inmobiliaria Vende Casa de dos plantas en Dorrego.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/162/ficha/casa-en-venta-en-juan-gilberto-godoy-123</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 50,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,11 +2128,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30.5</v>
+        <v>35.3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>1097.6</v>
+        <v>1100</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2181,28 +2181,28 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>81000</v>
+        <v>148000</v>
       </c>
       <c r="E25" t="n">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="F25" t="n">
-        <v>1051.9</v>
+        <v>808.7</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2250,33 +2250,33 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>DEPARTAMENTO UBICADO EN ZONA ALTAMENTE RESIDENCIAL Y COMERCIAL, FRENTE A PLAZA ITALIA, UBICADO EN 2° PISO POR ESCALERA.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://www.inmoclick.com.ar/4335-llopart-inmobiliaria/inmuebles/2892/ficha/departamento-en-venta-en-montevideo-613-plaza-italia</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 148,000 (Requiere contraoferta del 5.7%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20.9</v>
+        <v>32.2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80000</v>
+        <v>145000</v>
       </c>
       <c r="E26" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F26" t="n">
-        <v>888.9</v>
+        <v>1394.2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2324,33 +2324,33 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Departamento de categoría en pleno centro mendocino, Edificio Elipsium</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19113/ficha/departamento-en-venta-en-necochea-1400</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>31.2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="F27" t="n">
-        <v>1119.4</v>
+        <v>1250</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2398,99 +2398,769 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>Ente Inmobiliaria presenta una excelente oportunidad de adquisición en una de las zonas más destacadas de la ciudad.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3163/ficha/departamento-en-venta-en-peru-975</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>166</v>
+      </c>
+      <c r="F29" t="n">
+        <v>843.4</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>COCUCCI INMOBILIARIA VENDE , EXCELENTE SEMI PISO EN  PLENO CENTRO DE LA CIUDAD DE MENDOZA- SOBRE CALLE COLON AL 400   1ª PISO FRONTAL SUPER LUMINOSO. TOTALMENTE RECICLADO..</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19201/ficha/departamento-en-venta-en-colon-al-400</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>30</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>85</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1647.1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OPENHOUSE VENDE exclusivo departamento en Av. Colón.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2509/ficha/departamento-en-venta-en-av-colon</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>104</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1442.3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>El equipo ofrece a la venta.-</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20250/ficha/departamento-en-venta-en-necochea-400</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2142.9</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>El equipo Re/max Excelencia vende exclusivo piso en el corazón de la Quinta sección, sobre calle Rufino Ortega. El mismo forma parte de un complejo de solo cuatro unidades, de las cuales cada una constituye un piso completo. La unidad de referencia se encuentra en primer piso y al cual se accede directamente desde el ascensor (Desde el ascensor ingresa a su propio living), sin vecinos de piso lo cual permite privacidad, discreción y tranquilidad.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/1626-remax-excelencia/inmuebles/18665/ficha/departamento-en-venta-en-rufino-ortega-500</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>90</v>
+      </c>
+      <c r="F33" t="n">
+        <v>888.9</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>20</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D34" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>90</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1666.7</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>🛗 Edificio con ascensor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>86</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1744.2</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>EXCLUSIVO DEPARTAMENTO UBICADO EN CALLE RODRIGUEZ, ENTRE EMILIO CIVIT Y JULIO A ROCA, PRÓXIMO AL PARQUE GRAL SAN MARTÍN Y AL MICROCENTRO.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/4335-llopart-inmobiliaria/inmuebles/3106/ficha/departamento-en-venta-en-rodriguez-1059</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>67</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1119.4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Departamento En Las Tortugas</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 75,000)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>63300</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E37" t="n">
         <v>73</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F37" t="n">
         <v>867.1</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Estándar</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.9</v>
+        <v>62.2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95000</v>
+        <v>88000</v>
       </c>
       <c r="E6" t="n">
-        <v>294</v>
+        <v>99</v>
       </c>
       <c r="F6" t="n">
-        <v>323.1</v>
+        <v>888.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Re/Max Terruños ofrece a la venta propiedad ubicada en esquina, de construcción mixta, con 300 m² cubiertos aproximadamente, ideal tanto para vivienda familiar como para actividades profesionales.</t>
+          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2778/ficha/casa-en-venta-en-espana-2900</t>
+          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62.9</v>
+        <v>62.1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95000</v>
+        <v>110000</v>
       </c>
       <c r="E7" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F7" t="n">
-        <v>646.3</v>
+        <v>687.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
+          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,30 +944,30 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.8</v>
+        <v>56</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98000</v>
+        <v>120000</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>490</v>
+        <v>1237.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CASA EN VENTA</t>
+          <t>TRE INMOBILIARIA  VENDE Excelente departamento en 5ta Sección. Ubicado en una zona con rápida conectividad , este departamento combina amplitud, luminosidad y una ubicacióni privilegiada. Emplazado a pasos de la Casa de Gobierno, la ciclovía y con acceso inmediato a comercios, gastronomía y todos los medios de transporte.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/29719-martin-helder/inmuebles/52/ficha/casa-en-venta-en-beltran-425</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/880/ficha/departamento-en-venta-en-coronel-rodriguez-320-casi-vicente-gil-quinta-seccion</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62.2</v>
+        <v>50.8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88000</v>
+        <v>68000</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>888.9</v>
+        <v>906.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,28 +1071,28 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62.1</v>
+        <v>50.2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1101,17 +1101,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>110000</v>
+        <v>45000</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>687.5</v>
+        <v>600</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56</v>
+        <v>49.9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150000</v>
+        <v>70000</v>
       </c>
       <c r="E11" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>1515.2</v>
+        <v>1000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1214,37 +1214,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>RE/MAX Ofrece a la Venta departamento a metros de calle Emilio Civit, la calle más linda de Mendoza y a 5 minutos caminando del Parque General San Martín. Pensado para vivir cómodo todo el año, en un edificio con Amenities completos y seguridad las 24 horas.</t>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19860/ficha/departamento-en-venta-en-coronel-rodriguez-1000</t>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>50.2</v>
+        <v>48.1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45000</v>
+        <v>110000</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>600</v>
+        <v>1208.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en complejo cerrado sobre calle Huarpes 1945 - Sexta Sección - Ciudad - Mendoza.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/801/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>120000</v>
+        <v>90000</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
-        <v>1558.4</v>
+        <v>656.9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,11 +1388,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>49.9</v>
+        <v>45.7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70000</v>
+        <v>55000</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1462,11 +1462,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.3</v>
+        <v>44.5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="E15" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F15" t="n">
-        <v>656.9</v>
+        <v>852.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1510,37 +1510,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Dúplex tipo casa en Quinta Sección</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45.7</v>
+        <v>43.2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55000</v>
+        <v>75000</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="F16" t="n">
-        <v>625</v>
+        <v>543.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1589,32 +1589,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Amplio, luminoso y cómodo departamento ubicado en el Centro de la Cuidad de Mendoza, a metros de Av. San Martin. rodeado de comercios y galerías como así también de las actividades culturales, educativas y gastronómicas que presenta el centro mendocino. Se encuentra en un quinto piso con balcón a General Paz. cuenta con la siguiente distribución y comodidades, doble ingreso, hall de entrada, living comedor con salida a balcón, dos baños, tres dormitorios con amplísimos placares, cocina comedor, lavandería y dependencia de servicio. la propiedad se ofrece con cochera para un auto en Galería Bamac, con entrada por calle Buenos Aires.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/402/ficha/departamento-en-venta-en-general-paz-n0-65</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>44.9</v>
+        <v>40.5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77500</v>
+        <v>135000</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="F17" t="n">
-        <v>1174.2</v>
+        <v>592.1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1663,28 +1663,28 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Follow ofrece en venta un amplio departamento de 3 dormitorios, totalmente refaccionado, ubicado sobre calle Amigorena, en pleno centro de la Ciudad de Mendoza.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/274909-remax-follow/inmuebles/2357/ficha/departamento-en-venta-en-amigorena-0</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1565/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,500) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>44.5</v>
+        <v>40.5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1697,17 +1697,17 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150000</v>
+        <v>135000</v>
       </c>
       <c r="E18" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="F18" t="n">
-        <v>852.3</v>
+        <v>592.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1732,33 +1732,33 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dúplex tipo casa en Quinta Sección</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1485/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>43.4</v>
+        <v>40.2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>144400</v>
+        <v>90000</v>
       </c>
       <c r="E19" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>1110.8</v>
+        <v>796.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1806,27 +1806,27 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO EN VENTA 6 AMBIENTES CON AMPLIA COCHERA AV. GODOY CRUZ ESQUINA MITRE, CENTRO DE MENDOZA</t>
+          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19661/ficha/departamento-en-venta-en-avenida-godoy-cruz-400</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 144,400 (Requiere contraoferta del 3.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>38.5</v>
+        <v>39.1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50000</v>
+        <v>119000</v>
       </c>
       <c r="E23" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>322.6</v>
+        <v>1081.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2107,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ZELTA Inmobiliaria Vende Casa de dos plantas en Dorrego.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/302127-zelta-inmobiliaria/inmuebles/162/ficha/casa-en-venta-en-juan-gilberto-godoy-123</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 50,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 119,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,11 +2128,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>110000</v>
+        <v>132000</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F24" t="n">
-        <v>1100</v>
+        <v>1670.9</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2181,32 +2181,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado sobre calle Paso de Los Andes 940, entre calle Martin Zapata y Julio a Roca  - Quinta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/742/ficha/departamento-en-venta-en-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 132,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>32.7</v>
+        <v>35.3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>148000</v>
+        <v>110000</v>
       </c>
       <c r="E25" t="n">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>808.7</v>
+        <v>1100</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2250,33 +2250,33 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO UBICADO EN ZONA ALTAMENTE RESIDENCIAL Y COMERCIAL, FRENTE A PLAZA ITALIA, UBICADO EN 2° PISO POR ESCALERA.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4335-llopart-inmobiliaria/inmuebles/2892/ficha/departamento-en-venta-en-montevideo-613-plaza-italia</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 148,000 (Requiere contraoferta del 5.7%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>145000</v>
+        <v>65000</v>
       </c>
       <c r="E26" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F26" t="n">
-        <v>1394.2</v>
+        <v>915.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2324,33 +2324,33 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Departamento de categoría en pleno centro mendocino, Edificio Elipsium</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19113/ficha/departamento-en-venta-en-necochea-1400</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>31.2</v>
+        <v>32.5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="E27" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F27" t="n">
-        <v>1250</v>
+        <v>675.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2398,33 +2398,33 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Ente Inmobiliaria presenta una excelente oportunidad de adquisición en una de las zonas más destacadas de la ciudad.</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3163/ficha/departamento-en-venta-en-peru-975</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2437,17 +2437,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+        <v>88000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>91</v>
+      </c>
+      <c r="F28" t="n">
+        <v>967</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2481,17 +2477,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE | Exclusivos departamentos en pozo – Quinta Sección</t>
+          <t>Ubicado en una de las zonas más lindas del centro de Mendoza.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2240/ficha/departamento-en-venta-en-5ta-seccion</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/780/ficha/departamento-en-venta-en-gutierrez-al-400</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2502,7 +2498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2515,13 +2511,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>140000</v>
+        <v>135000</v>
       </c>
       <c r="E29" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="F29" t="n">
-        <v>843.4</v>
+        <v>1097.6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2530,7 +2526,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2550,22 +2546,22 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>COCUCCI INMOBILIARIA VENDE , EXCELENTE SEMI PISO EN  PLENO CENTRO DE LA CIUDAD DE MENDOZA- SOBRE CALLE COLON AL 400   1ª PISO FRONTAL SUPER LUMINOSO. TOTALMENTE RECICLADO..</t>
+          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17-cocucci-sa/inmuebles/19201/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2576,7 +2572,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2589,13 +2585,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>140000</v>
+        <v>92000</v>
       </c>
       <c r="E30" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F30" t="n">
-        <v>1647.1</v>
+        <v>1295.8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2604,7 +2600,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2629,17 +2625,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>OPENHOUSE VENDE exclusivo departamento en Av. Colón.</t>
+          <t>INMOBILIARIA TRE VENDE  esta excelente oportunidad de inversión o vivienda permanente en una de las zonas residenciales más consolidadas de la Ciudad. Ubicado en primer piso por escalera, la propiedad destaca por su amplitud y funcionalidad.Distribución y Características:</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/2509/ficha/departamento-en-venta-en-av-colon</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/782/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000)</t>
+          <t>Dentro del presupuesto (USD 92,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2650,7 +2646,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28.5</v>
+        <v>24.8</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2663,13 +2659,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="E31" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F31" t="n">
-        <v>1442.3</v>
+        <v>1756.8</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2698,27 +2694,27 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>El equipo ofrece a la venta.-</t>
+          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20250/ficha/departamento-en-venta-en-necochea-400</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -2737,13 +2733,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="E32" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F32" t="n">
-        <v>2142.9</v>
+        <v>888.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2752,7 +2748,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2772,33 +2768,33 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>El equipo Re/max Excelencia vende exclusivo piso en el corazón de la Quinta sección, sobre calle Rufino Ortega. El mismo forma parte de un complejo de solo cuatro unidades, de las cuales cada una constituye un piso completo. La unidad de referencia se encuentra en primer piso y al cual se accede directamente desde el ascensor (Desde el ascensor ingresa a su propio living), sin vecinos de piso lo cual permite privacidad, discreción y tranquilidad.</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/1626-remax-excelencia/inmuebles/18665/ficha/departamento-en-venta-en-rufino-ortega-500</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20.9</v>
+        <v>20</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2811,13 +2807,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80000</v>
+        <v>75000</v>
       </c>
       <c r="E33" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="F33" t="n">
-        <v>888.9</v>
+        <v>1119.4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2851,17 +2847,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2885,13 +2881,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>150000</v>
+        <v>63300</v>
       </c>
       <c r="E34" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F34" t="n">
-        <v>1666.7</v>
+        <v>867.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2920,247 +2916,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Departamento en Venta sobre Av. Belgrano, esquina Emilio Civit (sobre Heladería "Ferruccio Soppelsa")</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/19476/ficha/departamento-en-venta-en-avenida-belgrano-1000</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E35" t="n">
-        <v>86</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1744.2</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>EXCLUSIVO DEPARTAMENTO UBICADO EN CALLE RODRIGUEZ, ENTRE EMILIO CIVIT Y JULIO A ROCA, PRÓXIMO AL PARQUE GRAL SAN MARTÍN Y AL MICROCENTRO.</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/4335-llopart-inmobiliaria/inmuebles/3106/ficha/departamento-en-venta-en-rodriguez-1059</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>20</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E36" t="n">
-        <v>67</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E37" t="n">
-        <v>73</v>
-      </c>
-      <c r="F37" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85000</v>
+        <v>105000</v>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>702.5</v>
+        <v>1141.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,22 +553,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
+          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
+          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -583,17 +583,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58000</v>
+        <v>85000</v>
       </c>
       <c r="E3" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="F3" t="n">
-        <v>355.8</v>
+        <v>702.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -627,17 +627,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
+          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85000</v>
+        <v>58000</v>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="F4" t="n">
-        <v>658.9</v>
+        <v>355.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80000</v>
+        <v>85000</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F5" t="n">
-        <v>666.7</v>
+        <v>658.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CASA EN IMPORTANTE ESQUINA DE LA CIUDAD.</t>
+          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/136928-amtpropiedades/inmuebles/10/ficha/casa-en-venta-en-chile-y-coronel-plaza</t>
+          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88000</v>
+        <v>95000</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>888.9</v>
+        <v>646.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CASA EN VENTA 3 DORMITORIOS 2 BAÑOS SOBERANÍA NACIONAL MENDOZA - APTO CRÉDITO</t>
+          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/229229-remax-terrunos/inmuebles/2593/ficha/casa-en-venta-en-posta-retamo-0</t>
+          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -944,7 +944,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56</v>
+        <v>54.9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120000</v>
+        <v>128000</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>1237.1</v>
+        <v>1662.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -997,22 +997,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA  VENDE Excelente departamento en 5ta Sección. Ubicado en una zona con rápida conectividad , este departamento combina amplitud, luminosidad y una ubicacióni privilegiada. Emplazado a pasos de la Casa de Gobierno, la ciclovía y con acceso inmediato a comercios, gastronomía y todos los medios de transporte.</t>
+          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/880/ficha/departamento-en-venta-en-coronel-rodriguez-320-casi-vicente-gil-quinta-seccion</t>
+          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45000</v>
+        <v>95000</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>600</v>
+        <v>871.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,28 +1145,28 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
+          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
+          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70000</v>
+        <v>45000</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,11 +1240,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48.1</v>
+        <v>47.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>110000</v>
+        <v>90000</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>1208.8</v>
+        <v>656.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1293,32 +1293,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado en complejo cerrado sobre calle Huarpes 1945 - Sexta Sección - Ciudad - Mendoza.</t>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/801/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47.3</v>
+        <v>45.7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>90000</v>
+        <v>55000</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>656.9</v>
+        <v>625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,11 +1388,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45.7</v>
+        <v>44.5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55000</v>
+        <v>150000</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F14" t="n">
-        <v>625</v>
+        <v>852.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1436,33 +1436,33 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Dúplex tipo casa en Quinta Sección</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44.5</v>
+        <v>40.2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="E15" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="F15" t="n">
-        <v>852.3</v>
+        <v>796.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1510,33 +1510,33 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dúplex tipo casa en Quinta Sección</t>
+          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
+          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>43.2</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75000</v>
+        <v>145000</v>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>543.5</v>
+        <v>2071.4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1584,33 +1584,33 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Amplio, luminoso y cómodo departamento ubicado en el Centro de la Cuidad de Mendoza, a metros de Av. San Martin. rodeado de comercios y galerías como así también de las actividades culturales, educativas y gastronómicas que presenta el centro mendocino. Se encuentra en un quinto piso con balcón a General Paz. cuenta con la siguiente distribución y comodidades, doble ingreso, hall de entrada, living comedor con salida a balcón, dos baños, tres dormitorios con amplísimos placares, cocina comedor, lavandería y dependencia de servicio. la propiedad se ofrece con cochera para un auto en Galería Bamac, con entrada por calle Buenos Aires.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/9198-c-fainstein-rosas-negocios-inmobiliarios/inmuebles/402/ficha/departamento-en-venta-en-general-paz-n0-65</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>135000</v>
+        <v>145000</v>
       </c>
       <c r="E17" t="n">
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>592.1</v>
+        <v>2071.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1658,37 +1658,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1565/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40.5</v>
+        <v>35.3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E18" t="n">
-        <v>228</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>592.1</v>
+        <v>1100</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular propiedad en la Ciudad de Mendoza.</t>
+          <t>Departamento En Coronel Dorrego</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1485/ficha/departamento-en-venta-en-calle-cordoba-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40.2</v>
+        <v>32.8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90000</v>
+        <v>65000</v>
       </c>
       <c r="E19" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>796.5</v>
+        <v>915.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
+          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>145000</v>
+        <v>75000</v>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="F20" t="n">
-        <v>2071.4</v>
+        <v>675.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1880,33 +1880,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>40</v>
+        <v>30.5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>145000</v>
+        <v>135000</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
-        <v>2071.4</v>
+        <v>1097.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1954,37 +1954,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>39.8</v>
+        <v>30</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>140000</v>
+        <v>81000</v>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F22" t="n">
-        <v>1866.7</v>
+        <v>1051.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2028,33 +2028,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Estándar</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Departamento en Venta – Mendoza Capital</t>
+          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/276253-sere-inmobiliaria/inmuebles/136/ficha/departamento-en-venta-en-peatonal-y-9-de-julio</t>
+          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 140,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>39.1</v>
+        <v>20.9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>119000</v>
+        <v>80000</v>
       </c>
       <c r="E23" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>1081.8</v>
+        <v>888.9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE espectacular dúplex frontal en calle Montevideo de Ciudad de Mendoza.</t>
+          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1470/ficha/departamento-en-venta-en-calle-montevideo-ciudad</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 119,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>35.5</v>
+        <v>20</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>132000</v>
+        <v>75000</v>
       </c>
       <c r="E24" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>1670.9</v>
+        <v>1119.4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO ubicado sobre calle Paso de Los Andes 940, entre calle Martin Zapata y Julio a Roca  - Quinta Sección - Mendoza.</t>
+          <t>Departamento En Las Tortugas</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/742/ficha/departamento-en-venta-en-quinta-seccion-mendoza</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 132,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2202,11 +2202,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>35.3</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guaymallen</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>110000</v>
+        <v>63300</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>1100</v>
+        <v>867.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2255,686 +2255,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Departamento En Gobernador Benegas</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>Dentro del presupuesto (USD 63,300)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
-        <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>71</v>
-      </c>
-      <c r="F26" t="n">
-        <v>915.5</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E27" t="n">
-        <v>111</v>
-      </c>
-      <c r="F27" t="n">
-        <v>675.7</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>88000</v>
-      </c>
-      <c r="E28" t="n">
-        <v>91</v>
-      </c>
-      <c r="F28" t="n">
-        <v>967</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Ubicado en una de las zonas más lindas del centro de Mendoza.</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/780/ficha/departamento-en-venta-en-gutierrez-al-400</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 88,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>135000</v>
-      </c>
-      <c r="E29" t="n">
-        <v>123</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1097.6</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>92000</v>
-      </c>
-      <c r="E30" t="n">
-        <v>71</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1295.8</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA TRE VENDE  esta excelente oportunidad de inversión o vivienda permanente en una de las zonas residenciales más consolidadas de la Ciudad. Ubicado en primer piso por escalera, la propiedad destaca por su amplitud y funcionalidad.Distribución y Características:</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/782/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 92,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>130000</v>
-      </c>
-      <c r="E31" t="n">
-        <v>74</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1756.8</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>TRE INMOBILIARIA VENDE DEPARTAMENTO  ubicado sobre calle Huarpes 2046 - Sexta Sección - Mendoza.</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/844/ficha/departamento-en-venta-en-sexta-seccion-ciudad-mendoza</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E32" t="n">
-        <v>90</v>
-      </c>
-      <c r="F32" t="n">
-        <v>888.9</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>20</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E33" t="n">
-        <v>67</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1119.4</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Departamento En Las Tortugas</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>20</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>73</v>
-      </c>
-      <c r="F34" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>105000</v>
+        <v>89999</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>1141.3</v>
+        <v>818.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -553,47 +553,47 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EUSKADI VENDE EXCELENTE DEPARTAMENTO APTO CREDITO HIPOTECARIO EN ALTA MENDOZA - CIUDAD</t>
+          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/60778-euskadi-inmobiliaria-desarrollos/inmuebles/710/ficha/departamento-en-venta-en-doctor-salomon-miyara</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 105,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.5</v>
+        <v>63.8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85000</v>
+        <v>65000</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>702.5</v>
+        <v>81.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
+          <t>Lote Venta Moreno Barrio Privado Prados Del Oeste 2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
+          <t>https://terreno.mercadolibre.com.ar/MLA-1506999247-lote-venta-moreno-barrio-privado-prados-del-oeste-2-_JM</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 65,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58000</v>
+        <v>85000</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>355.8</v>
+        <v>702.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
+          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85000</v>
+        <v>58000</v>
       </c>
       <c r="E5" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="F5" t="n">
-        <v>658.9</v>
+        <v>355.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>En la hermosa ciudad de Mendoza, en la 6.ª Sección Residencial Norte, se encuentra esta propiedad ideal para aquellos que buscan invertir en un proyecto de reciclaje o construcción de departamentos. La casa, de 50 años de antigüedad, se encuentra totalmente construida en material y cuenta con un lote de 10 x 25.50 metros.</t>
+          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/298285-pablo-catalano/inmuebles/3/ficha/casa-en-venta-en-maure-250</t>
+          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,7 +796,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95000</v>
+        <v>85000</v>
       </c>
       <c r="E6" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F6" t="n">
-        <v>646.3</v>
+        <v>534.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dúplex Interno en Venta | Centro de Mendoza (Apto Crédito)</t>
+          <t>- 🏠 Plantas: 2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/61179-branko-molinari/inmuebles/240/ficha/casa-en-venta-en-rondeau-mendoza</t>
+          <t>https://www.inmoclick.com.ar/311873-carolina-munoz/inmuebles/1/ficha/casa-en-venta-en-remedios-de-escalada</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,7 +870,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>110000</v>
+        <v>120000</v>
       </c>
       <c r="E7" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>687.5</v>
+        <v>869.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ofrece una excelente propiedad en una ubicación estratégica a minutos del parque san martín , centros de salud , colegios.</t>
+          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20387/ficha/casa-en-venta-en-huarpes-1800</t>
+          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,30 +944,30 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54.9</v>
+        <v>61.6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>128000</v>
+        <v>120000</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F8" t="n">
-        <v>1662.3</v>
+        <v>810.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -997,28 +997,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TRE Inmobiliaria ofrece a la venta  dúplex de dos dormitorios con cochera en quinta sección residencial sur, calle O. V. Andrade muy cerca de ciclovía y metrotranvía , parque General San Martin, UTN, Arístides Villanueva .</t>
+          <t>Dueño vende .</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/12572-tre-inmobiliaria/inmuebles/697/ficha/departamento-en-venta-en-quinta-seccion-p-a</t>
+          <t>https://www.inmoclick.com.ar/19594-yanet-biluron/inmuebles/3/ficha/casa-en-venta-en-bolivia-3360</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | Dentro del presupuesto (USD 128,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50.8</v>
+        <v>61.1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68000</v>
+        <v>130000</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="F9" t="n">
-        <v>906.7</v>
+        <v>541.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1071,28 +1071,28 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
+          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
+          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.3</v>
+        <v>52.9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1101,17 +1101,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95000</v>
+        <v>80000</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>871.6</v>
+        <v>640</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1145,47 +1145,47 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>VENTA DEPARTAMENTO – GODOY CRUZ</t>
+          <t>Venta Casa 2 Plantas + 2 Dptos  Ideal P/alquiler</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/268429-re-max-vendimia/inmuebles/1974/ficha/departamento-en-venta-en-avenida-san-martin-100</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4103976960-venta-casa-2-plantas-2-dptos-ideal-palquiler-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50.2</v>
+        <v>52.9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>45000</v>
+        <v>72000</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="F11" t="n">
-        <v>600</v>
+        <v>461.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>El equipo de ofrece este amplio y luminoso departamento en venta, ubicado en la intersección de San Juan y Republica de Siria, en una zona estratégica de la ciudad de Mendoza.</t>
+          <t>Venta Casa Con Dpto En Bombal Sur Ideal Inversión</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/18796/ficha/departamento-en-venta-en-san-juan-400</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4028498792-venta-casa-con-dpto-en-bombal-sur-ideal-inversion-_JM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 45,000) | 🛗 Edificio con ascensor</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 72,000)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,26 +1240,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47.3</v>
+        <v>52.9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="F12" t="n">
-        <v>656.9</v>
+        <v>441.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1293,17 +1293,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+          <t>C21 Inmoandes Vende Casa En B° Viajantes - Dorrego</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4072927150-c21-inmoandes-vende-casa-en-b-viajantes-dorrego-_JM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1314,7 +1314,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.7</v>
+        <v>52.9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55000</v>
+        <v>75000</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>625</v>
+        <v>539.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Venta De Departamento Planta Alta Coronel Dorrego</t>
+          <t>Casa En Venta En Dorrego</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2130172827-venta-de-departamento-planta-alta-coronel-dorrego-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4100116772-casa-en-venta-en-dorrego-_JM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1388,35 +1388,35 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44.5</v>
+        <v>52.8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>150000</v>
+        <v>87500</v>
       </c>
       <c r="E14" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="F14" t="n">
-        <v>852.3</v>
+        <v>546.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No/Duda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1436,52 +1436,52 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dúplex tipo casa en Quinta Sección</t>
+          <t>Venta Casa Dorrego Guaymallén</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/669/ficha/departamento-en-venta-en-julio-a-roca-y-olascoaga-quinta-seccion-mendoza</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-3341239884-venta-casa-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Publicado en USD 150,000 (Requiere contraoferta del 7.1%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>40.2</v>
+        <v>52.8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90000</v>
+        <v>87500</v>
       </c>
       <c r="E15" t="n">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="F15" t="n">
-        <v>796.5</v>
+        <v>546.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Departamento en VENTA, en el tradicional Edificio La Micela III. Ubicado en calle Colón, entre Mitre y Chile, Ciudad de Mendoza.</t>
+          <t>Venta Casa Dorrego Guaymallén</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/279041-kw-mendoza/inmuebles/520/ficha/departamento-en-venta-en-colon-al-400</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-1932694261-venta-casa-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
+        <v>52.2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>145000</v>
+        <v>98000</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="F16" t="n">
-        <v>2071.4</v>
+        <v>583.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1584,52 +1584,52 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Venta Casa En Dorrego, 3 Habitaciones</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-3510108914-venta-casa-en-dorrego-3-habitaciones-_JM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40</v>
+        <v>52.1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>145000</v>
+        <v>100000</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>194</v>
       </c>
       <c r="F17" t="n">
-        <v>2071.4</v>
+        <v>515.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1658,33 +1658,33 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Venta Departamento 2 Habitaciones Bombal</t>
+          <t>Century21 López Vende Casa En Dorrego Guaymallén</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4086921576-century21-lopez-vende-casa-en-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>35.3</v>
+        <v>52.1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1693,17 +1693,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>110000</v>
+        <v>99000</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="F18" t="n">
-        <v>1100</v>
+        <v>405.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Departamento En Coronel Dorrego</t>
+          <t>Casa En Venta En Dorrego Con Gran Potencial</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-3879359370-casa-en-venta-en-dorrego-con-gran-potencial-_JM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 110,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 99,000)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1758,26 +1758,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32.8</v>
+        <v>51.6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65000</v>
+        <v>110000</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="F19" t="n">
-        <v>915.5</v>
+        <v>594.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1811,47 +1811,47 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>OPENHOUSE INMOBILIARIA VENDE cómodo departamento en calle Catamarca.</t>
+          <t>Venta - Casa En Dorrego - 3 Dormitorios   Estudio / 2 Baños</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/280057-openhouse-inmobiliaria/inmuebles/1694/ficha/departamento-en-venta-en-catamarca</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-2052068639-venta-casa-en-dorrego-3-dormitorios-estudio-2-banos-_JM</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000) | 🛗 Edificio con ascensor</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32.5</v>
+        <v>51.6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="E20" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="F20" t="n">
-        <v>675.7</v>
+        <v>618</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1885,47 +1885,47 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Riccardi Propiedades vende departamento con excelente ubicación en micro centro de Mendoza capital ,ubicado en calle Garibali y esquina San Juan , este departamento es ideal para quienes quieren estar conectados con la ciudad , de fácil acceso a Escuelas y todo tipo de servicios que ofrece su ubicación.</t>
+          <t>Casa En Venta, Dorrego, Guaymallén, Apto Crédito</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/3331-riccardi-propiedades/inmuebles/547/ficha/departamento-en-venta-en-garibaldi-93</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-2164633269-casa-en-venta-dorrego-guaymallen-apto-credito-_JM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30.5</v>
+        <v>51.3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>135000</v>
+        <v>115000</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F21" t="n">
-        <v>1097.6</v>
+        <v>871.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1959,32 +1959,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PANI SAR SAR INMOBILIARIA VENDE EXCLUSIVO DEPARTAMENTO EN EL RECONOCIDO EDIFICIO ELIPSIUM, SOBRE CALLE NECOCHEA 473, UBICADO EN PLENO CORAZÓN DE LA CIUDAD DE MENDOZA.</t>
+          <t>Venta Casa Alto Dorrego Guaymallen</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/5587-pani-sar-sar-inmobiliaria/inmuebles/602/ficha/departamento-en-venta-en-necochea-473-edificio-elipsium</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-2192308265-venta-casa-alto-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 135,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 115,000)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>50.8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>81000</v>
+        <v>68000</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" t="n">
-        <v>1051.9</v>
+        <v>906.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No/Duda</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2028,52 +2028,52 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Estándar</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ACL PROPIEDADES – VENDE DPTO EN CIUDAD - Ubicado en Godoy Cruz esquina 25 de Mayo, en una excelente zona de Ciudad. El departamento cuenta con 83,32 m² de sup. propia, distribuido en una sola planta y con excelentes vistas. Distribución: posee doble ingreso, Cocina con comedor de diario y balcón, Amplio living comedor con balcón, 3 dormitorios con placares, Toilette y Baño completo. Detalles y mejoras:</t>
+          <t>DRUMMOND NEGOCIOS INMOBILIARIOS VENDE</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/76974-acl-propiedades/inmuebles/591/ficha/departamento-en-venta-en-godoy-cruz-580</t>
+          <t>https://www.inmoclick.com.ar/124071-drummond-negocios-inmobiliarios/inmuebles/43/ficha/departamento-en-venta-en-espana-y-gutierrez</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 81,000) | 💡 Publicación indica apertura a ofertas o permutas</t>
+          <t>Dentro del presupuesto (USD 68,000) | 🔥 Red de gas natural confirmada | 🚗 Cuenta con cochera</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20.9</v>
+        <v>50.5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80000</v>
+        <v>130000</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="F23" t="n">
-        <v>888.9</v>
+        <v>1101.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2107,32 +2107,32 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Departamento En Venta - Benegas - Godoy Cruz - Mendoza</t>
+          <t>Venta Duplex Dorrego Guaymallen Mendoza</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-3756706742-departamento-en-venta-benegas-godoy-cruz-mendoza-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4098159170-venta-duplex-dorrego-guaymallen-mendoza-_JM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 80,000)</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75000</v>
+        <v>120000</v>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F24" t="n">
-        <v>1119.4</v>
+        <v>1558.4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2181,94 +2181,2536 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Departamento En Las Tortugas</t>
+          <t>DEPARTAMENTO 3 AMBIENTES EN VENTA MENDOZA SEXTA SECCIÓN - APTO CRÉDITO</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-2133562131-departamento-en-las-tortugas-_JM</t>
+          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20466/ficha/departamento-en-venta-en-martinez-de-rozas-0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 75,000)</t>
+          <t>Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera | 🛗 Edificio con ascensor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>145000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>327</v>
+      </c>
+      <c r="F25" t="n">
+        <v>443.4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Venta Casa Y Departamento Cochera Ciudad Mendoza</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-4051224196-venta-casa-y-departamento-cochera-ciudad-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Venta de Departamento – Cuarta Sección Oeste</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://www.inmoclick.com.ar/3076-ente-inmobiliaria/inmuebles/3329/ficha/departamento-en-venta-en-fray-inalican-363</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 70,000) | 🚗 Cuenta con cochera</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>221</v>
+      </c>
+      <c r="F27" t="n">
+        <v>633.5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Espectacular Casa En Venta En Dorrego</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3995094286-espectacular-casa-en-venta-en-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>745.6</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Venta De Casa + Departamento A Estrenar</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-2232985563-venta-de-casa-departamento-a-estrenar-_JM</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>137</v>
+      </c>
+      <c r="F29" t="n">
+        <v>656.9</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Venta Excelente Departamento Tipo Casa En Mendoza</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1808643353-venta-excelente-departamento-tipo-casa-en-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>98000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>395</v>
+      </c>
+      <c r="F30" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Complejo De 4 Unidades. Duplex + 3 Departamentos A Reciclar</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-2125784545-complejo-de-4-unidades-duplex-3-departamentos-a-reciclar-_JM</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>289</v>
+      </c>
+      <c r="F31" t="n">
+        <v>346</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Venta De Casa + Departamento Dorrego Guaymallen</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3950647808-venta-de-casa-departamento-dorrego-guaymallen-_JM</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>149000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>141</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1056.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Casa En Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3637330824-casa-en-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Publicado en USD 149,000 (Requiere contraoferta del 6.4%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>40</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>145000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>70</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2071.4</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4099145060-venta-departamento-2-habitaciones-bombal-_JM</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>145000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>70</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2071.4</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Venta Departamento 2 Habitaciones Bombal</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4055629092-venta-departamento-2-habitaciones-bombal-_JM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Publicado en USD 145,000 (Requiere contraoferta del 3.6%) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>67000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>228</v>
+      </c>
+      <c r="F35" t="n">
+        <v>293.9</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Venta Casa+depto  Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3974941690-venta-casadepto-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 67,000)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>77900</v>
+      </c>
+      <c r="E36" t="n">
+        <v>190</v>
+      </c>
+      <c r="F36" t="n">
+        <v>410</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Casa En Venta Barrio Trapiche 3 Dormitorios- Godoy Cruz- Mendoza</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3718800398-casa-en-venta-barrio-trapiche-3-dormitorios-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 77,900)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>182</v>
+      </c>
+      <c r="F37" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Casa En Venta A Remodelar En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-1948712741-casa-en-venta-a-remodelar-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>136</v>
+      </c>
+      <c r="F38" t="n">
+        <v>588.2</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Venta De Casa</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3809096022-venta-de-casa-_JM</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>177</v>
+      </c>
+      <c r="F39" t="n">
+        <v>497.2</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Casa En Godoy Cruz, Barrio Decavial</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-1854515963-casa-en-godoy-cruz-barrio-decavial-_JM</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 88,000)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>234</v>
+      </c>
+      <c r="F40" t="n">
+        <v>406</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Casa En Venta Apta Credito Barrio Supe Godoy Cruz Mendoza</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-1812749365-casa-en-venta-apta-credito-barrio-supe-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>170</v>
+      </c>
+      <c r="F41" t="n">
+        <v>588.2</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Venta Casa 3 Domit. Godoy Cruz Apta Credito</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-4132638026-venta-casa-3-domit-godoy-cruz-apta-credito-_JM</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 100,000)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>175</v>
+      </c>
+      <c r="F42" t="n">
+        <v>628.6</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Casa En Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-1779109501-casa-en-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 110,000)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>90</v>
+      </c>
+      <c r="F43" t="n">
+        <v>444.4</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Casa En Villa Hipodromo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3501150246-casa-en-villa-hipodromo-_JM</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 40,000)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>200</v>
+      </c>
+      <c r="F44" t="n">
+        <v>600</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Casa+ Dos Deptos, B° Jardín Serrano, Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-4123427708-casa-dos-deptos-b-jardin-serrano-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000)</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Guaymallen</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Departamento En Coronel Dorrego</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-3024664484-departamento-en-coronel-dorrego-_JM</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 110,000)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>216</v>
+      </c>
+      <c r="F46" t="n">
+        <v>314.8</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Venta De Casa Y Departamento Calle Aristobulo Del Valle-godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-4128507110-venta-de-casa-y-departamento-calle-aristobulo-del-valle-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000)</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>215</v>
+      </c>
+      <c r="F47" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Venta De Casa Y Departamento O Negocio Comercial</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-1948712309-venta-de-casa-y-departamento-o-negocio-comercial-_JM</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 68,000)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E48" t="n">
+        <v>180</v>
+      </c>
+      <c r="F48" t="n">
+        <v>305.6</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Venta Oportunidad Casa + Departamento Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-2211338699-venta-oportunidad-casa-departamento-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 55,000)</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>53000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>131</v>
+      </c>
+      <c r="F49" t="n">
+        <v>404.6</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Trapiche Casa Y Departamento</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-4026113040-trapiche-casa-y-departamento-_JM</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 53,000)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>69900</v>
+      </c>
+      <c r="E50" t="n">
+        <v>148</v>
+      </c>
+      <c r="F50" t="n">
+        <v>472.3</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Vendo Casa 3 Habitaciones Mas Departamento</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3896201338-vendo-casa-3-habitaciones-mas-departamento-_JM</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 69,900)</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>87000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>204</v>
+      </c>
+      <c r="F51" t="n">
+        <v>426.5</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Venta De Casa 2 Dorm. + Departamento 3 Dorm.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-3949768066-venta-de-casa-2-dorm-departamento-3-dorm-_JM</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,000)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>149</v>
+      </c>
+      <c r="F52" t="n">
+        <v>604</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Excelente Casa Y Departamento Interno</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-2222331929-excelente-casa-y-departamento-interno-_JM</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 90,000)</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>32</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>105</v>
+      </c>
+      <c r="F53" t="n">
+        <v>619</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Casa Con Departamento Independiente</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-2116722067-casa-con-departamento-independiente-_JM</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 65,000)</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>32</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E54" t="n">
+        <v>174</v>
+      </c>
+      <c r="F54" t="n">
+        <v>546</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Venta  Casa + Departamento Barrio Fuchs Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-2134705917-venta-casa-departamento-barrio-fuchs-godoy-cruz-_JM</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 95,000)</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>123600</v>
+      </c>
+      <c r="E55" t="n">
+        <v>230</v>
+      </c>
+      <c r="F55" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Venta De Casa Y Departamento En Barrio Trapiche</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-4035968914-venta-de-casa-y-departamento-en-barrio-trapiche-_JM</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 123,600)</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>30</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E56" t="n">
+        <v>137</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1021.9</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Venta De Casa Esquina Y Departamento A Terminar</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.ar/MLA-1948711555-venta-de-casa-esquina-y-departamento-a-terminar-_JM</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 140,000)</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>20</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Godoy Cruz</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>63300</v>
-      </c>
-      <c r="E25" t="n">
-        <v>73</v>
-      </c>
-      <c r="F25" t="n">
-        <v>867.1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No/Duda</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Departamento En Gobernador Benegas</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://departamento.mercadolibre.com.ar/MLA-1713408519-departamento-en-gobernador-benegas-_JM</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Dentro del presupuesto (USD 63,300)</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="D57" t="n">
+        <v>133000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1773.3</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Departamento Frente Al Mar (1659)</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-1507878043-departamento-frente-al-mar-1659-_JM</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 133,000)</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>20</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>65</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1846.2</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No/Duda</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Departamento En Venta Godoy Cruz Mendoza</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>https://departamento.mercadolibre.com.ar/MLA-4095525316-departamento-en-venta-godoy-cruz-mendoza-_JM</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Dentro del presupuesto (USD 120,000)</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | ⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>

--- a/data/oportunidades_mendoza.xlsx
+++ b/data/oportunidades_mendoza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,26 +500,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100</v>
+        <v>63.8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>89999</v>
+        <v>65000</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>818.2</v>
+        <v>81.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -553,32 +553,32 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Departamento en Microcentro en Venta – 3 Dormitorios / 2 Baños / Cochera/ Amoblado</t>
+          <t>Lote Venta Moreno Barrio Privado Prados Del Oeste 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20134/ficha/departamento-en-venta-en-corrientes-100</t>
+          <t>https://terreno.mercadolibre.com.ar/MLA-1506999247-lote-venta-moreno-barrio-privado-prados-del-oeste-2-_JM</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 89,999) | 🛡️ Cuenta con seguridad 24 hs / barrio privado | 🚗 Cuenta con cochera</t>
+          <t>Dentro del presupuesto (USD 65,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Consultar conexión a red de gas natural</t>
+          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.8</v>
+        <v>52.9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65000</v>
+        <v>80000</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
-        <v>81.2</v>
+        <v>640</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,47 +627,47 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lote Venta Moreno Barrio Privado Prados Del Oeste 2</t>
+          <t>Venta Casa 2 Plantas + 2 Dptos  Ideal P/alquiler</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.ar/MLA-1506999247-lote-venta-moreno-barrio-privado-prados-del-oeste-2-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4103976960-venta-casa-2-plantas-2-dptos-ideal-palquiler-_JM</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Dentro del presupuesto (USD 65,000) | 🛡️ Cuenta con seguridad 24 hs / barrio privado</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 80,000)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚠️ Ubicado en Godoy Cruz fuera de Barrio Bombal (-15 pts) | Consultar conexión a red de gas natural</t>
+          <t>⚠️ Sin seguridad 24 hs ni barrio privado (penalizado en puntaje) | Consultar conexión a red de gas natural</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63.5</v>
+        <v>52.9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85000</v>
+        <v>72000</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>702.5</v>
+        <v>461.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -701,17 +701,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Equipo RE/MAX ofrece a la venta departamento céntrico ubicado en planta baja, dentro de complejo cerrado.</t>
+          <t>Venta Casa Con Dpto En Bombal Sur Ideal Inversión</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/17515-remax-solutions/inmuebles/20400/ficha/departamento-en-venta-en-avenida-espana-1700</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4028498792-venta-casa-con-dpto-en-bombal-sur-ideal-inversion-_JM</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>📍 Excelente ubicación: Barrio Bombal / Bombal Sur (Godoy Cruz) | ✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 72,000)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -722,11 +722,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63.5</v>
+        <v>52.9</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>58000</v>
+        <v>75000</v>
       </c>
       <c r="E5" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>355.8</v>
+        <v>441.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -775,17 +775,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Ubicación Granaderos 2020 esq. Parana (6ta Sección), inmediaciones a calle Suipacha .Terreno 174 m2., Cubiertos 163 m2</t>
+          <t>C21 Inmoandes Vende Casa En B° Viajantes - Dorrego</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/440-fernando-puebla-inmobiliaria/inmuebles/925/ficha/casa-en-venta-en-granaderos-2020-ciudad-mendoza</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4072927150-c21-inmoandes-vende-casa-en-b-viajantes-dorrego-_JM</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 58,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63.5</v>
+        <v>52.9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
-        <v>534.6</v>
+        <v>539.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>- 🏠 Plantas: 2</t>
+          <t>Casa En Venta En Dorrego</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311873-carolina-munoz/inmuebles/1/ficha/casa-en-venta-en-remedios-de-escalada</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4100116772-casa-en-venta-en-dorrego-_JM</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 85,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 75,000)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -870,11 +870,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61.6</v>
+        <v>52.8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120000</v>
+        <v>87500</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="F7" t="n">
-        <v>869.6</v>
+        <v>546.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Hermosa propiedad! Ubicación privilegiada en sexta sección, orientación este sobre calle Bolivia entre Italia y Hossay, cómoda, luminosa y muy segura.</t>
+          <t>Venta Casa Dorrego Guaymallén</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/4201-vanina-rubio/inmuebles/256/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-3341239884-venta-casa-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -944,11 +944,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61.6</v>
+        <v>52.8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120000</v>
+        <v>87500</v>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F8" t="n">
-        <v>810.8</v>
+        <v>546.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dueño vende .</t>
+          <t>Venta Casa Dorrego Guaymallén</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/19594-yanet-biluron/inmuebles/3/ficha/casa-en-venta-en-bolivia-3360</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-1932694261-venta-casa-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 120,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 87,500)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1018,11 +1018,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61.1</v>
+        <v>52.2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>130000</v>
+        <v>98000</v>
       </c>
       <c r="E9" t="n">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>541.7</v>
+        <v>583.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>🏡 DUEÑO VENDE – CASA ESQUINA EN BARRIO SANIDAD, MENDOZA</t>
+          <t>Venta Casa En Dorrego, 3 Habitaciones</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.inmoclick.com.ar/311675-mica-mutt/inmuebles/6/ficha/casa-en-venta-en-san-jose-1903</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-3510108914-venta-casa-en-dorrego-3-habitaciones-_JM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 130,000) | 🚗 Cuenta con cochera</t>
+          <t>✨ Amplio: cuenta con 3+ dormitorios o 4+ ambientes (+10 pts) | Dentro del presupuesto (USD 98,000)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1092,11 +1092,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52.9</v>
+        <v>52.1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Guaymallen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="F10" t="n">
-        <v>640</v>
+        <v>515.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Venta Casa 2 Plantas + 2 Dptos  Ideal P/alquiler</t>
+          <t>Century21 López Vende Casa En Dorrego Guaymallén</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://casa.mercadolibre.com.ar/MLA-4103976960-venta-casa-2-plantas-2-dptos-ideal-palquiler-_JM</t>
+          <t>https://casa.mercadolibre.com.ar/MLA-4086921576-century21-lopez-vende-casa-en-dorrego-guaymallen-_JM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-      